--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -245,8 +245,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W28" headerRowCount="1">
-  <autoFilter ref="A17:W28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W26" headerRowCount="1">
+  <autoFilter ref="A17:W26"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +12.86% / +12.88% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.33957356103763</v>
+        <v>-11.68395842288645</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="O3" t="n">
         <v>43.3</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>74.09999999999999</v>
+        <v>78.277</v>
       </c>
       <c r="V3" t="n">
-        <v>19.093</v>
+        <v>19.984</v>
       </c>
       <c r="W3" t="n">
-        <v>-40.074</v>
+        <v>-39.407</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +12.86% / +12.88% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-12.33957356103763</v>
+        <v>-11.68395842288645</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,7 +1009,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="O6" t="n">
         <v>43.3</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>74.09999999999999</v>
+        <v>78.277</v>
       </c>
       <c r="V6" t="n">
-        <v>19.093</v>
+        <v>19.984</v>
       </c>
       <c r="W6" t="n">
-        <v>-40.074</v>
+        <v>-39.407</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | SAHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.12% / +0.21% / -1.15%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.759722999036975</v>
+        <v>-4.452690982762753</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,7 +1096,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.8</v>
+        <v>134.6</v>
       </c>
       <c r="O7" t="n">
         <v>46.9</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>75.73399999999999</v>
+        <v>81.889</v>
       </c>
       <c r="V7" t="n">
-        <v>30.323</v>
+        <v>30.743</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.546</v>
+        <v>-37.12</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +0.51% / +0.94% / -0.53% | PETKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.98% / +0.00% / -2.04% | KCHOL.IS: +0.51% / +0.94% / -0.53% | PETKM.IS: -2.53% / +1.94% / -3.24%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.943116548288067</v>
+        <v>-11.2855233690596</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,7 +1183,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.2</v>
+        <v>191.8</v>
       </c>
       <c r="O8" t="n">
         <v>47.2</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>57.834</v>
+        <v>55.481</v>
       </c>
       <c r="V8" t="n">
-        <v>19.568</v>
+        <v>17.786</v>
       </c>
       <c r="W8" t="n">
-        <v>-20.218</v>
+        <v>-22.571</v>
       </c>
     </row>
     <row r="9">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +12.86% / +12.88% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-12.33957356103763</v>
+        <v>-11.68395842288645</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,7 +1270,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="O9" t="n">
         <v>43.3</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>74.09999999999999</v>
+        <v>78.277</v>
       </c>
       <c r="V9" t="n">
-        <v>19.093</v>
+        <v>19.984</v>
       </c>
       <c r="W9" t="n">
-        <v>-40.074</v>
+        <v>-39.407</v>
       </c>
     </row>
     <row r="10">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALTNY.IS, EUREN.IS, TOASO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ALTNY.IS: 2026-09-10 | EUREN.IS: 2026-09-10 | TOASO.IS: 2026-09-11</t>
+          <t>TOASO.IS: 2026-09-11</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -2.09% / +2.18% / -2.30% | EUREN.IS: -0.53% / +2.28% / -0.51% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>TOASO.IS: -2.86% / +0.00% / -3.84%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.89989816434251</v>
+        <v>-7.033361173465869</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,7 +1357,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>177.5</v>
+        <v>177.1</v>
       </c>
       <c r="O10" t="n">
         <v>48.3</v>
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>10.072</v>
+        <v>10.218</v>
       </c>
       <c r="T10" t="n">
-        <v>10.072</v>
+        <v>10.218</v>
       </c>
       <c r="U10" t="n">
-        <v>13.948</v>
+        <v>12.576</v>
       </c>
       <c r="V10" t="n">
-        <v>5.949</v>
+        <v>4.673</v>
       </c>
       <c r="W10" t="n">
-        <v>-11.44</v>
+        <v>-12.812</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="O12" t="n">
         <v>47.7</v>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.86% / +12.88% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>11.93533637679618</v>
+        <v>11.17342779149584</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1594,7 +1594,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="O13" t="n">
         <v>45.1</v>
@@ -1617,13 +1617,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>93.288</v>
+        <v>91.97199999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>106.249</v>
+        <v>104.846</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.962</v>
+        <v>-19.278</v>
       </c>
     </row>
     <row r="14">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1665,14 +1665,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.86% / +12.88% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>11.93533637679618</v>
+        <v>11.17342779149584</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1681,7 +1681,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="O14" t="n">
         <v>45.1</v>
@@ -1704,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>93.288</v>
+        <v>91.97199999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>106.249</v>
+        <v>104.846</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.962</v>
+        <v>-19.278</v>
       </c>
     </row>
     <row r="16">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +12.86% / +12.88% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.33957356103763</v>
+        <v>-11.68395842288645</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,7 +1894,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="O18" t="n">
         <v>43.3</v>
@@ -1917,13 +1917,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>74.09999999999999</v>
+        <v>78.277</v>
       </c>
       <c r="V18" t="n">
-        <v>19.093</v>
+        <v>19.984</v>
       </c>
       <c r="W18" t="n">
-        <v>-40.074</v>
+        <v>-39.407</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +0.51% / +0.94% / -0.53% | PETKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.98% / +0.00% / -2.04% | KCHOL.IS: +0.51% / +0.94% / -0.53% | PETKM.IS: -2.53% / +1.94% / -3.24%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.943116548288067</v>
+        <v>-11.2855233690596</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,7 +2137,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.2</v>
+        <v>191.8</v>
       </c>
       <c r="O21" t="n">
         <v>47.2</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>57.834</v>
+        <v>55.481</v>
       </c>
       <c r="V21" t="n">
-        <v>19.568</v>
+        <v>17.786</v>
       </c>
       <c r="W21" t="n">
-        <v>-20.218</v>
+        <v>-22.571</v>
       </c>
     </row>
     <row r="22">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | SAHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.12% / +0.21% / -1.15%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.759722999036975</v>
+        <v>-4.452690982762753</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,7 +2226,7 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.8</v>
+        <v>134.6</v>
       </c>
       <c r="O22" t="n">
         <v>46.9</v>
@@ -2249,13 +2249,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>75.73399999999999</v>
+        <v>81.889</v>
       </c>
       <c r="V22" t="n">
-        <v>30.323</v>
+        <v>30.743</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.546</v>
+        <v>-37.12</v>
       </c>
     </row>
     <row r="23">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.86% / +12.88% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>11.93533637679618</v>
+        <v>11.17342779149584</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2315,7 +2315,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="O23" t="n">
         <v>45.1</v>
@@ -2338,13 +2338,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>93.288</v>
+        <v>91.97199999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>106.249</v>
+        <v>104.846</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.962</v>
+        <v>-19.278</v>
       </c>
     </row>
     <row r="24">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2388,14 +2388,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.86% / +12.88% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>11.93533637679618</v>
+        <v>11.17342779149584</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2404,7 +2404,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="O24" t="n">
         <v>45.1</v>
@@ -2427,13 +2427,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>93.288</v>
+        <v>91.97199999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>106.249</v>
+        <v>104.846</v>
       </c>
       <c r="W24" t="n">
-        <v>-17.962</v>
+        <v>-19.278</v>
       </c>
     </row>
     <row r="25">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N26" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="O26" t="n">
         <v>47.7</v>
@@ -2608,22 +2608,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ALTNY.IS, EUREN.IS, TOASO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ALTNY.IS: 2026-09-10 | EUREN.IS: 2026-09-10 | TOASO.IS: 2026-09-11</t>
+          <t>TOASO.IS: 2026-09-11</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -2.09% / +2.18% / -2.30% | EUREN.IS: -0.53% / +2.28% / -0.51% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>TOASO.IS: -2.86% / +0.00% / -3.84%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.89989816434251</v>
+        <v>-7.033361173465869</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2647,7 +2647,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N27" t="n">
-        <v>177.5</v>
+        <v>177.1</v>
       </c>
       <c r="O27" t="n">
         <v>48.3</v>
@@ -2661,22 +2661,22 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>10.072</v>
+        <v>10.218</v>
       </c>
       <c r="T27" t="n">
-        <v>10.072</v>
+        <v>10.218</v>
       </c>
       <c r="U27" t="n">
-        <v>13.948</v>
+        <v>12.576</v>
       </c>
       <c r="V27" t="n">
-        <v>5.949</v>
+        <v>4.673</v>
       </c>
       <c r="W27" t="n">
-        <v>-11.44</v>
+        <v>-12.812</v>
       </c>
     </row>
   </sheetData>
@@ -2698,7 +2698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>ENERY.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.38% / +5.84% / -1.29% | ENERY.IS: +9.92% / +9.92% / -3.45%</t>
+          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>5.209312045290782</v>
+        <v>5.590666465264316</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.5</v>
+        <v>92.8</v>
       </c>
       <c r="O3" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>319.614</v>
+        <v>291.746</v>
       </c>
       <c r="V3" t="n">
-        <v>111.941</v>
+        <v>112.709</v>
       </c>
       <c r="W3" t="n">
-        <v>-23.733</v>
+        <v>-20.662</v>
       </c>
     </row>
     <row r="4">
@@ -2953,25 +2953,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.24959773313421</v>
+        <v>-11.28509221401519</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2980,36 +2992,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>118.6</v>
+        <v>120.8</v>
       </c>
       <c r="O4" t="n">
-        <v>46.9</v>
+        <v>45.9</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.929</v>
+        <v>25.958</v>
       </c>
       <c r="T4" t="n">
-        <v>25.929</v>
+        <v>25.958</v>
       </c>
       <c r="U4" t="n">
-        <v>58.058</v>
+        <v>57.995</v>
       </c>
       <c r="V4" t="n">
-        <v>19.407</v>
+        <v>19.359</v>
       </c>
       <c r="W4" t="n">
-        <v>-55.328</v>
+        <v>-55.391</v>
       </c>
     </row>
     <row r="5">
@@ -3028,22 +3040,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>ENERY.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3051,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.38% / +5.84% / -1.29% | ENERY.IS: +9.92% / +9.92% / -3.45%</t>
+          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>5.188250140922235</v>
+        <v>5.569528217365249</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3067,10 +3079,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="O5" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3090,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>316.391</v>
+        <v>288.736</v>
       </c>
       <c r="V5" t="n">
-        <v>93.00700000000001</v>
+        <v>93.70699999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-23.5</v>
+        <v>-20.456</v>
       </c>
     </row>
     <row r="6">
@@ -3115,12 +3127,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3138,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.48% / +20.01% / -1.13% | CANTE.IS: +5.78% / +15.33% / -2.99% | ENERY.IS: +12.45% / +12.49% / -0.50% | SOKM.IS: +4.61% / +5.14% / -2.94% | TKFEN.IS: +14.88% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | CANTE.IS: +5.72% / +15.33% / -2.99% | ENERY.IS: +13.32% / +14.65% / -0.50% | SOKM.IS: +3.71% / +5.44% / -2.94% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.349349339393774</v>
+        <v>-7.758112081454938</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3154,13 +3166,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138.3</v>
+        <v>138</v>
       </c>
       <c r="O6" t="n">
         <v>43.1</v>
       </c>
       <c r="P6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3177,13 +3189,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>26.069</v>
+        <v>25.513</v>
       </c>
       <c r="V6" t="n">
-        <v>15.189</v>
+        <v>14.681</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.056</v>
+        <v>-39.612</v>
       </c>
     </row>
     <row r="7">
@@ -3202,25 +3214,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.24959773313421</v>
+        <v>-11.28509221401519</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3229,36 +3253,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>118.6</v>
+        <v>120.8</v>
       </c>
       <c r="O7" t="n">
-        <v>46.9</v>
+        <v>45.9</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.929</v>
+        <v>25.958</v>
       </c>
       <c r="T7" t="n">
-        <v>25.929</v>
+        <v>25.958</v>
       </c>
       <c r="U7" t="n">
-        <v>58.058</v>
+        <v>57.995</v>
       </c>
       <c r="V7" t="n">
-        <v>19.407</v>
+        <v>19.359</v>
       </c>
       <c r="W7" t="n">
-        <v>-55.328</v>
+        <v>-55.391</v>
       </c>
     </row>
     <row r="8">
@@ -3277,12 +3301,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3300,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.92% / +3.54% / -3.83% | ENERY.IS: +12.45% / +12.49% / -0.50% | ISCTR.IS: +1.13% / +1.43% / -0.67%</t>
+          <t>CANTE.IS: -1.97% / +3.54% / -3.83% | ENERY.IS: +13.32% / +14.65% / -0.50% | ISCTR.IS: +0.57% / +1.45% / -0.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3273749473108545</v>
+        <v>0.3755830373549429</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3316,7 +3340,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.1</v>
+        <v>152.8</v>
       </c>
       <c r="O8" t="n">
         <v>42.4</v>
@@ -3339,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>28.565</v>
+        <v>29.565</v>
       </c>
       <c r="V8" t="n">
-        <v>5.153</v>
+        <v>5.204</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.115</v>
+        <v>-28.257</v>
       </c>
     </row>
     <row r="9">
@@ -3364,12 +3388,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3391,7 +3415,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3439,25 +3463,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>38.04089454478734</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.035858361542709</v>
+        <v>-3.071345346052845</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3466,21 +3502,21 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.2</v>
+        <v>114.5</v>
       </c>
       <c r="O10" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>20.181</v>
@@ -3489,13 +3525,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.676</v>
+        <v>10.635</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.456</v>
+        <v>-2.491</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.184</v>
+        <v>-27.224</v>
       </c>
     </row>
     <row r="11">
@@ -3514,25 +3550,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>63.58450648919234</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.1667183383606</v>
+        <v>-11.20224596569523</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3541,36 +3589,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>178.7</v>
+        <v>180.8</v>
       </c>
       <c r="O11" t="n">
-        <v>52.1</v>
+        <v>51.4</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>24.618</v>
+        <v>24.648</v>
       </c>
       <c r="T11" t="n">
-        <v>24.618</v>
+        <v>24.648</v>
       </c>
       <c r="U11" t="n">
-        <v>33.934</v>
+        <v>33.88</v>
       </c>
       <c r="V11" t="n">
-        <v>6.526</v>
+        <v>6.483</v>
       </c>
       <c r="W11" t="n">
-        <v>-43.739</v>
+        <v>-43.792</v>
       </c>
     </row>
     <row r="12">
@@ -3589,12 +3637,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3612,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.48% / +20.01% / -1.13% | TKFEN.IS: +14.88% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>10.17796909328752</v>
+        <v>9.012541089943404</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3628,7 +3676,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="O12" t="n">
         <v>43.3</v>
@@ -3651,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>43.265</v>
+        <v>41.75</v>
       </c>
       <c r="V12" t="n">
-        <v>53.522</v>
+        <v>51.899</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.023</v>
+        <v>-18.538</v>
       </c>
     </row>
     <row r="13">
@@ -3671,57 +3719,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENERY.IS, ENJSA.IS</t>
+          <t>ENERY.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-03</t>
+          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>55.65159289883979</v>
+        <v>86.93022416585528</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.92% / +9.92% / -3.45% | ENJSA.IS: +1.24% / +3.48% / -2.80%</t>
+          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-15.6923812251032</v>
+        <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>5.583505794380317</v>
+        <v>5.590666465264316</v>
       </c>
       <c r="L13" t="n">
-        <v>32.200703125</v>
+        <v>28.4081875</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>76.3</v>
+        <v>92.8</v>
       </c>
       <c r="O13" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3732,19 +3780,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>19.807</v>
+        <v>18.106</v>
       </c>
       <c r="T13" t="n">
-        <v>19.807</v>
+        <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>225.119</v>
+        <v>291.746</v>
       </c>
       <c r="V13" t="n">
-        <v>96.89700000000001</v>
+        <v>112.709</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.063</v>
+        <v>-20.662</v>
       </c>
     </row>
     <row r="14">
@@ -3758,57 +3806,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ENERY.IS, ENJSA.IS</t>
+          <t>ENERY.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-03</t>
+          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>55.65159289883979</v>
+        <v>83.80706321463933</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.92% / +9.92% / -3.45% | ENJSA.IS: +1.24% / +3.48% / -2.80%</t>
+          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-15.6923812251032</v>
+        <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>5.583505794380317</v>
+        <v>5.569528217365249</v>
       </c>
       <c r="L14" t="n">
-        <v>32.200703125</v>
+        <v>32.3216328125</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>76.3</v>
+        <v>82</v>
       </c>
       <c r="O14" t="n">
-        <v>45.2</v>
+        <v>43.1</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3819,19 +3867,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>19.807</v>
+        <v>21.096</v>
       </c>
       <c r="T14" t="n">
-        <v>19.807</v>
+        <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>225.119</v>
+        <v>288.736</v>
       </c>
       <c r="V14" t="n">
-        <v>96.89700000000001</v>
+        <v>93.70699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.063</v>
+        <v>-20.456</v>
       </c>
     </row>
     <row r="16">
@@ -3961,12 +4009,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 | 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3976,22 +4024,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>ENERY.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3999,14 +4047,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.38% / +5.84% / -1.29% | ENERY.IS: +9.92% / +9.92% / -3.45%</t>
+          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>5.209312045290782</v>
+        <v>5.590666465264316</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4015,10 +4063,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.5</v>
+        <v>92.8</v>
       </c>
       <c r="O18" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4038,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>319.614</v>
+        <v>291.746</v>
       </c>
       <c r="V18" t="n">
-        <v>111.941</v>
+        <v>112.709</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.733</v>
+        <v>-20.662</v>
       </c>
     </row>
     <row r="19">
@@ -4065,25 +4113,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.24959773313421</v>
+        <v>-11.28509221401519</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4092,42 +4152,42 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>118.6</v>
+        <v>120.8</v>
       </c>
       <c r="O19" t="n">
-        <v>46.9</v>
+        <v>45.9</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.929</v>
+        <v>25.958</v>
       </c>
       <c r="T19" t="n">
-        <v>25.929</v>
+        <v>25.958</v>
       </c>
       <c r="U19" t="n">
-        <v>58.058</v>
+        <v>57.995</v>
       </c>
       <c r="V19" t="n">
-        <v>19.407</v>
+        <v>19.359</v>
       </c>
       <c r="W19" t="n">
-        <v>-55.328</v>
+        <v>-55.391</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4142,22 +4202,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>ENERY.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4165,14 +4225,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.38% / +5.84% / -1.29% | ENERY.IS: +9.92% / +9.92% / -3.45%</t>
+          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>5.188250140922235</v>
+        <v>5.569528217365249</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4181,10 +4241,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="O20" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4204,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>316.391</v>
+        <v>288.736</v>
       </c>
       <c r="V20" t="n">
-        <v>93.00700000000001</v>
+        <v>93.70699999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-23.5</v>
+        <v>-20.456</v>
       </c>
     </row>
     <row r="21">
@@ -4231,25 +4291,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>63.58450648919234</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.1667183383606</v>
+        <v>-11.20224596569523</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4258,36 +4330,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>178.7</v>
+        <v>180.8</v>
       </c>
       <c r="O21" t="n">
-        <v>52.1</v>
+        <v>51.4</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>24.618</v>
+        <v>24.648</v>
       </c>
       <c r="T21" t="n">
-        <v>24.618</v>
+        <v>24.648</v>
       </c>
       <c r="U21" t="n">
-        <v>33.934</v>
+        <v>33.88</v>
       </c>
       <c r="V21" t="n">
-        <v>6.526</v>
+        <v>6.483</v>
       </c>
       <c r="W21" t="n">
-        <v>-43.739</v>
+        <v>-43.792</v>
       </c>
     </row>
     <row r="22">
@@ -4308,12 +4380,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4331,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.48% / +20.01% / -1.13% | CANTE.IS: +5.78% / +15.33% / -2.99% | ENERY.IS: +12.45% / +12.49% / -0.50% | SOKM.IS: +4.61% / +5.14% / -2.94% | TKFEN.IS: +14.88% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | CANTE.IS: +5.72% / +15.33% / -2.99% | ENERY.IS: +13.32% / +14.65% / -0.50% | SOKM.IS: +3.71% / +5.44% / -2.94% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.349349339393774</v>
+        <v>-7.758112081454938</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4347,13 +4419,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138.3</v>
+        <v>138</v>
       </c>
       <c r="O22" t="n">
         <v>43.1</v>
       </c>
       <c r="P22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4370,79 +4442,79 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>26.069</v>
+        <v>25.513</v>
       </c>
       <c r="V22" t="n">
-        <v>15.189</v>
+        <v>14.681</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.056</v>
+        <v>-39.612</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENERY.IS, ENJSA.IS</t>
+          <t>CANTE.IS, ENERY.IS, ISCTR.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-03</t>
+          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>55.65159289883979</v>
+        <v>48.21914524341393</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.92% / +9.92% / -3.45% | ENJSA.IS: +1.24% / +3.48% / -2.80%</t>
+          <t>CANTE.IS: -1.97% / +3.54% / -3.83% | ENERY.IS: +13.32% / +14.65% / -0.50% | ISCTR.IS: +0.57% / +1.45% / -0.66%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-15.6923812251032</v>
+        <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>5.583505794380317</v>
+        <v>0.3755830373549429</v>
       </c>
       <c r="L23" t="n">
-        <v>32.200703125</v>
+        <v>16.16102048107813</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>76.3</v>
+        <v>152.8</v>
       </c>
       <c r="O23" t="n">
-        <v>45.2</v>
+        <v>42.4</v>
       </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4450,88 +4522,88 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>19.807</v>
+        <v>21.943</v>
       </c>
       <c r="T23" t="n">
-        <v>19.807</v>
+        <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>225.119</v>
+        <v>29.565</v>
       </c>
       <c r="V23" t="n">
-        <v>96.89700000000001</v>
+        <v>5.204</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.063</v>
+        <v>-28.257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>55.65159289883979</v>
+        <v>38.04089454478734</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.92% / +9.92% / -3.45% | ENJSA.IS: +1.24% / +3.48% / -2.80%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-15.6923812251032</v>
+        <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>5.583505794380317</v>
+        <v>-3.071345346052845</v>
       </c>
       <c r="L24" t="n">
-        <v>32.200703125</v>
+        <v>5.808640829284117</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>76.3</v>
+        <v>114.5</v>
       </c>
       <c r="O24" t="n">
-        <v>45.2</v>
+        <v>49.8</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4539,354 +4611,188 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>19.807</v>
+        <v>20.181</v>
       </c>
       <c r="T24" t="n">
-        <v>19.807</v>
+        <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>225.119</v>
+        <v>10.635</v>
       </c>
       <c r="V24" t="n">
-        <v>96.89700000000001</v>
+        <v>-2.491</v>
       </c>
       <c r="W24" t="n">
-        <v>-17.063</v>
+        <v>-27.224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>CANTE.IS, ENERY.IS, ISCTR.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>48.21914524341393</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>CANTE.IS: -1.92% / +3.54% / -3.83% | ENERY.IS: +12.45% / +12.49% / -0.50% | ISCTR.IS: +1.13% / +1.43% / -0.67%</t>
-        </is>
-      </c>
+        <v>28.40086810394897</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>21.4002873140223</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3273749473108545</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L25" t="n">
-        <v>16.16102048107813</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>153.1</v>
+        <v>74.7</v>
       </c>
       <c r="O25" t="n">
-        <v>42.4</v>
+        <v>49.3</v>
       </c>
       <c r="P25" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>21.943</v>
+        <v>13.28</v>
       </c>
       <c r="T25" t="n">
-        <v>21.943</v>
+        <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>28.565</v>
+        <v>7.136</v>
       </c>
       <c r="V25" t="n">
-        <v>5.153</v>
+        <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-28.115</v>
+        <v>-16.407</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>38.04089454478734</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>6.880672511445463</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>13.75066280702224</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.035858361542709</v>
+        <v>9.012541089943404</v>
       </c>
       <c r="L26" t="n">
-        <v>5.808640829284117</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M26" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>113.2</v>
+        <v>47.6</v>
       </c>
       <c r="O26" t="n">
-        <v>50.4</v>
+        <v>43.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>20.181</v>
+        <v>28.439</v>
       </c>
       <c r="T26" t="n">
-        <v>20.181</v>
+        <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>10.676</v>
+        <v>41.75</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.456</v>
+        <v>51.899</v>
       </c>
       <c r="W26" t="n">
-        <v>-27.184</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DD_KAR_TOP3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>28.40086810394897</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>15.38514121842653</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-6.616392554049999</v>
-      </c>
-      <c r="L27" t="n">
-        <v>5.127814043936619</v>
-      </c>
-      <c r="M27" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N27" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="T27" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="U27" t="n">
-        <v>7.136</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-0.962</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-16.407</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>6.880672511445463</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +9.48% / +20.01% / -1.13% | TKFEN.IS: +14.88% / +31.83% / -0.56%</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>-18.9000927288166</v>
-      </c>
-      <c r="K28" t="n">
-        <v>10.17796909328752</v>
-      </c>
-      <c r="L28" t="n">
-        <v>31.31195090134997</v>
-      </c>
-      <c r="M28" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N28" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>28.439</v>
-      </c>
-      <c r="T28" t="n">
-        <v>28.439</v>
-      </c>
-      <c r="U28" t="n">
-        <v>43.265</v>
-      </c>
-      <c r="V28" t="n">
-        <v>53.522</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-17.023</v>
+        <v>-18.538</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.68395842288645</v>
+        <v>-11.23317023879997</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>78.277</v>
+        <v>79.187</v>
       </c>
       <c r="V3" t="n">
-        <v>19.984</v>
+        <v>20.597</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.407</v>
+        <v>-38.497</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.68395842288645</v>
+        <v>-11.23317023879997</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>78.277</v>
+        <v>79.187</v>
       </c>
       <c r="V6" t="n">
-        <v>19.984</v>
+        <v>20.597</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.407</v>
+        <v>-38.497</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.12% / +0.21% / -1.15%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.452690982762753</v>
+        <v>-4.577625008043729</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>81.889</v>
+        <v>81.652</v>
       </c>
       <c r="V7" t="n">
-        <v>30.743</v>
+        <v>30.572</v>
       </c>
       <c r="W7" t="n">
-        <v>-37.12</v>
+        <v>-37.358</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.98% / +0.00% / -2.04% | KCHOL.IS: +0.51% / +0.94% / -0.53% | PETKM.IS: -2.53% / +1.94% / -3.24%</t>
+          <t>ALARK.IS: -3.77% / +0.00% / -3.75% | KCHOL.IS: +0.38% / +1.47% / -0.53% | PETKM.IS: -3.10% / +1.94% / -3.32%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-11.2855233690596</v>
+        <v>-12.03206209363676</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>55.481</v>
+        <v>54.173</v>
       </c>
       <c r="V8" t="n">
-        <v>17.786</v>
+        <v>16.795</v>
       </c>
       <c r="W8" t="n">
-        <v>-22.571</v>
+        <v>-23.879</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.68395842288645</v>
+        <v>-11.23317023879997</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>78.277</v>
+        <v>79.187</v>
       </c>
       <c r="V9" t="n">
-        <v>19.984</v>
+        <v>20.597</v>
       </c>
       <c r="W9" t="n">
-        <v>-39.407</v>
+        <v>-38.497</v>
       </c>
     </row>
     <row r="10">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TOASO.IS: 2026-09-11</t>
+          <t>TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TOASO.IS: -2.86% / +0.00% / -3.84%</t>
+          <t>TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.033361173465869</v>
+        <v>-7.448063190891519</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,10 +1357,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>177.1</v>
+        <v>177.6</v>
       </c>
       <c r="O10" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -1374,19 +1374,19 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>10.218</v>
+        <v>10.619</v>
       </c>
       <c r="T10" t="n">
-        <v>10.218</v>
+        <v>10.619</v>
       </c>
       <c r="U10" t="n">
-        <v>12.576</v>
+        <v>12.073</v>
       </c>
       <c r="V10" t="n">
-        <v>4.673</v>
+        <v>4.206</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.812</v>
+        <v>-13.315</v>
       </c>
     </row>
     <row r="11">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-11</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
+          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>11.17342779149584</v>
+        <v>10.82326005816285</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1594,13 +1594,13 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>59.7</v>
+        <v>60.2</v>
       </c>
       <c r="O13" t="n">
-        <v>45.1</v>
+        <v>44.7</v>
       </c>
       <c r="P13" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1617,13 +1617,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>91.97199999999999</v>
+        <v>91.367</v>
       </c>
       <c r="V13" t="n">
-        <v>104.846</v>
+        <v>104.2</v>
       </c>
       <c r="W13" t="n">
-        <v>-19.278</v>
+        <v>-19.883</v>
       </c>
     </row>
     <row r="14">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-11</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1665,14 +1665,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
+          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>11.17342779149584</v>
+        <v>10.82326005816285</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1681,13 +1681,13 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>59.7</v>
+        <v>60.2</v>
       </c>
       <c r="O14" t="n">
-        <v>45.1</v>
+        <v>44.7</v>
       </c>
       <c r="P14" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1704,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>91.97199999999999</v>
+        <v>91.367</v>
       </c>
       <c r="V14" t="n">
-        <v>104.846</v>
+        <v>104.2</v>
       </c>
       <c r="W14" t="n">
-        <v>-19.278</v>
+        <v>-19.883</v>
       </c>
     </row>
     <row r="16">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +13.69% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.68395842288645</v>
+        <v>-11.23317023879997</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1917,13 +1917,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>78.277</v>
+        <v>79.187</v>
       </c>
       <c r="V18" t="n">
-        <v>19.984</v>
+        <v>20.597</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.407</v>
+        <v>-38.497</v>
       </c>
     </row>
     <row r="19">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.98% / +0.00% / -2.04% | KCHOL.IS: +0.51% / +0.94% / -0.53% | PETKM.IS: -2.53% / +1.94% / -3.24%</t>
+          <t>ALARK.IS: -3.77% / +0.00% / -3.75% | KCHOL.IS: +0.38% / +1.47% / -0.53% | PETKM.IS: -3.10% / +1.94% / -3.32%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.2855233690596</v>
+        <v>-12.03206209363676</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>55.481</v>
+        <v>54.173</v>
       </c>
       <c r="V21" t="n">
-        <v>17.786</v>
+        <v>16.795</v>
       </c>
       <c r="W21" t="n">
-        <v>-22.571</v>
+        <v>-23.879</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.12% / +0.21% / -1.15%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.452690982762753</v>
+        <v>-4.577625008043729</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2249,13 +2249,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>81.889</v>
+        <v>81.652</v>
       </c>
       <c r="V22" t="n">
-        <v>30.743</v>
+        <v>30.572</v>
       </c>
       <c r="W22" t="n">
-        <v>-37.12</v>
+        <v>-37.358</v>
       </c>
     </row>
     <row r="23">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-11</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
+          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>11.17342779149584</v>
+        <v>10.82326005816285</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2315,13 +2315,13 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>59.7</v>
+        <v>60.2</v>
       </c>
       <c r="O23" t="n">
-        <v>45.1</v>
+        <v>44.7</v>
       </c>
       <c r="P23" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2338,13 +2338,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>91.97199999999999</v>
+        <v>91.367</v>
       </c>
       <c r="V23" t="n">
-        <v>104.846</v>
+        <v>104.2</v>
       </c>
       <c r="W23" t="n">
-        <v>-19.278</v>
+        <v>-19.883</v>
       </c>
     </row>
     <row r="24">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-11</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2388,14 +2388,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +13.69% / +15.11% / -0.46% | KUYAS.IS: -2.29% / +0.34% / -2.55%</t>
+          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>11.17342779149584</v>
+        <v>10.82326005816285</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2404,13 +2404,13 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>59.7</v>
+        <v>60.2</v>
       </c>
       <c r="O24" t="n">
-        <v>45.1</v>
+        <v>44.7</v>
       </c>
       <c r="P24" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2427,13 +2427,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>91.97199999999999</v>
+        <v>91.367</v>
       </c>
       <c r="V24" t="n">
-        <v>104.846</v>
+        <v>104.2</v>
       </c>
       <c r="W24" t="n">
-        <v>-19.278</v>
+        <v>-19.883</v>
       </c>
     </row>
     <row r="25">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TOASO.IS: 2026-09-11</t>
+          <t>TOASO.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TOASO.IS: -2.86% / +0.00% / -3.84%</t>
+          <t>TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.033361173465869</v>
+        <v>-7.448063190891519</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2647,10 +2647,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N27" t="n">
-        <v>177.1</v>
+        <v>177.6</v>
       </c>
       <c r="O27" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -2664,19 +2664,19 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>10.218</v>
+        <v>10.619</v>
       </c>
       <c r="T27" t="n">
-        <v>10.218</v>
+        <v>10.619</v>
       </c>
       <c r="U27" t="n">
-        <v>12.576</v>
+        <v>12.073</v>
       </c>
       <c r="V27" t="n">
-        <v>4.673</v>
+        <v>4.206</v>
       </c>
       <c r="W27" t="n">
-        <v>-12.812</v>
+        <v>-13.315</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>5.590666465264316</v>
+        <v>6.417902914621387</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>291.746</v>
+        <v>294.815</v>
       </c>
       <c r="V3" t="n">
-        <v>112.709</v>
+        <v>114.376</v>
       </c>
       <c r="W3" t="n">
-        <v>-20.662</v>
+        <v>-17.593</v>
       </c>
     </row>
     <row r="4">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>5.569528217365249</v>
+        <v>6.396599061847152</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>288.736</v>
+        <v>291.782</v>
       </c>
       <c r="V5" t="n">
-        <v>93.70699999999999</v>
+        <v>95.224</v>
       </c>
       <c r="W5" t="n">
-        <v>-20.456</v>
+        <v>-17.411</v>
       </c>
     </row>
     <row r="6">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, ENERY.IS, SOKM.IS, TKFEN.IS</t>
+          <t>BRSAN.IS, CANTE.IS, ENERY.IS, GUBRF.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | CANTE.IS: +5.72% / +15.33% / -2.99% | ENERY.IS: +13.32% / +14.65% / -0.50% | SOKM.IS: +3.71% / +5.44% / -2.94% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | CANTE.IS: +6.53% / +15.33% / -2.99% | ENERY.IS: +14.24% / +14.65% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.758112081454938</v>
+        <v>-7.936175822329239</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3166,13 +3166,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138</v>
+        <v>138.5</v>
       </c>
       <c r="O6" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="P6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3189,13 +3189,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>25.513</v>
+        <v>25.27</v>
       </c>
       <c r="V6" t="n">
-        <v>14.681</v>
+        <v>14.46</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.612</v>
+        <v>-39.854</v>
       </c>
     </row>
     <row r="7">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.97% / +3.54% / -3.83% | ENERY.IS: +13.32% / +14.65% / -0.50% | ISCTR.IS: +0.57% / +1.45% / -0.66%</t>
+          <t>CANTE.IS: -1.23% / +3.54% / -3.83% | ENERY.IS: +14.24% / +14.65% / -0.50% | ISCTR.IS: +0.36% / +1.96% / -0.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3755830373549429</v>
+        <v>0.7414445465500297</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>29.565</v>
+        <v>30.037</v>
       </c>
       <c r="V8" t="n">
-        <v>5.204</v>
+        <v>5.587</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.257</v>
+        <v>-27.785</v>
       </c>
     </row>
     <row r="9">
@@ -3493,7 +3493,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.071345346052845</v>
+        <v>-3.071095994391637</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3525,7 +3525,7 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.635</v>
+        <v>10.636</v>
       </c>
       <c r="V10" t="n">
         <v>-2.491</v>
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.012541089943404</v>
+        <v>8.069960920368358</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>41.75</v>
+        <v>40.524</v>
       </c>
       <c r="V12" t="n">
-        <v>51.899</v>
+        <v>50.585</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.538</v>
+        <v>-19.764</v>
       </c>
     </row>
     <row r="13">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>5.590666465264316</v>
+        <v>6.417902914621387</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3786,13 +3786,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>291.746</v>
+        <v>294.815</v>
       </c>
       <c r="V13" t="n">
-        <v>112.709</v>
+        <v>114.376</v>
       </c>
       <c r="W13" t="n">
-        <v>-20.662</v>
+        <v>-17.593</v>
       </c>
     </row>
     <row r="14">
@@ -3834,14 +3834,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>5.569528217365249</v>
+        <v>6.396599061847152</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3873,13 +3873,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>288.736</v>
+        <v>291.782</v>
       </c>
       <c r="V14" t="n">
-        <v>93.70699999999999</v>
+        <v>95.224</v>
       </c>
       <c r="W14" t="n">
-        <v>-20.456</v>
+        <v>-17.411</v>
       </c>
     </row>
     <row r="16">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>5.590666465264316</v>
+        <v>6.417902914621387</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4086,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>291.746</v>
+        <v>294.815</v>
       </c>
       <c r="V18" t="n">
-        <v>112.709</v>
+        <v>114.376</v>
       </c>
       <c r="W18" t="n">
-        <v>-20.662</v>
+        <v>-17.593</v>
       </c>
     </row>
     <row r="19">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.77% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>5.569528217365249</v>
+        <v>6.396599061847152</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4264,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>288.736</v>
+        <v>291.782</v>
       </c>
       <c r="V20" t="n">
-        <v>93.70699999999999</v>
+        <v>95.224</v>
       </c>
       <c r="W20" t="n">
-        <v>-20.456</v>
+        <v>-17.411</v>
       </c>
     </row>
     <row r="21">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, ENERY.IS, SOKM.IS, TKFEN.IS</t>
+          <t>BRSAN.IS, CANTE.IS, ENERY.IS, GUBRF.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | CANTE.IS: +5.72% / +15.33% / -2.99% | ENERY.IS: +13.32% / +14.65% / -0.50% | SOKM.IS: +3.71% / +5.44% / -2.94% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | CANTE.IS: +6.53% / +15.33% / -2.99% | ENERY.IS: +14.24% / +14.65% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.758112081454938</v>
+        <v>-7.936175822329239</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4419,13 +4419,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138</v>
+        <v>138.5</v>
       </c>
       <c r="O22" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="P22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4442,13 +4442,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>25.513</v>
+        <v>25.27</v>
       </c>
       <c r="V22" t="n">
-        <v>14.681</v>
+        <v>14.46</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.612</v>
+        <v>-39.854</v>
       </c>
     </row>
     <row r="23">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.97% / +3.54% / -3.83% | ENERY.IS: +13.32% / +14.65% / -0.50% | ISCTR.IS: +0.57% / +1.45% / -0.66%</t>
+          <t>CANTE.IS: -1.23% / +3.54% / -3.83% | ENERY.IS: +14.24% / +14.65% / -0.50% | ISCTR.IS: +0.36% / +1.96% / -0.66%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3755830373549429</v>
+        <v>0.7414445465500297</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4531,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>29.565</v>
+        <v>30.037</v>
       </c>
       <c r="V23" t="n">
-        <v>5.204</v>
+        <v>5.587</v>
       </c>
       <c r="W23" t="n">
-        <v>-28.257</v>
+        <v>-27.785</v>
       </c>
     </row>
     <row r="24">
@@ -4588,7 +4588,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.071345346052845</v>
+        <v>-3.071095994391637</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4620,7 +4620,7 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.635</v>
+        <v>10.636</v>
       </c>
       <c r="V24" t="n">
         <v>-2.491</v>
@@ -4747,14 +4747,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.85% / +20.01% / -1.13% | TKFEN.IS: +15.04% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>9.012541089943404</v>
+        <v>8.069960920368358</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4786,13 +4786,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>41.75</v>
+        <v>40.524</v>
       </c>
       <c r="V26" t="n">
-        <v>51.899</v>
+        <v>50.585</v>
       </c>
       <c r="W26" t="n">
-        <v>-18.538</v>
+        <v>-19.764</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.23317023879997</v>
+        <v>-11.51313114891116</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>79.187</v>
+        <v>78.622</v>
       </c>
       <c r="V3" t="n">
-        <v>20.597</v>
+        <v>20.216</v>
       </c>
       <c r="W3" t="n">
-        <v>-38.497</v>
+        <v>-39.063</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.23317023879997</v>
+        <v>-11.51313114891116</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>79.187</v>
+        <v>78.622</v>
       </c>
       <c r="V6" t="n">
-        <v>20.597</v>
+        <v>20.216</v>
       </c>
       <c r="W6" t="n">
-        <v>-38.497</v>
+        <v>-39.063</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
+          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.577625008043729</v>
+        <v>-4.934633682820555</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>81.652</v>
+        <v>80.97199999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>30.572</v>
+        <v>30.083</v>
       </c>
       <c r="W7" t="n">
-        <v>-37.358</v>
+        <v>-38.037</v>
       </c>
     </row>
     <row r="8">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALARK.IS, KCHOL.IS, PETKM.IS</t>
+          <t>ENERY.IS, KCHOL.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-11 | KCHOL.IS: 2026-09-10 | PETKM.IS: 2026-09-11</t>
+          <t>ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10 | PETKM.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -3.77% / +0.00% / -3.75% | KCHOL.IS: +0.38% / +1.47% / -0.53% | PETKM.IS: -3.10% / +1.94% / -3.32%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +0.51% / +1.47% / -0.53% | PETKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-12.03206209363676</v>
+        <v>-12.36822629324095</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>191.8</v>
+        <v>192.8</v>
       </c>
       <c r="O8" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>54.173</v>
+        <v>53.584</v>
       </c>
       <c r="V8" t="n">
-        <v>16.795</v>
+        <v>16.348</v>
       </c>
       <c r="W8" t="n">
-        <v>-23.879</v>
+        <v>-24.468</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.23317023879997</v>
+        <v>-11.51313114891116</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>79.187</v>
+        <v>78.622</v>
       </c>
       <c r="V9" t="n">
-        <v>20.597</v>
+        <v>20.216</v>
       </c>
       <c r="W9" t="n">
-        <v>-38.497</v>
+        <v>-39.063</v>
       </c>
     </row>
     <row r="10">
@@ -1348,7 +1348,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.448063190891519</v>
+        <v>-7.589190302070103</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1374,19 +1374,19 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>10.619</v>
+        <v>10.755</v>
       </c>
       <c r="T10" t="n">
-        <v>10.619</v>
+        <v>10.755</v>
       </c>
       <c r="U10" t="n">
-        <v>12.073</v>
+        <v>11.903</v>
       </c>
       <c r="V10" t="n">
-        <v>4.206</v>
+        <v>4.047</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.315</v>
+        <v>-13.485</v>
       </c>
     </row>
     <row r="11">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>10.82326005816285</v>
+        <v>10.87182432070222</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1617,13 +1617,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>91.367</v>
+        <v>91.45099999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>104.2</v>
+        <v>104.29</v>
       </c>
       <c r="W13" t="n">
-        <v>-19.883</v>
+        <v>-19.799</v>
       </c>
     </row>
     <row r="14">
@@ -1665,14 +1665,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>10.82326005816285</v>
+        <v>10.87182432070222</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1704,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>91.367</v>
+        <v>91.45099999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>104.2</v>
+        <v>104.29</v>
       </c>
       <c r="W14" t="n">
-        <v>-19.883</v>
+        <v>-19.799</v>
       </c>
     </row>
     <row r="16">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +14.81% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.23317023879997</v>
+        <v>-11.51313114891116</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1917,13 +1917,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>79.187</v>
+        <v>78.622</v>
       </c>
       <c r="V18" t="n">
-        <v>20.597</v>
+        <v>20.216</v>
       </c>
       <c r="W18" t="n">
-        <v>-38.497</v>
+        <v>-39.063</v>
       </c>
     </row>
     <row r="19">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, KCHOL.IS, PETKM.IS</t>
+          <t>ENERY.IS, KCHOL.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-11 | KCHOL.IS: 2026-09-10 | PETKM.IS: 2026-09-11</t>
+          <t>ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10 | PETKM.IS: 2026-09-14</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -3.77% / +0.00% / -3.75% | KCHOL.IS: +0.38% / +1.47% / -0.53% | PETKM.IS: -3.10% / +1.94% / -3.32%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +0.51% / +1.47% / -0.53% | PETKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.03206209363676</v>
+        <v>-12.36822629324095</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2137,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>191.8</v>
+        <v>192.8</v>
       </c>
       <c r="O21" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>54.173</v>
+        <v>53.584</v>
       </c>
       <c r="V21" t="n">
-        <v>16.795</v>
+        <v>16.348</v>
       </c>
       <c r="W21" t="n">
-        <v>-23.879</v>
+        <v>-24.468</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
+          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.577625008043729</v>
+        <v>-4.934633682820555</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2249,13 +2249,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>81.652</v>
+        <v>80.97199999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>30.572</v>
+        <v>30.083</v>
       </c>
       <c r="W22" t="n">
-        <v>-37.358</v>
+        <v>-38.037</v>
       </c>
     </row>
     <row r="23">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>10.82326005816285</v>
+        <v>10.87182432070222</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2338,13 +2338,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>91.367</v>
+        <v>91.45099999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>104.2</v>
+        <v>104.29</v>
       </c>
       <c r="W23" t="n">
-        <v>-19.883</v>
+        <v>-19.799</v>
       </c>
     </row>
     <row r="24">
@@ -2388,14 +2388,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.81% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>10.82326005816285</v>
+        <v>10.87182432070222</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2427,13 +2427,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>91.367</v>
+        <v>91.45099999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>104.2</v>
+        <v>104.29</v>
       </c>
       <c r="W24" t="n">
-        <v>-19.883</v>
+        <v>-19.799</v>
       </c>
     </row>
     <row r="25">
@@ -2638,7 +2638,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.448063190891519</v>
+        <v>-7.589190302070103</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2664,19 +2664,19 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>10.619</v>
+        <v>10.755</v>
       </c>
       <c r="T27" t="n">
-        <v>10.619</v>
+        <v>10.755</v>
       </c>
       <c r="U27" t="n">
-        <v>12.073</v>
+        <v>11.903</v>
       </c>
       <c r="V27" t="n">
-        <v>4.206</v>
+        <v>4.047</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.315</v>
+        <v>-13.485</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>6.417902914621387</v>
+        <v>6.137524147620987</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>294.815</v>
+        <v>293.774</v>
       </c>
       <c r="V3" t="n">
-        <v>114.376</v>
+        <v>113.811</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.593</v>
+        <v>-18.633</v>
       </c>
     </row>
     <row r="4">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>6.396599061847152</v>
+        <v>6.116276424011224</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>291.782</v>
+        <v>290.75</v>
       </c>
       <c r="V5" t="n">
-        <v>95.224</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-17.411</v>
+        <v>-18.443</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | CANTE.IS: +6.53% / +15.33% / -2.99% | ENERY.IS: +14.24% / +14.65% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | CANTE.IS: +5.73% / +15.33% / -2.99% | ENERY.IS: +14.43% / +14.66% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.936175822329239</v>
+        <v>-7.841835324120328</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3189,13 +3189,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>25.27</v>
+        <v>25.399</v>
       </c>
       <c r="V6" t="n">
-        <v>14.46</v>
+        <v>14.577</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.854</v>
+        <v>-39.726</v>
       </c>
     </row>
     <row r="7">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.23% / +3.54% / -3.83% | ENERY.IS: +14.24% / +14.65% / -0.50% | ISCTR.IS: +0.36% / +1.96% / -0.66%</t>
+          <t>CANTE.IS: -1.96% / +3.54% / -3.83% | ENERY.IS: +14.43% / +14.66% / -0.50% | ISCTR.IS: +0.43% / +1.97% / -0.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7414445465500297</v>
+        <v>0.6272257890539423</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>30.037</v>
+        <v>29.89</v>
       </c>
       <c r="V8" t="n">
-        <v>5.587</v>
+        <v>5.467</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.785</v>
+        <v>-27.932</v>
       </c>
     </row>
     <row r="9">
@@ -3493,7 +3493,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.071095994391637</v>
+        <v>-3.071157877503605</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.069960920368358</v>
+        <v>8.494416033952334</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>40.524</v>
+        <v>41.076</v>
       </c>
       <c r="V12" t="n">
-        <v>50.585</v>
+        <v>51.177</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.764</v>
+        <v>-19.212</v>
       </c>
     </row>
     <row r="13">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>6.417902914621387</v>
+        <v>6.137524147620987</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3786,13 +3786,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>294.815</v>
+        <v>293.774</v>
       </c>
       <c r="V13" t="n">
-        <v>114.376</v>
+        <v>113.811</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.593</v>
+        <v>-18.633</v>
       </c>
     </row>
     <row r="14">
@@ -3834,14 +3834,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>6.396599061847152</v>
+        <v>6.116276424011224</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3873,13 +3873,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>291.782</v>
+        <v>290.75</v>
       </c>
       <c r="V14" t="n">
-        <v>95.224</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.411</v>
+        <v>-18.443</v>
       </c>
     </row>
     <row r="16">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>6.417902914621387</v>
+        <v>6.137524147620987</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4086,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>294.815</v>
+        <v>293.774</v>
       </c>
       <c r="V18" t="n">
-        <v>114.376</v>
+        <v>113.811</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.593</v>
+        <v>-18.633</v>
       </c>
     </row>
     <row r="19">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.67% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>6.396599061847152</v>
+        <v>6.116276424011224</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4264,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>291.782</v>
+        <v>290.75</v>
       </c>
       <c r="V20" t="n">
-        <v>95.224</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-17.411</v>
+        <v>-18.443</v>
       </c>
     </row>
     <row r="21">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | CANTE.IS: +6.53% / +15.33% / -2.99% | ENERY.IS: +14.24% / +14.65% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | CANTE.IS: +5.73% / +15.33% / -2.99% | ENERY.IS: +14.43% / +14.66% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.936175822329239</v>
+        <v>-7.841835324120328</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4442,13 +4442,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>25.27</v>
+        <v>25.399</v>
       </c>
       <c r="V22" t="n">
-        <v>14.46</v>
+        <v>14.577</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.854</v>
+        <v>-39.726</v>
       </c>
     </row>
     <row r="23">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.23% / +3.54% / -3.83% | ENERY.IS: +14.24% / +14.65% / -0.50% | ISCTR.IS: +0.36% / +1.96% / -0.66%</t>
+          <t>CANTE.IS: -1.96% / +3.54% / -3.83% | ENERY.IS: +14.43% / +14.66% / -0.50% | ISCTR.IS: +0.43% / +1.97% / -0.66%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7414445465500297</v>
+        <v>0.6272257890539423</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4531,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>30.037</v>
+        <v>29.89</v>
       </c>
       <c r="V23" t="n">
-        <v>5.587</v>
+        <v>5.467</v>
       </c>
       <c r="W23" t="n">
-        <v>-27.785</v>
+        <v>-27.932</v>
       </c>
     </row>
     <row r="24">
@@ -4588,7 +4588,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.071095994391637</v>
+        <v>-3.071157877503605</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4747,14 +4747,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.62% / +20.01% / -1.13% | TKFEN.IS: +13.40% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>8.069960920368358</v>
+        <v>8.494416033952334</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4786,13 +4786,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>40.524</v>
+        <v>41.076</v>
       </c>
       <c r="V26" t="n">
-        <v>50.585</v>
+        <v>51.177</v>
       </c>
       <c r="W26" t="n">
-        <v>-19.764</v>
+        <v>-19.212</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.51313114891116</v>
+        <v>-10.74481637270631</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>101.8</v>
+        <v>101.6</v>
       </c>
       <c r="O3" t="n">
         <v>43.3</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>78.622</v>
+        <v>75.501</v>
       </c>
       <c r="V3" t="n">
-        <v>20.216</v>
+        <v>21.26</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.063</v>
+        <v>-36.539</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.51313114891116</v>
+        <v>-10.74481637270631</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,7 +1009,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>101.8</v>
+        <v>101.6</v>
       </c>
       <c r="O6" t="n">
         <v>43.3</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>78.622</v>
+        <v>75.501</v>
       </c>
       <c r="V6" t="n">
-        <v>20.216</v>
+        <v>21.26</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.063</v>
+        <v>-36.539</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -1.70% / +0.89% / -1.73%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.934633682820555</v>
+        <v>-5.202295134448609</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,7 +1096,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.6</v>
+        <v>134.3</v>
       </c>
       <c r="O7" t="n">
         <v>46.9</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>80.97199999999999</v>
+        <v>73.32899999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>30.083</v>
+        <v>29.717</v>
       </c>
       <c r="W7" t="n">
-        <v>-38.037</v>
+        <v>-37.023</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +0.51% / +1.47% / -0.53% | PETKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +0.95% / +2.98% / -0.08% | KCHOL.IS: -0.51% / +1.47% / -0.62% | PETKM.IS: -0.36% / +0.76% / -1.78%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-12.36822629324095</v>
+        <v>-12.48391680803764</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,7 +1183,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.8</v>
+        <v>192.4</v>
       </c>
       <c r="O8" t="n">
         <v>47</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>53.584</v>
+        <v>53.381</v>
       </c>
       <c r="V8" t="n">
-        <v>16.348</v>
+        <v>16.195</v>
       </c>
       <c r="W8" t="n">
-        <v>-24.468</v>
+        <v>-24.671</v>
       </c>
     </row>
     <row r="9">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.51313114891116</v>
+        <v>-10.74481637270631</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,7 +1270,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>101.8</v>
+        <v>101.6</v>
       </c>
       <c r="O9" t="n">
         <v>43.3</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>78.622</v>
+        <v>75.501</v>
       </c>
       <c r="V9" t="n">
-        <v>20.216</v>
+        <v>21.26</v>
       </c>
       <c r="W9" t="n">
-        <v>-39.063</v>
+        <v>-36.539</v>
       </c>
     </row>
     <row r="10">
@@ -1318,37 +1318,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TOASO.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>23.02092795860866</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>TOASO.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.589190302070103</v>
+        <v>-7.296631823399213</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,36 +1345,36 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>177.6</v>
+        <v>177.3</v>
       </c>
       <c r="O10" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>10.755</v>
+        <v>10.751</v>
       </c>
       <c r="T10" t="n">
-        <v>10.755</v>
+        <v>10.751</v>
       </c>
       <c r="U10" t="n">
-        <v>11.903</v>
+        <v>12.257</v>
       </c>
       <c r="V10" t="n">
-        <v>4.047</v>
+        <v>4.376</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.485</v>
+        <v>-13.131</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1393,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1420,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>66.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1480,12 +1468,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1507,7 +1495,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="O12" t="n">
         <v>47.7</v>
@@ -1555,12 +1543,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1578,14 +1566,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>10.87182432070222</v>
+        <v>9.747373013040296</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1594,7 +1582,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="O13" t="n">
         <v>44.7</v>
@@ -1617,13 +1605,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>91.45099999999999</v>
+        <v>89.509</v>
       </c>
       <c r="V13" t="n">
-        <v>104.29</v>
+        <v>102.218</v>
       </c>
       <c r="W13" t="n">
-        <v>-19.799</v>
+        <v>-21.741</v>
       </c>
     </row>
     <row r="14">
@@ -1642,12 +1630,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1665,14 +1653,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>10.87182432070222</v>
+        <v>9.747373013040296</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1681,7 +1669,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="O14" t="n">
         <v>44.7</v>
@@ -1704,13 +1692,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>91.45099999999999</v>
+        <v>89.509</v>
       </c>
       <c r="V14" t="n">
-        <v>104.29</v>
+        <v>102.218</v>
       </c>
       <c r="W14" t="n">
-        <v>-19.799</v>
+        <v>-21.741</v>
       </c>
     </row>
     <row r="16">
@@ -1855,12 +1843,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1878,14 +1866,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | ENERY.IS: +14.90% / +15.11% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.51313114891116</v>
+        <v>-10.74481637270631</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,7 +1882,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>101.8</v>
+        <v>101.6</v>
       </c>
       <c r="O18" t="n">
         <v>43.3</v>
@@ -1917,13 +1905,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>78.622</v>
+        <v>75.501</v>
       </c>
       <c r="V18" t="n">
-        <v>20.216</v>
+        <v>21.26</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.063</v>
+        <v>-36.539</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1932,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1971,7 +1959,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -2021,12 +2009,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2048,7 +2036,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2098,12 +2086,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2121,14 +2109,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +0.51% / +1.47% / -0.53% | PETKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +0.95% / +2.98% / -0.08% | KCHOL.IS: -0.51% / +1.47% / -0.62% | PETKM.IS: -0.36% / +0.76% / -1.78%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.36822629324095</v>
+        <v>-12.48391680803764</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,7 +2125,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.8</v>
+        <v>192.4</v>
       </c>
       <c r="O21" t="n">
         <v>47</v>
@@ -2160,13 +2148,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>53.584</v>
+        <v>53.381</v>
       </c>
       <c r="V21" t="n">
-        <v>16.348</v>
+        <v>16.195</v>
       </c>
       <c r="W21" t="n">
-        <v>-24.468</v>
+        <v>-24.671</v>
       </c>
     </row>
     <row r="22">
@@ -2187,12 +2175,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2210,14 +2198,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +4.51% / -3.01% | SAHOL.IS: -0.39% / +0.89% / -1.15%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -1.70% / +0.89% / -1.73%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.934633682820555</v>
+        <v>-5.202295134448609</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,7 +2214,7 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.6</v>
+        <v>134.3</v>
       </c>
       <c r="O22" t="n">
         <v>46.9</v>
@@ -2249,13 +2237,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>80.97199999999999</v>
+        <v>73.32899999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>30.083</v>
+        <v>29.717</v>
       </c>
       <c r="W22" t="n">
-        <v>-38.037</v>
+        <v>-37.023</v>
       </c>
     </row>
     <row r="23">
@@ -2276,12 +2264,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2299,14 +2287,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>10.87182432070222</v>
+        <v>9.747373013040296</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2315,7 +2303,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="O23" t="n">
         <v>44.7</v>
@@ -2338,13 +2326,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>91.45099999999999</v>
+        <v>89.509</v>
       </c>
       <c r="V23" t="n">
-        <v>104.29</v>
+        <v>102.218</v>
       </c>
       <c r="W23" t="n">
-        <v>-19.799</v>
+        <v>-21.741</v>
       </c>
     </row>
     <row r="24">
@@ -2365,12 +2353,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2388,14 +2376,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.90% / +15.11% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>10.87182432070222</v>
+        <v>9.747373013040296</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2404,7 +2392,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="O24" t="n">
         <v>44.7</v>
@@ -2427,13 +2415,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>91.45099999999999</v>
+        <v>89.509</v>
       </c>
       <c r="V24" t="n">
-        <v>104.29</v>
+        <v>102.218</v>
       </c>
       <c r="W24" t="n">
-        <v>-19.799</v>
+        <v>-21.741</v>
       </c>
     </row>
     <row r="25">
@@ -2454,12 +2442,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2481,7 +2469,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>66.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2531,12 +2519,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2558,7 +2546,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N26" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="O26" t="n">
         <v>47.7</v>
@@ -2608,37 +2596,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>TOASO.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>23.02092795860866</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>TOASO.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.589190302070103</v>
+        <v>-7.296631823399213</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2647,36 +2623,36 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N27" t="n">
-        <v>177.6</v>
+        <v>177.3</v>
       </c>
       <c r="O27" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>10.755</v>
+        <v>10.751</v>
       </c>
       <c r="T27" t="n">
-        <v>10.755</v>
+        <v>10.751</v>
       </c>
       <c r="U27" t="n">
-        <v>11.903</v>
+        <v>12.257</v>
       </c>
       <c r="V27" t="n">
-        <v>4.047</v>
+        <v>4.376</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.485</v>
+        <v>-13.131</v>
       </c>
     </row>
   </sheetData>
@@ -2866,22 +2842,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ENERY.IS, TOASO.IS</t>
+          <t>ENERY.IS, KUYAS.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2889,14 +2865,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>6.137524147620987</v>
+        <v>7.22960503785941</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,10 +2881,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.8</v>
+        <v>93.2</v>
       </c>
       <c r="O3" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2928,13 +2904,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>293.774</v>
+        <v>271.457</v>
       </c>
       <c r="V3" t="n">
-        <v>113.811</v>
+        <v>116.011</v>
       </c>
       <c r="W3" t="n">
-        <v>-18.633</v>
+        <v>-13.615</v>
       </c>
     </row>
     <row r="4">
@@ -2953,37 +2929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.28509221401519</v>
+        <v>-11.71888903249241</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,36 +2956,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>120.8</v>
+        <v>120.6</v>
       </c>
       <c r="O4" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>25.958</v>
+        <v>26.32</v>
       </c>
       <c r="T4" t="n">
-        <v>25.958</v>
+        <v>26.32</v>
       </c>
       <c r="U4" t="n">
-        <v>57.995</v>
+        <v>57.222</v>
       </c>
       <c r="V4" t="n">
-        <v>19.359</v>
+        <v>18.775</v>
       </c>
       <c r="W4" t="n">
-        <v>-55.391</v>
+        <v>-56.164</v>
       </c>
     </row>
     <row r="5">
@@ -3040,22 +3004,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENERY.IS, TOASO.IS</t>
+          <t>ENERY.IS, KUYAS.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3063,14 +3027,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>6.116276424011224</v>
+        <v>7.208138690034493</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3079,10 +3043,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3102,13 +3066,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>290.75</v>
+        <v>268.604</v>
       </c>
       <c r="V5" t="n">
-        <v>94.70999999999999</v>
+        <v>96.71299999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-18.443</v>
+        <v>-13.467</v>
       </c>
     </row>
     <row r="6">
@@ -3127,22 +3091,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, ENERY.IS, GUBRF.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, GUBRF.IS, ISCTR.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3150,14 +3114,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | CANTE.IS: +5.73% / +15.33% / -2.99% | ENERY.IS: +14.43% / +14.66% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: +6.49% / +15.33% / -2.99% | ENERY.IS: +15.31% / +17.84% / -0.50% | GUBRF.IS: -2.21% / +0.16% / -2.19% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.841835324120328</v>
+        <v>-7.703054731208104</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3166,10 +3130,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138.5</v>
+        <v>138.7</v>
       </c>
       <c r="O6" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3189,13 +3153,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>25.399</v>
+        <v>25.588</v>
       </c>
       <c r="V6" t="n">
-        <v>14.577</v>
+        <v>14.75</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.726</v>
+        <v>-39.537</v>
       </c>
     </row>
     <row r="7">
@@ -3214,37 +3178,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.28509221401519</v>
+        <v>-11.71888903249241</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,36 +3205,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>120.8</v>
+        <v>120.6</v>
       </c>
       <c r="O7" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>25.958</v>
+        <v>26.32</v>
       </c>
       <c r="T7" t="n">
-        <v>25.958</v>
+        <v>26.32</v>
       </c>
       <c r="U7" t="n">
-        <v>57.995</v>
+        <v>57.222</v>
       </c>
       <c r="V7" t="n">
-        <v>19.359</v>
+        <v>18.775</v>
       </c>
       <c r="W7" t="n">
-        <v>-55.391</v>
+        <v>-56.164</v>
       </c>
     </row>
     <row r="8">
@@ -3301,12 +3253,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3324,14 +3276,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.96% / +3.54% / -3.83% | ENERY.IS: +14.43% / +14.66% / -0.50% | ISCTR.IS: +0.43% / +1.97% / -0.66%</t>
+          <t>CANTE.IS: -1.26% / +3.54% / -3.83% | ENERY.IS: +15.31% / +17.84% / -0.50% | ISCTR.IS: -0.77% / +1.97% / -0.76%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6272257890539423</v>
+        <v>0.6712351228919111</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3340,10 +3292,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>152.8</v>
+        <v>152.5</v>
       </c>
       <c r="O8" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3363,13 +3315,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>29.89</v>
+        <v>29.191</v>
       </c>
       <c r="V8" t="n">
-        <v>5.467</v>
+        <v>5.514</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.932</v>
+        <v>-27.714</v>
       </c>
     </row>
     <row r="9">
@@ -3388,12 +3340,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3415,7 +3367,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>74.7</v>
+        <v>74.5</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3463,37 +3415,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS, ENJSA.IS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>38.04089454478734</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.071157877503605</v>
+        <v>-3.400945810124201</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3502,21 +3442,21 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114.5</v>
+        <v>114.2</v>
       </c>
       <c r="O10" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>20.181</v>
@@ -3525,13 +3465,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.636</v>
+        <v>10.259</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.491</v>
+        <v>-2.823</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.224</v>
+        <v>-27.6</v>
       </c>
     </row>
     <row r="11">
@@ -3550,37 +3490,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>63.58450648919234</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.20224596569523</v>
+        <v>-11.63644788450836</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,36 +3517,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>180.8</v>
+        <v>180.4</v>
       </c>
       <c r="O11" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>24.648</v>
+        <v>25.016</v>
       </c>
       <c r="T11" t="n">
-        <v>24.648</v>
+        <v>25.016</v>
       </c>
       <c r="U11" t="n">
-        <v>33.88</v>
+        <v>33.226</v>
       </c>
       <c r="V11" t="n">
-        <v>6.483</v>
+        <v>5.963</v>
       </c>
       <c r="W11" t="n">
-        <v>-43.792</v>
+        <v>-44.447</v>
       </c>
     </row>
     <row r="12">
@@ -3637,22 +3565,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -3660,14 +3588,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.494416033952334</v>
+        <v>8.896719099171492</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3676,13 +3604,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
       <c r="O12" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="P12" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3699,13 +3627,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>41.076</v>
+        <v>41.599</v>
       </c>
       <c r="V12" t="n">
-        <v>51.177</v>
+        <v>51.737</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.212</v>
+        <v>-18.689</v>
       </c>
     </row>
     <row r="13">
@@ -3724,22 +3652,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENERY.IS, TOASO.IS</t>
+          <t>ENERY.IS, KUYAS.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3747,14 +3675,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>6.137524147620987</v>
+        <v>7.22960503785941</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3763,10 +3691,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>92.8</v>
+        <v>93.2</v>
       </c>
       <c r="O13" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
       <c r="P13" t="n">
         <v>4.3</v>
@@ -3786,13 +3714,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>293.774</v>
+        <v>271.457</v>
       </c>
       <c r="V13" t="n">
-        <v>113.811</v>
+        <v>116.011</v>
       </c>
       <c r="W13" t="n">
-        <v>-18.633</v>
+        <v>-13.615</v>
       </c>
     </row>
     <row r="14">
@@ -3811,22 +3739,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ENERY.IS, TOASO.IS</t>
+          <t>ENERY.IS, KUYAS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3834,14 +3762,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>6.116276424011224</v>
+        <v>7.208138690034493</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3850,10 +3778,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>82</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="P14" t="n">
         <v>4.7</v>
@@ -3873,13 +3801,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>290.75</v>
+        <v>268.604</v>
       </c>
       <c r="V14" t="n">
-        <v>94.70999999999999</v>
+        <v>96.71299999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-18.443</v>
+        <v>-13.467</v>
       </c>
     </row>
     <row r="16">
@@ -4024,22 +3952,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENERY.IS, TOASO.IS</t>
+          <t>ENERY.IS, KUYAS.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4047,14 +3975,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>6.137524147620987</v>
+        <v>7.22960503785941</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4063,10 +3991,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.8</v>
+        <v>93.2</v>
       </c>
       <c r="O18" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4086,13 +4014,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>293.774</v>
+        <v>271.457</v>
       </c>
       <c r="V18" t="n">
-        <v>113.811</v>
+        <v>116.011</v>
       </c>
       <c r="W18" t="n">
-        <v>-18.633</v>
+        <v>-13.615</v>
       </c>
     </row>
     <row r="19">
@@ -4113,37 +4041,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.28509221401519</v>
+        <v>-11.71888903249241</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4152,36 +4068,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>120.8</v>
+        <v>120.6</v>
       </c>
       <c r="O19" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>25.958</v>
+        <v>26.32</v>
       </c>
       <c r="T19" t="n">
-        <v>25.958</v>
+        <v>26.32</v>
       </c>
       <c r="U19" t="n">
-        <v>57.995</v>
+        <v>57.222</v>
       </c>
       <c r="V19" t="n">
-        <v>19.359</v>
+        <v>18.775</v>
       </c>
       <c r="W19" t="n">
-        <v>-55.391</v>
+        <v>-56.164</v>
       </c>
     </row>
     <row r="20">
@@ -4202,22 +4118,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENERY.IS, TOASO.IS</t>
+          <t>ENERY.IS, KUYAS.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | TOASO.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4225,14 +4141,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +11.86% / +12.04% / -3.45% | TOASO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>6.116276424011224</v>
+        <v>7.208138690034493</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4241,10 +4157,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4264,13 +4180,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>290.75</v>
+        <v>268.604</v>
       </c>
       <c r="V20" t="n">
-        <v>94.70999999999999</v>
+        <v>96.71299999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-18.443</v>
+        <v>-13.467</v>
       </c>
     </row>
     <row r="21">
@@ -4291,37 +4207,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS, ENJSA.IS, SOKM.IS, TRENJ.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14 | SOKM.IS: 2026-09-14 | TRENJ.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>63.58450648919234</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.20224596569523</v>
+        <v>-11.63644788450836</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4330,36 +4234,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>180.8</v>
+        <v>180.4</v>
       </c>
       <c r="O21" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>24.648</v>
+        <v>25.016</v>
       </c>
       <c r="T21" t="n">
-        <v>24.648</v>
+        <v>25.016</v>
       </c>
       <c r="U21" t="n">
-        <v>33.88</v>
+        <v>33.226</v>
       </c>
       <c r="V21" t="n">
-        <v>6.483</v>
+        <v>5.963</v>
       </c>
       <c r="W21" t="n">
-        <v>-43.792</v>
+        <v>-44.447</v>
       </c>
     </row>
     <row r="22">
@@ -4380,22 +4284,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, ENERY.IS, GUBRF.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, GUBRF.IS, ISCTR.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4403,14 +4307,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | CANTE.IS: +5.73% / +15.33% / -2.99% | ENERY.IS: +14.43% / +14.66% / -0.50% | GUBRF.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: +6.49% / +15.33% / -2.99% | ENERY.IS: +15.31% / +17.84% / -0.50% | GUBRF.IS: -2.21% / +0.16% / -2.19% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.841835324120328</v>
+        <v>-7.703054731208104</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4419,10 +4323,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138.5</v>
+        <v>138.7</v>
       </c>
       <c r="O22" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4442,13 +4346,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>25.399</v>
+        <v>25.588</v>
       </c>
       <c r="V22" t="n">
-        <v>14.577</v>
+        <v>14.75</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.726</v>
+        <v>-39.537</v>
       </c>
     </row>
     <row r="23">
@@ -4469,12 +4373,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4492,14 +4396,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.96% / +3.54% / -3.83% | ENERY.IS: +14.43% / +14.66% / -0.50% | ISCTR.IS: +0.43% / +1.97% / -0.66%</t>
+          <t>CANTE.IS: -1.26% / +3.54% / -3.83% | ENERY.IS: +15.31% / +17.84% / -0.50% | ISCTR.IS: -0.77% / +1.97% / -0.76%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6272257890539423</v>
+        <v>0.6712351228919111</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4508,10 +4412,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>152.8</v>
+        <v>152.5</v>
       </c>
       <c r="O23" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4531,13 +4435,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>29.89</v>
+        <v>29.191</v>
       </c>
       <c r="V23" t="n">
-        <v>5.467</v>
+        <v>5.514</v>
       </c>
       <c r="W23" t="n">
-        <v>-27.932</v>
+        <v>-27.714</v>
       </c>
     </row>
     <row r="24">
@@ -4558,37 +4462,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS, ENJSA.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-09-14 | ENERY.IS: 2026-09-14 | ENJSA.IS: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>38.04089454478734</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.071157877503605</v>
+        <v>-3.400945810124201</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4597,21 +4489,21 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114.5</v>
+        <v>114.2</v>
       </c>
       <c r="O24" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>20.181</v>
@@ -4620,13 +4512,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.636</v>
+        <v>10.259</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.491</v>
+        <v>-2.823</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.224</v>
+        <v>-27.6</v>
       </c>
     </row>
     <row r="25">
@@ -4647,12 +4539,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4674,7 +4566,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>74.7</v>
+        <v>74.5</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4724,22 +4616,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4747,14 +4639,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.54% / +20.01% / -1.13% | TKFEN.IS: +14.31% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>8.494416033952334</v>
+        <v>8.896719099171492</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4763,13 +4655,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
       <c r="O26" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="P26" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4786,13 +4678,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>41.076</v>
+        <v>41.599</v>
       </c>
       <c r="V26" t="n">
-        <v>51.177</v>
+        <v>51.737</v>
       </c>
       <c r="W26" t="n">
-        <v>-19.212</v>
+        <v>-18.689</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.74481637270631</v>
+        <v>-11.77252799348939</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>75.501</v>
+        <v>73.48</v>
       </c>
       <c r="V3" t="n">
-        <v>21.26</v>
+        <v>19.864</v>
       </c>
       <c r="W3" t="n">
-        <v>-36.539</v>
+        <v>-38.56</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.74481637270631</v>
+        <v>-11.77252799348939</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>75.501</v>
+        <v>73.48</v>
       </c>
       <c r="V6" t="n">
-        <v>21.26</v>
+        <v>19.864</v>
       </c>
       <c r="W6" t="n">
-        <v>-36.539</v>
+        <v>-38.56</v>
       </c>
     </row>
     <row r="7">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CANTE.IS, SAHOL.IS</t>
+          <t>CANTE.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | SAHOL.IS: 2026-09-11</t>
+          <t>CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -1.70% / +0.89% / -1.73%</t>
+          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.202295134448609</v>
+        <v>-7.397220774440417</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.3</v>
+        <v>134.8</v>
       </c>
       <c r="O7" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="P7" t="n">
         <v>3.1</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>73.32899999999999</v>
+        <v>69.316</v>
       </c>
       <c r="V7" t="n">
-        <v>29.717</v>
+        <v>26.714</v>
       </c>
       <c r="W7" t="n">
-        <v>-37.023</v>
+        <v>-41.036</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +0.95% / +2.98% / -0.08% | KCHOL.IS: -0.51% / +1.47% / -0.62% | PETKM.IS: -0.36% / +0.76% / -1.78%</t>
+          <t>ENERY.IS: +0.79% / +2.98% / -0.24% | KCHOL.IS: -2.43% / +1.47% / -2.81% | PETKM.IS: -3.15% / +0.76% / -3.30%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-12.48391680803764</v>
+        <v>-13.90072974058688</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>53.381</v>
+        <v>50.898</v>
       </c>
       <c r="V8" t="n">
-        <v>16.195</v>
+        <v>14.314</v>
       </c>
       <c r="W8" t="n">
-        <v>-24.671</v>
+        <v>-27.154</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.74481637270631</v>
+        <v>-11.77252799348939</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>75.501</v>
+        <v>73.48</v>
       </c>
       <c r="V9" t="n">
-        <v>21.26</v>
+        <v>19.864</v>
       </c>
       <c r="W9" t="n">
-        <v>-36.539</v>
+        <v>-38.56</v>
       </c>
     </row>
     <row r="10">
@@ -1336,7 +1336,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.296631823399213</v>
+        <v>-7.426657813919613</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1368,13 +1368,13 @@
         <v>10.751</v>
       </c>
       <c r="U10" t="n">
-        <v>12.257</v>
+        <v>12.099</v>
       </c>
       <c r="V10" t="n">
-        <v>4.376</v>
+        <v>4.23</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.131</v>
+        <v>-13.289</v>
       </c>
     </row>
     <row r="11">
@@ -1566,14 +1566,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>9.747373013040296</v>
+        <v>10.0335006811529</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1605,13 +1605,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>89.509</v>
+        <v>90.003</v>
       </c>
       <c r="V13" t="n">
-        <v>102.218</v>
+        <v>102.745</v>
       </c>
       <c r="W13" t="n">
-        <v>-21.741</v>
+        <v>-21.247</v>
       </c>
     </row>
     <row r="14">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>9.747373013040296</v>
+        <v>10.0335006811529</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1692,13 +1692,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>89.509</v>
+        <v>90.003</v>
       </c>
       <c r="V14" t="n">
-        <v>102.218</v>
+        <v>102.745</v>
       </c>
       <c r="W14" t="n">
-        <v>-21.741</v>
+        <v>-21.247</v>
       </c>
     </row>
     <row r="16">
@@ -1866,14 +1866,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +16.01% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.74481637270631</v>
+        <v>-11.77252799348939</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1905,13 +1905,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>75.501</v>
+        <v>73.48</v>
       </c>
       <c r="V18" t="n">
-        <v>21.26</v>
+        <v>19.864</v>
       </c>
       <c r="W18" t="n">
-        <v>-36.539</v>
+        <v>-38.56</v>
       </c>
     </row>
     <row r="19">
@@ -2109,14 +2109,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ENERY.IS: +0.95% / +2.98% / -0.08% | KCHOL.IS: -0.51% / +1.47% / -0.62% | PETKM.IS: -0.36% / +0.76% / -1.78%</t>
+          <t>ENERY.IS: +0.79% / +2.98% / -0.24% | KCHOL.IS: -2.43% / +1.47% / -2.81% | PETKM.IS: -3.15% / +0.76% / -3.30%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.48391680803764</v>
+        <v>-13.90072974058688</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2148,13 +2148,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>53.381</v>
+        <v>50.898</v>
       </c>
       <c r="V21" t="n">
-        <v>16.195</v>
+        <v>14.314</v>
       </c>
       <c r="W21" t="n">
-        <v>-24.671</v>
+        <v>-27.154</v>
       </c>
     </row>
     <row r="22">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANTE.IS, SAHOL.IS</t>
+          <t>CANTE.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | SAHOL.IS: 2026-09-11</t>
+          <t>CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2198,14 +2198,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | SAHOL.IS: -1.70% / +0.89% / -1.73%</t>
+          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.202295134448609</v>
+        <v>-7.397220774440417</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2214,10 +2214,10 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.3</v>
+        <v>134.8</v>
       </c>
       <c r="O22" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="P22" t="n">
         <v>3.1</v>
@@ -2237,13 +2237,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>73.32899999999999</v>
+        <v>69.316</v>
       </c>
       <c r="V22" t="n">
-        <v>29.717</v>
+        <v>26.714</v>
       </c>
       <c r="W22" t="n">
-        <v>-37.023</v>
+        <v>-41.036</v>
       </c>
     </row>
     <row r="23">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>9.747373013040296</v>
+        <v>10.0335006811529</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2326,13 +2326,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>89.509</v>
+        <v>90.003</v>
       </c>
       <c r="V23" t="n">
-        <v>102.218</v>
+        <v>102.745</v>
       </c>
       <c r="W23" t="n">
-        <v>-21.741</v>
+        <v>-21.247</v>
       </c>
     </row>
     <row r="24">
@@ -2376,14 +2376,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +16.01% / +18.35% / -0.46% | KUYAS.IS: -3.39% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>9.747373013040296</v>
+        <v>10.0335006811529</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2415,13 +2415,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>89.509</v>
+        <v>90.003</v>
       </c>
       <c r="V24" t="n">
-        <v>102.218</v>
+        <v>102.745</v>
       </c>
       <c r="W24" t="n">
-        <v>-21.741</v>
+        <v>-21.247</v>
       </c>
     </row>
     <row r="25">
@@ -2614,7 +2614,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.296631823399213</v>
+        <v>-7.426657813919613</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2646,13 +2646,13 @@
         <v>10.751</v>
       </c>
       <c r="U27" t="n">
-        <v>12.257</v>
+        <v>12.099</v>
       </c>
       <c r="V27" t="n">
-        <v>4.376</v>
+        <v>4.23</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.131</v>
+        <v>-13.289</v>
       </c>
     </row>
   </sheetData>
@@ -2687,7 +2687,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2865,14 +2865,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>7.22960503785941</v>
+        <v>6.965980265787119</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2904,13 +2904,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>271.457</v>
+        <v>270.544</v>
       </c>
       <c r="V3" t="n">
-        <v>116.011</v>
+        <v>115.48</v>
       </c>
       <c r="W3" t="n">
-        <v>-13.615</v>
+        <v>-14.529</v>
       </c>
     </row>
     <row r="4">
@@ -2947,7 +2947,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.71888903249241</v>
+        <v>-12.78783400662118</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2973,19 +2973,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>26.32</v>
+        <v>27.212</v>
       </c>
       <c r="T4" t="n">
-        <v>26.32</v>
+        <v>27.212</v>
       </c>
       <c r="U4" t="n">
-        <v>57.222</v>
+        <v>55.319</v>
       </c>
       <c r="V4" t="n">
-        <v>18.775</v>
+        <v>17.337</v>
       </c>
       <c r="W4" t="n">
-        <v>-56.164</v>
+        <v>-58.067</v>
       </c>
     </row>
     <row r="5">
@@ -3027,14 +3027,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>7.208138690034493</v>
+        <v>6.944566693136123</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3066,13 +3066,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>268.604</v>
+        <v>267.698</v>
       </c>
       <c r="V5" t="n">
-        <v>96.71299999999999</v>
+        <v>96.23</v>
       </c>
       <c r="W5" t="n">
-        <v>-13.467</v>
+        <v>-14.373</v>
       </c>
     </row>
     <row r="6">
@@ -3114,14 +3114,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +6.49% / +15.33% / -2.99% | ENERY.IS: +15.31% / +17.84% / -0.50% | GUBRF.IS: -2.21% / +0.16% / -2.19% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: +4.08% / +15.33% / -2.99% | ENERY.IS: +15.40% / +17.84% / -0.50% | GUBRF.IS: -1.75% / +0.14% / -2.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.703054731208104</v>
+        <v>-7.474712421640628</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3153,13 +3153,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>25.588</v>
+        <v>25.898</v>
       </c>
       <c r="V6" t="n">
-        <v>14.75</v>
+        <v>15.034</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.537</v>
+        <v>-39.226</v>
       </c>
     </row>
     <row r="7">
@@ -3196,7 +3196,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.71888903249241</v>
+        <v>-12.78783400662118</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3222,19 +3222,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>26.32</v>
+        <v>27.212</v>
       </c>
       <c r="T7" t="n">
-        <v>26.32</v>
+        <v>27.212</v>
       </c>
       <c r="U7" t="n">
-        <v>57.222</v>
+        <v>55.319</v>
       </c>
       <c r="V7" t="n">
-        <v>18.775</v>
+        <v>17.337</v>
       </c>
       <c r="W7" t="n">
-        <v>-56.164</v>
+        <v>-58.067</v>
       </c>
     </row>
     <row r="8">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, ISCTR.IS</t>
+          <t>ENERY.IS, ISCTR.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10</t>
+          <t>ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10 | SASA.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3276,14 +3276,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.26% / +3.54% / -3.83% | ENERY.IS: +15.31% / +17.84% / -0.50% | ISCTR.IS: -0.77% / +1.97% / -0.76%</t>
+          <t>ENERY.IS: +15.40% / +17.84% / -0.50% | ISCTR.IS: -2.29% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6712351228919111</v>
+        <v>-0.4763882887171778</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3292,10 +3292,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>152.5</v>
+        <v>153</v>
       </c>
       <c r="O8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3315,13 +3315,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>29.191</v>
+        <v>27.718</v>
       </c>
       <c r="V8" t="n">
-        <v>5.514</v>
+        <v>4.311</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.714</v>
+        <v>-29.186</v>
       </c>
     </row>
     <row r="9">
@@ -3433,7 +3433,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.400945810124201</v>
+        <v>-4.563388469867014</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3459,19 +3459,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20.181</v>
+        <v>20.983</v>
       </c>
       <c r="T10" t="n">
-        <v>20.181</v>
+        <v>20.983</v>
       </c>
       <c r="U10" t="n">
-        <v>10.259</v>
+        <v>8.932</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.823</v>
+        <v>-3.992</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.6</v>
+        <v>-28.927</v>
       </c>
     </row>
     <row r="11">
@@ -3508,7 +3508,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.63644788450836</v>
+        <v>-12.70639109087314</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3534,19 +3534,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>25.016</v>
+        <v>25.924</v>
       </c>
       <c r="T11" t="n">
-        <v>25.016</v>
+        <v>25.924</v>
       </c>
       <c r="U11" t="n">
-        <v>33.226</v>
+        <v>31.612</v>
       </c>
       <c r="V11" t="n">
-        <v>5.963</v>
+        <v>4.68</v>
       </c>
       <c r="W11" t="n">
-        <v>-44.447</v>
+        <v>-46.06</v>
       </c>
     </row>
     <row r="12">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.896719099171492</v>
+        <v>10.5099231963651</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3627,13 +3627,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>41.599</v>
+        <v>43.697</v>
       </c>
       <c r="V12" t="n">
-        <v>51.737</v>
+        <v>53.985</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.689</v>
+        <v>-16.591</v>
       </c>
     </row>
     <row r="13">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>7.22960503785941</v>
+        <v>6.965980265787119</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3714,13 +3714,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>271.457</v>
+        <v>270.544</v>
       </c>
       <c r="V13" t="n">
-        <v>116.011</v>
+        <v>115.48</v>
       </c>
       <c r="W13" t="n">
-        <v>-13.615</v>
+        <v>-14.529</v>
       </c>
     </row>
     <row r="14">
@@ -3762,14 +3762,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>7.208138690034493</v>
+        <v>6.944566693136123</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3801,13 +3801,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>268.604</v>
+        <v>267.698</v>
       </c>
       <c r="V14" t="n">
-        <v>96.71299999999999</v>
+        <v>96.23</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.467</v>
+        <v>-14.373</v>
       </c>
     </row>
     <row r="16">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>7.22960503785941</v>
+        <v>6.965980265787119</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4014,13 +4014,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>271.457</v>
+        <v>270.544</v>
       </c>
       <c r="V18" t="n">
-        <v>116.011</v>
+        <v>115.48</v>
       </c>
       <c r="W18" t="n">
-        <v>-13.615</v>
+        <v>-14.529</v>
       </c>
     </row>
     <row r="19">
@@ -4059,7 +4059,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.71888903249241</v>
+        <v>-12.78783400662118</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4085,19 +4085,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>26.32</v>
+        <v>27.212</v>
       </c>
       <c r="T19" t="n">
-        <v>26.32</v>
+        <v>27.212</v>
       </c>
       <c r="U19" t="n">
-        <v>57.222</v>
+        <v>55.319</v>
       </c>
       <c r="V19" t="n">
-        <v>18.775</v>
+        <v>17.337</v>
       </c>
       <c r="W19" t="n">
-        <v>-56.164</v>
+        <v>-58.067</v>
       </c>
     </row>
     <row r="20">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.71% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>7.208138690034493</v>
+        <v>6.944566693136123</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4180,13 +4180,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>268.604</v>
+        <v>267.698</v>
       </c>
       <c r="V20" t="n">
-        <v>96.71299999999999</v>
+        <v>96.23</v>
       </c>
       <c r="W20" t="n">
-        <v>-13.467</v>
+        <v>-14.373</v>
       </c>
     </row>
     <row r="21">
@@ -4225,7 +4225,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.63644788450836</v>
+        <v>-12.70639109087314</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4251,19 +4251,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>25.016</v>
+        <v>25.924</v>
       </c>
       <c r="T21" t="n">
-        <v>25.016</v>
+        <v>25.924</v>
       </c>
       <c r="U21" t="n">
-        <v>33.226</v>
+        <v>31.612</v>
       </c>
       <c r="V21" t="n">
-        <v>5.963</v>
+        <v>4.68</v>
       </c>
       <c r="W21" t="n">
-        <v>-44.447</v>
+        <v>-46.06</v>
       </c>
     </row>
     <row r="22">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: +6.49% / +15.33% / -2.99% | ENERY.IS: +15.31% / +17.84% / -0.50% | GUBRF.IS: -2.21% / +0.16% / -2.19% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: +4.08% / +15.33% / -2.99% | ENERY.IS: +15.40% / +17.84% / -0.50% | GUBRF.IS: -1.75% / +0.14% / -2.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.703054731208104</v>
+        <v>-7.474712421640628</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4346,13 +4346,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>25.588</v>
+        <v>25.898</v>
       </c>
       <c r="V22" t="n">
-        <v>14.75</v>
+        <v>15.034</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.537</v>
+        <v>-39.226</v>
       </c>
     </row>
     <row r="23">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, ISCTR.IS</t>
+          <t>ENERY.IS, ISCTR.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10</t>
+          <t>ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10 | SASA.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.26% / +3.54% / -3.83% | ENERY.IS: +15.31% / +17.84% / -0.50% | ISCTR.IS: -0.77% / +1.97% / -0.76%</t>
+          <t>ENERY.IS: +15.40% / +17.84% / -0.50% | ISCTR.IS: -2.29% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6712351228919111</v>
+        <v>-0.4763882887171778</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4412,10 +4412,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>152.5</v>
+        <v>153</v>
       </c>
       <c r="O23" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4435,13 +4435,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>29.191</v>
+        <v>27.718</v>
       </c>
       <c r="V23" t="n">
-        <v>5.514</v>
+        <v>4.311</v>
       </c>
       <c r="W23" t="n">
-        <v>-27.714</v>
+        <v>-29.186</v>
       </c>
     </row>
     <row r="24">
@@ -4480,7 +4480,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.400945810124201</v>
+        <v>-4.563388469867014</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4506,19 +4506,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>20.181</v>
+        <v>20.983</v>
       </c>
       <c r="T24" t="n">
-        <v>20.181</v>
+        <v>20.983</v>
       </c>
       <c r="U24" t="n">
-        <v>10.259</v>
+        <v>8.932</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.823</v>
+        <v>-3.992</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.6</v>
+        <v>-28.927</v>
       </c>
     </row>
     <row r="25">
@@ -4639,14 +4639,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +19.91% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>8.896719099171492</v>
+        <v>10.5099231963651</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4678,13 +4678,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>41.599</v>
+        <v>43.697</v>
       </c>
       <c r="V26" t="n">
-        <v>51.737</v>
+        <v>53.985</v>
       </c>
       <c r="W26" t="n">
-        <v>-18.689</v>
+        <v>-16.591</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.77252799348939</v>
+        <v>-11.33874110560147</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>73.48</v>
+        <v>74.333</v>
       </c>
       <c r="V3" t="n">
-        <v>19.864</v>
+        <v>20.453</v>
       </c>
       <c r="W3" t="n">
-        <v>-38.56</v>
+        <v>-37.707</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.77252799348939</v>
+        <v>-11.33874110560147</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>73.48</v>
+        <v>74.333</v>
       </c>
       <c r="V6" t="n">
-        <v>19.864</v>
+        <v>20.453</v>
       </c>
       <c r="W6" t="n">
-        <v>-38.56</v>
+        <v>-37.707</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.397220774440417</v>
+        <v>-7.754200362813613</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>19.727</v>
+        <v>19.819</v>
       </c>
       <c r="T7" t="n">
-        <v>19.727</v>
+        <v>19.819</v>
       </c>
       <c r="U7" t="n">
-        <v>69.316</v>
+        <v>68.663</v>
       </c>
       <c r="V7" t="n">
-        <v>26.714</v>
+        <v>26.225</v>
       </c>
       <c r="W7" t="n">
-        <v>-41.036</v>
+        <v>-41.689</v>
       </c>
     </row>
     <row r="8">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENERY.IS, KCHOL.IS, PETKM.IS</t>
+          <t>DOHOL.IS, ENERY.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10 | PETKM.IS: 2026-09-14</t>
+          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +0.79% / +2.98% / -0.24% | KCHOL.IS: -2.43% / +1.47% / -2.81% | PETKM.IS: -3.15% / +0.76% / -3.30%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.38% / +1.47% / -2.81%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.90072974058688</v>
+        <v>-13.68024273423835</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.4</v>
+        <v>192.9</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>50.898</v>
+        <v>51.284</v>
       </c>
       <c r="V8" t="n">
-        <v>14.314</v>
+        <v>14.606</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.154</v>
+        <v>-26.768</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.77252799348939</v>
+        <v>-11.33874110560147</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>73.48</v>
+        <v>74.333</v>
       </c>
       <c r="V9" t="n">
-        <v>19.864</v>
+        <v>20.453</v>
       </c>
       <c r="W9" t="n">
-        <v>-38.56</v>
+        <v>-37.707</v>
       </c>
     </row>
     <row r="10">
@@ -1336,7 +1336,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.426657813919613</v>
+        <v>-7.55668380443999</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1368,13 +1368,13 @@
         <v>10.751</v>
       </c>
       <c r="U10" t="n">
-        <v>12.099</v>
+        <v>11.942</v>
       </c>
       <c r="V10" t="n">
-        <v>4.23</v>
+        <v>4.083</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.289</v>
+        <v>-13.446</v>
       </c>
     </row>
     <row r="11">
@@ -1566,14 +1566,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>10.0335006811529</v>
+        <v>10.8306138039028</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1605,13 +1605,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>90.003</v>
+        <v>91.38</v>
       </c>
       <c r="V13" t="n">
-        <v>102.745</v>
+        <v>104.214</v>
       </c>
       <c r="W13" t="n">
-        <v>-21.247</v>
+        <v>-19.87</v>
       </c>
     </row>
     <row r="14">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>10.0335006811529</v>
+        <v>10.8306138039028</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1692,13 +1692,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>90.003</v>
+        <v>91.38</v>
       </c>
       <c r="V14" t="n">
-        <v>102.745</v>
+        <v>104.214</v>
       </c>
       <c r="W14" t="n">
-        <v>-21.247</v>
+        <v>-19.87</v>
       </c>
     </row>
     <row r="16">
@@ -1866,14 +1866,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | ENERY.IS: +15.82% / +18.35% / -0.46%</t>
+          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.77252799348939</v>
+        <v>-11.33874110560147</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1905,13 +1905,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>73.48</v>
+        <v>74.333</v>
       </c>
       <c r="V18" t="n">
-        <v>19.864</v>
+        <v>20.453</v>
       </c>
       <c r="W18" t="n">
-        <v>-38.56</v>
+        <v>-37.707</v>
       </c>
     </row>
     <row r="19">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ENERY.IS, KCHOL.IS, PETKM.IS</t>
+          <t>DOHOL.IS, ENERY.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10 | PETKM.IS: 2026-09-14</t>
+          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2109,14 +2109,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ENERY.IS: +0.79% / +2.98% / -0.24% | KCHOL.IS: -2.43% / +1.47% / -2.81% | PETKM.IS: -3.15% / +0.76% / -3.30%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.38% / +1.47% / -2.81%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.90072974058688</v>
+        <v>-13.68024273423835</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2125,10 +2125,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.4</v>
+        <v>192.9</v>
       </c>
       <c r="O21" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2148,13 +2148,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>50.898</v>
+        <v>51.284</v>
       </c>
       <c r="V21" t="n">
-        <v>14.314</v>
+        <v>14.606</v>
       </c>
       <c r="W21" t="n">
-        <v>-27.154</v>
+        <v>-26.768</v>
       </c>
     </row>
     <row r="22">
@@ -2198,14 +2198,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -2.28% / +4.51% / -3.01% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.397220774440417</v>
+        <v>-7.754200362813613</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2231,19 +2231,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>19.727</v>
+        <v>19.819</v>
       </c>
       <c r="T22" t="n">
-        <v>19.727</v>
+        <v>19.819</v>
       </c>
       <c r="U22" t="n">
-        <v>69.316</v>
+        <v>68.663</v>
       </c>
       <c r="V22" t="n">
-        <v>26.714</v>
+        <v>26.225</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.036</v>
+        <v>-41.689</v>
       </c>
     </row>
     <row r="23">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>10.0335006811529</v>
+        <v>10.8306138039028</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2326,13 +2326,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>90.003</v>
+        <v>91.38</v>
       </c>
       <c r="V23" t="n">
-        <v>102.745</v>
+        <v>104.214</v>
       </c>
       <c r="W23" t="n">
-        <v>-21.247</v>
+        <v>-19.87</v>
       </c>
     </row>
     <row r="24">
@@ -2376,14 +2376,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +15.82% / +18.35% / -0.46% | KUYAS.IS: -2.63% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>10.0335006811529</v>
+        <v>10.8306138039028</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2415,13 +2415,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>90.003</v>
+        <v>91.38</v>
       </c>
       <c r="V24" t="n">
-        <v>102.745</v>
+        <v>104.214</v>
       </c>
       <c r="W24" t="n">
-        <v>-21.247</v>
+        <v>-19.87</v>
       </c>
     </row>
     <row r="25">
@@ -2614,7 +2614,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.426657813919613</v>
+        <v>-7.55668380443999</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2646,13 +2646,13 @@
         <v>10.751</v>
       </c>
       <c r="U27" t="n">
-        <v>12.099</v>
+        <v>11.942</v>
       </c>
       <c r="V27" t="n">
-        <v>4.23</v>
+        <v>4.083</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.289</v>
+        <v>-13.446</v>
       </c>
     </row>
   </sheetData>
@@ -2865,14 +2865,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>6.965980265787119</v>
+        <v>7.514610973351199</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2904,13 +2904,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>270.544</v>
+        <v>272.444</v>
       </c>
       <c r="V3" t="n">
-        <v>115.48</v>
+        <v>116.585</v>
       </c>
       <c r="W3" t="n">
-        <v>-14.529</v>
+        <v>-12.628</v>
       </c>
     </row>
     <row r="4">
@@ -2947,7 +2947,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.78783400662118</v>
+        <v>-12.7652142704672</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2973,19 +2973,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>27.212</v>
+        <v>27.193</v>
       </c>
       <c r="T4" t="n">
-        <v>27.212</v>
+        <v>27.193</v>
       </c>
       <c r="U4" t="n">
-        <v>55.319</v>
+        <v>55.359</v>
       </c>
       <c r="V4" t="n">
-        <v>17.337</v>
+        <v>17.367</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.067</v>
+        <v>-58.027</v>
       </c>
     </row>
     <row r="5">
@@ -3027,14 +3027,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>6.944566693136123</v>
+        <v>7.493087570046697</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3066,13 +3066,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>267.698</v>
+        <v>269.583</v>
       </c>
       <c r="V5" t="n">
-        <v>96.23</v>
+        <v>97.236</v>
       </c>
       <c r="W5" t="n">
-        <v>-14.373</v>
+        <v>-12.487</v>
       </c>
     </row>
     <row r="6">
@@ -3114,14 +3114,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +4.08% / +15.33% / -2.99% | ENERY.IS: +15.40% / +17.84% / -0.50% | GUBRF.IS: -1.75% / +0.14% / -2.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: +3.28% / +15.33% / -2.99% | ENERY.IS: +17.15% / +17.84% / -0.50% | GUBRF.IS: -3.58% / +0.14% / -3.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.474712421640628</v>
+        <v>-7.523385322341502</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3153,13 +3153,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>25.898</v>
+        <v>25.832</v>
       </c>
       <c r="V6" t="n">
-        <v>15.034</v>
+        <v>14.973</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.226</v>
+        <v>-39.292</v>
       </c>
     </row>
     <row r="7">
@@ -3196,7 +3196,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-12.78783400662118</v>
+        <v>-12.7652142704672</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3222,19 +3222,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>27.212</v>
+        <v>27.193</v>
       </c>
       <c r="T7" t="n">
-        <v>27.212</v>
+        <v>27.193</v>
       </c>
       <c r="U7" t="n">
-        <v>55.319</v>
+        <v>55.359</v>
       </c>
       <c r="V7" t="n">
-        <v>17.337</v>
+        <v>17.367</v>
       </c>
       <c r="W7" t="n">
-        <v>-58.067</v>
+        <v>-58.027</v>
       </c>
     </row>
     <row r="8">
@@ -3276,14 +3276,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +15.40% / +17.84% / -0.50% | ISCTR.IS: -2.29% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +17.15% / +17.84% / -0.50% | ISCTR.IS: -2.80% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4763882887171778</v>
+        <v>-0.1686725268721601</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3315,13 +3315,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>27.718</v>
+        <v>28.113</v>
       </c>
       <c r="V8" t="n">
-        <v>4.311</v>
+        <v>4.633</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.186</v>
+        <v>-28.791</v>
       </c>
     </row>
     <row r="9">
@@ -3433,7 +3433,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.563388469867014</v>
+        <v>-3.856927603309057</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3459,19 +3459,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20.983</v>
+        <v>20.398</v>
       </c>
       <c r="T10" t="n">
-        <v>20.983</v>
+        <v>20.398</v>
       </c>
       <c r="U10" t="n">
-        <v>8.932</v>
+        <v>9.739000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.992</v>
+        <v>-3.282</v>
       </c>
       <c r="W10" t="n">
-        <v>-28.927</v>
+        <v>-28.121</v>
       </c>
     </row>
     <row r="11">
@@ -3508,7 +3508,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.70639109087314</v>
+        <v>-12.68375023132146</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3534,19 +3534,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>25.924</v>
+        <v>25.905</v>
       </c>
       <c r="T11" t="n">
-        <v>25.924</v>
+        <v>25.905</v>
       </c>
       <c r="U11" t="n">
-        <v>31.612</v>
+        <v>31.647</v>
       </c>
       <c r="V11" t="n">
-        <v>4.68</v>
+        <v>4.707</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.06</v>
+        <v>-46.026</v>
       </c>
     </row>
     <row r="12">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>10.5099231963651</v>
+        <v>10.48253072482315</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3627,13 +3627,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>43.697</v>
+        <v>43.661</v>
       </c>
       <c r="V12" t="n">
-        <v>53.985</v>
+        <v>53.947</v>
       </c>
       <c r="W12" t="n">
-        <v>-16.591</v>
+        <v>-16.627</v>
       </c>
     </row>
     <row r="13">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>6.965980265787119</v>
+        <v>7.514610973351199</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3714,13 +3714,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>270.544</v>
+        <v>272.444</v>
       </c>
       <c r="V13" t="n">
-        <v>115.48</v>
+        <v>116.585</v>
       </c>
       <c r="W13" t="n">
-        <v>-14.529</v>
+        <v>-12.628</v>
       </c>
     </row>
     <row r="14">
@@ -3762,14 +3762,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>6.944566693136123</v>
+        <v>7.493087570046697</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3801,13 +3801,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>267.698</v>
+        <v>269.583</v>
       </c>
       <c r="V14" t="n">
-        <v>96.23</v>
+        <v>97.236</v>
       </c>
       <c r="W14" t="n">
-        <v>-14.373</v>
+        <v>-12.487</v>
       </c>
     </row>
     <row r="16">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>6.965980265787119</v>
+        <v>7.514610973351199</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4014,13 +4014,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>270.544</v>
+        <v>272.444</v>
       </c>
       <c r="V18" t="n">
-        <v>115.48</v>
+        <v>116.585</v>
       </c>
       <c r="W18" t="n">
-        <v>-14.529</v>
+        <v>-12.628</v>
       </c>
     </row>
     <row r="19">
@@ -4059,7 +4059,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.78783400662118</v>
+        <v>-12.7652142704672</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4085,19 +4085,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>27.212</v>
+        <v>27.193</v>
       </c>
       <c r="T19" t="n">
-        <v>27.212</v>
+        <v>27.193</v>
       </c>
       <c r="U19" t="n">
-        <v>55.319</v>
+        <v>55.359</v>
       </c>
       <c r="V19" t="n">
-        <v>17.337</v>
+        <v>17.367</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.067</v>
+        <v>-58.027</v>
       </c>
     </row>
     <row r="20">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +12.80% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>6.944566693136123</v>
+        <v>7.493087570046697</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4180,13 +4180,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>267.698</v>
+        <v>269.583</v>
       </c>
       <c r="V20" t="n">
-        <v>96.23</v>
+        <v>97.236</v>
       </c>
       <c r="W20" t="n">
-        <v>-14.373</v>
+        <v>-12.487</v>
       </c>
     </row>
     <row r="21">
@@ -4225,7 +4225,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.70639109087314</v>
+        <v>-12.68375023132146</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4251,19 +4251,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>25.924</v>
+        <v>25.905</v>
       </c>
       <c r="T21" t="n">
-        <v>25.924</v>
+        <v>25.905</v>
       </c>
       <c r="U21" t="n">
-        <v>31.612</v>
+        <v>31.647</v>
       </c>
       <c r="V21" t="n">
-        <v>4.68</v>
+        <v>4.707</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.06</v>
+        <v>-46.026</v>
       </c>
     </row>
     <row r="22">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: +4.08% / +15.33% / -2.99% | ENERY.IS: +15.40% / +17.84% / -0.50% | GUBRF.IS: -1.75% / +0.14% / -2.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: +3.28% / +15.33% / -2.99% | ENERY.IS: +17.15% / +17.84% / -0.50% | GUBRF.IS: -3.58% / +0.14% / -3.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.474712421640628</v>
+        <v>-7.523385322341502</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4346,13 +4346,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>25.898</v>
+        <v>25.832</v>
       </c>
       <c r="V22" t="n">
-        <v>15.034</v>
+        <v>14.973</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.226</v>
+        <v>-39.292</v>
       </c>
     </row>
     <row r="23">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +15.40% / +17.84% / -0.50% | ISCTR.IS: -2.29% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +17.15% / +17.84% / -0.50% | ISCTR.IS: -2.80% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4763882887171778</v>
+        <v>-0.1686725268721601</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4435,13 +4435,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>27.718</v>
+        <v>28.113</v>
       </c>
       <c r="V23" t="n">
-        <v>4.311</v>
+        <v>4.633</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.186</v>
+        <v>-28.791</v>
       </c>
     </row>
     <row r="24">
@@ -4480,7 +4480,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.563388469867014</v>
+        <v>-3.856927603309057</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4506,19 +4506,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>20.983</v>
+        <v>20.398</v>
       </c>
       <c r="T24" t="n">
-        <v>20.983</v>
+        <v>20.398</v>
       </c>
       <c r="U24" t="n">
-        <v>8.932</v>
+        <v>9.739000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.992</v>
+        <v>-3.282</v>
       </c>
       <c r="W24" t="n">
-        <v>-28.927</v>
+        <v>-28.121</v>
       </c>
     </row>
     <row r="25">
@@ -4639,14 +4639,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.29% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>10.5099231963651</v>
+        <v>10.48253072482315</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4678,13 +4678,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>43.697</v>
+        <v>43.661</v>
       </c>
       <c r="V26" t="n">
-        <v>53.985</v>
+        <v>53.947</v>
       </c>
       <c r="W26" t="n">
-        <v>-16.591</v>
+        <v>-16.627</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>DOHOL.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
+          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.33874110560147</v>
+        <v>-11.77408939648555</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,10 +772,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>101.6</v>
+        <v>102.1</v>
       </c>
       <c r="O3" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="P3" t="n">
         <v>6.8</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>74.333</v>
+        <v>73.477</v>
       </c>
       <c r="V3" t="n">
-        <v>20.453</v>
+        <v>19.862</v>
       </c>
       <c r="W3" t="n">
-        <v>-37.707</v>
+        <v>-38.563</v>
       </c>
     </row>
     <row r="4">
@@ -980,12 +980,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>DOHOL.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
+          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.33874110560147</v>
+        <v>-11.77408939648555</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,10 +1009,10 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>101.6</v>
+        <v>102.1</v>
       </c>
       <c r="O6" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="P6" t="n">
         <v>6.8</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>74.333</v>
+        <v>73.477</v>
       </c>
       <c r="V6" t="n">
-        <v>20.453</v>
+        <v>19.862</v>
       </c>
       <c r="W6" t="n">
-        <v>-37.707</v>
+        <v>-38.563</v>
       </c>
     </row>
     <row r="7">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CANTE.IS, DOHOL.IS</t>
+          <t>DOHOL.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-09-15</t>
+          <t>DOHOL.IS: 2026-09-15 | FROTO.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.754200362813613</v>
+        <v>-8.243709623367824</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,13 +1096,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.8</v>
+        <v>135.3</v>
       </c>
       <c r="O7" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>19.819</v>
+        <v>20.244</v>
       </c>
       <c r="T7" t="n">
-        <v>19.819</v>
+        <v>20.244</v>
       </c>
       <c r="U7" t="n">
-        <v>68.663</v>
+        <v>67.768</v>
       </c>
       <c r="V7" t="n">
-        <v>26.225</v>
+        <v>25.555</v>
       </c>
       <c r="W7" t="n">
-        <v>-41.689</v>
+        <v>-42.584</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.38% / +1.47% / -2.81%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.47% / +1.47% / -2.81%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.68024273423835</v>
+        <v>-13.70637168969533</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>51.284</v>
+        <v>51.238</v>
       </c>
       <c r="V8" t="n">
-        <v>14.606</v>
+        <v>14.572</v>
       </c>
       <c r="W8" t="n">
-        <v>-26.768</v>
+        <v>-26.813</v>
       </c>
     </row>
     <row r="9">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>DOHOL.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
+          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.33874110560147</v>
+        <v>-11.77408939648555</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,10 +1270,10 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>101.6</v>
+        <v>102.1</v>
       </c>
       <c r="O9" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="P9" t="n">
         <v>6.8</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>74.333</v>
+        <v>73.477</v>
       </c>
       <c r="V9" t="n">
-        <v>20.453</v>
+        <v>19.862</v>
       </c>
       <c r="W9" t="n">
-        <v>-37.707</v>
+        <v>-38.563</v>
       </c>
     </row>
     <row r="10">
@@ -1336,7 +1336,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.55668380443999</v>
+        <v>-7.589190302070103</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1348,7 +1348,7 @@
         <v>177.3</v>
       </c>
       <c r="O10" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -1362,19 +1362,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>10.751</v>
+        <v>10.755</v>
       </c>
       <c r="T10" t="n">
-        <v>10.751</v>
+        <v>10.755</v>
       </c>
       <c r="U10" t="n">
-        <v>11.942</v>
+        <v>11.903</v>
       </c>
       <c r="V10" t="n">
-        <v>4.083</v>
+        <v>4.047</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.446</v>
+        <v>-13.485</v>
       </c>
     </row>
     <row r="11">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1566,14 +1566,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>10.8306138039028</v>
+        <v>10.28295965565247</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1582,10 +1582,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
       <c r="O13" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="P13" t="n">
         <v>6.2</v>
@@ -1605,13 +1605,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>91.38</v>
+        <v>90.434</v>
       </c>
       <c r="V13" t="n">
-        <v>104.214</v>
+        <v>103.205</v>
       </c>
       <c r="W13" t="n">
-        <v>-19.87</v>
+        <v>-20.816</v>
       </c>
     </row>
     <row r="14">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>10.8306138039028</v>
+        <v>10.28295965565247</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1669,10 +1669,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
       <c r="O14" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="P14" t="n">
         <v>6.2</v>
@@ -1692,13 +1692,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>91.38</v>
+        <v>90.434</v>
       </c>
       <c r="V14" t="n">
-        <v>104.214</v>
+        <v>103.205</v>
       </c>
       <c r="W14" t="n">
-        <v>-19.87</v>
+        <v>-20.816</v>
       </c>
     </row>
     <row r="16">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS</t>
+          <t>DOHOL.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
+          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1866,14 +1866,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.33874110560147</v>
+        <v>-11.77408939648555</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1882,10 +1882,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>101.6</v>
+        <v>102.1</v>
       </c>
       <c r="O18" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="P18" t="n">
         <v>6.8</v>
@@ -1905,13 +1905,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>74.333</v>
+        <v>73.477</v>
       </c>
       <c r="V18" t="n">
-        <v>20.453</v>
+        <v>19.862</v>
       </c>
       <c r="W18" t="n">
-        <v>-37.707</v>
+        <v>-38.563</v>
       </c>
     </row>
     <row r="19">
@@ -2109,14 +2109,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.38% / +1.47% / -2.81%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.47% / +1.47% / -2.81%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.68024273423835</v>
+        <v>-13.70637168969533</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2148,13 +2148,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>51.284</v>
+        <v>51.238</v>
       </c>
       <c r="V21" t="n">
-        <v>14.606</v>
+        <v>14.572</v>
       </c>
       <c r="W21" t="n">
-        <v>-26.768</v>
+        <v>-26.813</v>
       </c>
     </row>
     <row r="22">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANTE.IS, DOHOL.IS</t>
+          <t>DOHOL.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-09-15</t>
+          <t>DOHOL.IS: 2026-09-15 | FROTO.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2198,14 +2198,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -3.03% / +4.51% / -3.76% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.754200362813613</v>
+        <v>-8.243709623367824</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2214,13 +2214,13 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.8</v>
+        <v>135.3</v>
       </c>
       <c r="O22" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2231,19 +2231,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>19.819</v>
+        <v>20.244</v>
       </c>
       <c r="T22" t="n">
-        <v>19.819</v>
+        <v>20.244</v>
       </c>
       <c r="U22" t="n">
-        <v>68.663</v>
+        <v>67.768</v>
       </c>
       <c r="V22" t="n">
-        <v>26.225</v>
+        <v>25.555</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.689</v>
+        <v>-42.584</v>
       </c>
     </row>
     <row r="23">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>10.8306138039028</v>
+        <v>10.28295965565247</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2303,10 +2303,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
       <c r="O23" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="P23" t="n">
         <v>6.2</v>
@@ -2326,13 +2326,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>91.38</v>
+        <v>90.434</v>
       </c>
       <c r="V23" t="n">
-        <v>104.214</v>
+        <v>103.205</v>
       </c>
       <c r="W23" t="n">
-        <v>-19.87</v>
+        <v>-20.816</v>
       </c>
     </row>
     <row r="24">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-14</t>
+          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2376,14 +2376,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -2.98% / +0.00% / -3.51%</t>
+          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>10.8306138039028</v>
+        <v>10.28295965565247</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2392,10 +2392,10 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
       <c r="O24" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="P24" t="n">
         <v>6.2</v>
@@ -2415,13 +2415,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>91.38</v>
+        <v>90.434</v>
       </c>
       <c r="V24" t="n">
-        <v>104.214</v>
+        <v>103.205</v>
       </c>
       <c r="W24" t="n">
-        <v>-19.87</v>
+        <v>-20.816</v>
       </c>
     </row>
     <row r="25">
@@ -2614,7 +2614,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.55668380443999</v>
+        <v>-7.589190302070103</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2626,7 +2626,7 @@
         <v>177.3</v>
       </c>
       <c r="O27" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -2640,19 +2640,19 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>10.751</v>
+        <v>10.755</v>
       </c>
       <c r="T27" t="n">
-        <v>10.751</v>
+        <v>10.755</v>
       </c>
       <c r="U27" t="n">
-        <v>11.942</v>
+        <v>11.903</v>
       </c>
       <c r="V27" t="n">
-        <v>4.083</v>
+        <v>4.047</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.446</v>
+        <v>-13.485</v>
       </c>
     </row>
   </sheetData>
@@ -2865,14 +2865,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>7.514610973351199</v>
+        <v>7.43636031085706</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2884,7 +2884,7 @@
         <v>93.2</v>
       </c>
       <c r="O3" t="n">
-        <v>45.3</v>
+        <v>44.7</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2904,13 +2904,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>272.444</v>
+        <v>272.173</v>
       </c>
       <c r="V3" t="n">
-        <v>116.585</v>
+        <v>116.427</v>
       </c>
       <c r="W3" t="n">
-        <v>-12.628</v>
+        <v>-12.899</v>
       </c>
     </row>
     <row r="4">
@@ -2947,7 +2947,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.7652142704672</v>
+        <v>-12.8807018120048</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2973,19 +2973,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>27.193</v>
+        <v>27.29</v>
       </c>
       <c r="T4" t="n">
-        <v>27.193</v>
+        <v>27.29</v>
       </c>
       <c r="U4" t="n">
-        <v>55.359</v>
+        <v>55.153</v>
       </c>
       <c r="V4" t="n">
-        <v>17.367</v>
+        <v>17.212</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.027</v>
+        <v>-58.233</v>
       </c>
     </row>
     <row r="5">
@@ -3027,14 +3027,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>7.493087570046697</v>
+        <v>7.414852572591513</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3046,7 +3046,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3066,13 +3066,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>269.583</v>
+        <v>269.314</v>
       </c>
       <c r="V5" t="n">
-        <v>97.236</v>
+        <v>97.093</v>
       </c>
       <c r="W5" t="n">
-        <v>-12.487</v>
+        <v>-12.756</v>
       </c>
     </row>
     <row r="6">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, GUBRF.IS, ISCTR.IS, TKFEN.IS</t>
+          <t>ENERY.IS, GUBRF.IS, ISCTR.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | SASA.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3114,14 +3114,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +3.28% / +15.33% / -2.99% | ENERY.IS: +17.15% / +17.84% / -0.50% | GUBRF.IS: -3.58% / +0.14% / -3.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | GUBRF.IS: -3.78% / +0.15% / -3.92% | ISCTR.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.523385322341502</v>
+        <v>-8.20386729215855</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3130,10 +3130,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138.7</v>
+        <v>139.2</v>
       </c>
       <c r="O6" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3153,13 +3153,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>25.832</v>
+        <v>24.906</v>
       </c>
       <c r="V6" t="n">
-        <v>14.973</v>
+        <v>14.127</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.292</v>
+        <v>-40.218</v>
       </c>
     </row>
     <row r="7">
@@ -3196,7 +3196,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-12.7652142704672</v>
+        <v>-12.8807018120048</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3222,19 +3222,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>27.193</v>
+        <v>27.29</v>
       </c>
       <c r="T7" t="n">
-        <v>27.193</v>
+        <v>27.29</v>
       </c>
       <c r="U7" t="n">
-        <v>55.359</v>
+        <v>55.153</v>
       </c>
       <c r="V7" t="n">
-        <v>17.367</v>
+        <v>17.212</v>
       </c>
       <c r="W7" t="n">
-        <v>-58.027</v>
+        <v>-58.233</v>
       </c>
     </row>
     <row r="8">
@@ -3276,14 +3276,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.15% / +17.84% / -0.50% | ISCTR.IS: -2.80% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | ISCTR.IS: -3.08% / +1.99% / -3.07% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1686725268721601</v>
+        <v>-0.2509101988227402</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3315,13 +3315,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>28.113</v>
+        <v>28.007</v>
       </c>
       <c r="V8" t="n">
-        <v>4.633</v>
+        <v>4.547</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.791</v>
+        <v>-28.897</v>
       </c>
     </row>
     <row r="9">
@@ -3433,7 +3433,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.856927603309057</v>
+        <v>-3.897983070125099</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3459,19 +3459,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20.398</v>
+        <v>20.432</v>
       </c>
       <c r="T10" t="n">
-        <v>20.398</v>
+        <v>20.432</v>
       </c>
       <c r="U10" t="n">
-        <v>9.739000000000001</v>
+        <v>9.692</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.282</v>
+        <v>-3.323</v>
       </c>
       <c r="W10" t="n">
-        <v>-28.121</v>
+        <v>-28.168</v>
       </c>
     </row>
     <row r="11">
@@ -3508,7 +3508,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.68375023132146</v>
+        <v>-12.79934562068065</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3534,19 +3534,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>25.905</v>
+        <v>26.003</v>
       </c>
       <c r="T11" t="n">
-        <v>25.905</v>
+        <v>26.003</v>
       </c>
       <c r="U11" t="n">
-        <v>31.647</v>
+        <v>31.472</v>
       </c>
       <c r="V11" t="n">
-        <v>4.707</v>
+        <v>4.568</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.026</v>
+        <v>-46.2</v>
       </c>
     </row>
     <row r="12">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>10.48253072482315</v>
+        <v>9.526648711131092</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3627,13 +3627,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>43.661</v>
+        <v>42.418</v>
       </c>
       <c r="V12" t="n">
-        <v>53.947</v>
+        <v>52.615</v>
       </c>
       <c r="W12" t="n">
-        <v>-16.627</v>
+        <v>-17.87</v>
       </c>
     </row>
     <row r="13">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>7.514610973351199</v>
+        <v>7.43636031085706</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3694,7 +3694,7 @@
         <v>93.2</v>
       </c>
       <c r="O13" t="n">
-        <v>45.3</v>
+        <v>44.7</v>
       </c>
       <c r="P13" t="n">
         <v>4.3</v>
@@ -3714,13 +3714,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>272.444</v>
+        <v>272.173</v>
       </c>
       <c r="V13" t="n">
-        <v>116.585</v>
+        <v>116.427</v>
       </c>
       <c r="W13" t="n">
-        <v>-12.628</v>
+        <v>-12.899</v>
       </c>
     </row>
     <row r="14">
@@ -3762,14 +3762,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>7.493087570046697</v>
+        <v>7.414852572591513</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3781,7 +3781,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="P14" t="n">
         <v>4.7</v>
@@ -3801,13 +3801,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>269.583</v>
+        <v>269.314</v>
       </c>
       <c r="V14" t="n">
-        <v>97.236</v>
+        <v>97.093</v>
       </c>
       <c r="W14" t="n">
-        <v>-12.487</v>
+        <v>-12.756</v>
       </c>
     </row>
     <row r="16">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>7.514610973351199</v>
+        <v>7.43636031085706</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3994,7 +3994,7 @@
         <v>93.2</v>
       </c>
       <c r="O18" t="n">
-        <v>45.3</v>
+        <v>44.7</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4014,13 +4014,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>272.444</v>
+        <v>272.173</v>
       </c>
       <c r="V18" t="n">
-        <v>116.585</v>
+        <v>116.427</v>
       </c>
       <c r="W18" t="n">
-        <v>-12.628</v>
+        <v>-12.899</v>
       </c>
     </row>
     <row r="19">
@@ -4059,7 +4059,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.7652142704672</v>
+        <v>-12.8807018120048</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4085,19 +4085,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>27.193</v>
+        <v>27.29</v>
       </c>
       <c r="T19" t="n">
-        <v>27.193</v>
+        <v>27.29</v>
       </c>
       <c r="U19" t="n">
-        <v>55.359</v>
+        <v>55.153</v>
       </c>
       <c r="V19" t="n">
-        <v>17.367</v>
+        <v>17.212</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.027</v>
+        <v>-58.233</v>
       </c>
     </row>
     <row r="20">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.52% / +15.15% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>7.493087570046697</v>
+        <v>7.414852572591513</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4160,7 +4160,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4180,13 +4180,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>269.583</v>
+        <v>269.314</v>
       </c>
       <c r="V20" t="n">
-        <v>97.236</v>
+        <v>97.093</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.487</v>
+        <v>-12.756</v>
       </c>
     </row>
     <row r="21">
@@ -4225,7 +4225,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.68375023132146</v>
+        <v>-12.79934562068065</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4251,19 +4251,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>25.905</v>
+        <v>26.003</v>
       </c>
       <c r="T21" t="n">
-        <v>25.905</v>
+        <v>26.003</v>
       </c>
       <c r="U21" t="n">
-        <v>31.647</v>
+        <v>31.472</v>
       </c>
       <c r="V21" t="n">
-        <v>4.707</v>
+        <v>4.568</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.026</v>
+        <v>-46.2</v>
       </c>
     </row>
     <row r="22">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, GUBRF.IS, ISCTR.IS, TKFEN.IS</t>
+          <t>ENERY.IS, GUBRF.IS, ISCTR.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | SASA.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: +3.28% / +15.33% / -2.99% | ENERY.IS: +17.15% / +17.84% / -0.50% | GUBRF.IS: -3.58% / +0.14% / -3.67% | ISCTR.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | GUBRF.IS: -3.78% / +0.15% / -3.92% | ISCTR.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.523385322341502</v>
+        <v>-8.20386729215855</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4323,10 +4323,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138.7</v>
+        <v>139.2</v>
       </c>
       <c r="O22" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4346,13 +4346,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>25.832</v>
+        <v>24.906</v>
       </c>
       <c r="V22" t="n">
-        <v>14.973</v>
+        <v>14.127</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.292</v>
+        <v>-40.218</v>
       </c>
     </row>
     <row r="23">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.15% / +17.84% / -0.50% | ISCTR.IS: -2.80% / +1.99% / -2.93% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | ISCTR.IS: -3.08% / +1.99% / -3.07% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1686725268721601</v>
+        <v>-0.2509101988227402</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4435,13 +4435,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>28.113</v>
+        <v>28.007</v>
       </c>
       <c r="V23" t="n">
-        <v>4.633</v>
+        <v>4.547</v>
       </c>
       <c r="W23" t="n">
-        <v>-28.791</v>
+        <v>-28.897</v>
       </c>
     </row>
     <row r="24">
@@ -4480,7 +4480,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.856927603309057</v>
+        <v>-3.897983070125099</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4506,19 +4506,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>20.398</v>
+        <v>20.432</v>
       </c>
       <c r="T24" t="n">
-        <v>20.398</v>
+        <v>20.432</v>
       </c>
       <c r="U24" t="n">
-        <v>9.739000000000001</v>
+        <v>9.692</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.282</v>
+        <v>-3.323</v>
       </c>
       <c r="W24" t="n">
-        <v>-28.121</v>
+        <v>-28.168</v>
       </c>
     </row>
     <row r="25">
@@ -4639,14 +4639,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.82% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>10.48253072482315</v>
+        <v>9.526648711131092</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4678,13 +4678,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>43.661</v>
+        <v>42.418</v>
       </c>
       <c r="V26" t="n">
-        <v>53.947</v>
+        <v>52.615</v>
       </c>
       <c r="W26" t="n">
-        <v>-16.627</v>
+        <v>-17.87</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,7 +573,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -733,22 +733,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ENERY.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.77408939648555</v>
+        <v>-12.88475179946702</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,13 +772,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O3" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="P3" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>73.477</v>
+        <v>64.297</v>
       </c>
       <c r="V3" t="n">
-        <v>19.862</v>
+        <v>18.353</v>
       </c>
       <c r="W3" t="n">
-        <v>-38.563</v>
+        <v>-39.082</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,22 +970,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ENERY.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.77408939648555</v>
+        <v>-12.88475179946702</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,13 +1009,13 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O6" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="P6" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>73.477</v>
+        <v>64.297</v>
       </c>
       <c r="V6" t="n">
-        <v>19.862</v>
+        <v>18.353</v>
       </c>
       <c r="W6" t="n">
-        <v>-38.563</v>
+        <v>-39.082</v>
       </c>
     </row>
     <row r="7">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DOHOL.IS, FROTO.IS</t>
+          <t>FROTO.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | FROTO.IS: 2026-09-15</t>
+          <t>FROTO.IS: 2026-09-15 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FROTO.IS: -1.68% / +0.57% / -2.23% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.243709623367824</v>
+        <v>-10.85755502119113</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>135.3</v>
+        <v>135.5</v>
       </c>
       <c r="O7" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>20.244</v>
+        <v>22.516</v>
       </c>
       <c r="T7" t="n">
-        <v>20.244</v>
+        <v>22.516</v>
       </c>
       <c r="U7" t="n">
-        <v>67.768</v>
+        <v>48.269</v>
       </c>
       <c r="V7" t="n">
-        <v>25.555</v>
+        <v>21.979</v>
       </c>
       <c r="W7" t="n">
-        <v>-42.584</v>
+        <v>-43.086</v>
       </c>
     </row>
     <row r="8">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ENERY.IS, KCHOL.IS</t>
+          <t>ENERY.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10</t>
+          <t>ENERY.IS: 2026-09-14 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.47% / +1.47% / -2.81%</t>
+          <t>ENERY.IS: +3.53% / +6.94% / -0.24% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.70637168969533</v>
+        <v>-14.96376449252201</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.9</v>
+        <v>193.5</v>
       </c>
       <c r="O8" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>51.238</v>
+        <v>49.055</v>
       </c>
       <c r="V8" t="n">
-        <v>14.572</v>
+        <v>12.902</v>
       </c>
       <c r="W8" t="n">
-        <v>-26.813</v>
+        <v>-29.021</v>
       </c>
     </row>
     <row r="9">
@@ -1231,22 +1231,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ENERY.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.77408939648555</v>
+        <v>-12.88475179946702</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,13 +1270,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O9" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="P9" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>73.477</v>
+        <v>64.297</v>
       </c>
       <c r="V9" t="n">
-        <v>19.862</v>
+        <v>18.353</v>
       </c>
       <c r="W9" t="n">
-        <v>-38.563</v>
+        <v>-39.082</v>
       </c>
     </row>
     <row r="10">
@@ -1318,25 +1318,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>23.02092795860866</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.589190302070103</v>
+        <v>-7.596583166845939</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1345,36 +1357,36 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>177.3</v>
+        <v>177.4</v>
       </c>
       <c r="O10" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>10.755</v>
+        <v>10.762</v>
       </c>
       <c r="T10" t="n">
-        <v>10.755</v>
+        <v>10.762</v>
       </c>
       <c r="U10" t="n">
-        <v>11.903</v>
+        <v>11.894</v>
       </c>
       <c r="V10" t="n">
-        <v>4.047</v>
+        <v>4.038</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.485</v>
+        <v>-13.494</v>
       </c>
     </row>
     <row r="11">
@@ -1393,12 +1405,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1420,7 +1432,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1468,12 +1480,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1495,7 +1507,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="O12" t="n">
         <v>47.7</v>
@@ -1543,22 +1555,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1566,14 +1578,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>10.28295965565247</v>
+        <v>8.999673187694079</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1582,10 +1594,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="O13" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="P13" t="n">
         <v>6.2</v>
@@ -1605,13 +1617,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>90.434</v>
+        <v>88.218</v>
       </c>
       <c r="V13" t="n">
-        <v>103.205</v>
+        <v>100.84</v>
       </c>
       <c r="W13" t="n">
-        <v>-20.816</v>
+        <v>-23.032</v>
       </c>
     </row>
     <row r="14">
@@ -1630,22 +1642,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1653,14 +1665,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>10.28295965565247</v>
+        <v>8.999673187694079</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1669,10 +1681,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="O14" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="P14" t="n">
         <v>6.2</v>
@@ -1692,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>90.434</v>
+        <v>88.218</v>
       </c>
       <c r="V14" t="n">
-        <v>103.205</v>
+        <v>100.84</v>
       </c>
       <c r="W14" t="n">
-        <v>-20.816</v>
+        <v>-23.032</v>
       </c>
     </row>
     <row r="16">
@@ -1843,22 +1855,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ENERY.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-07</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1866,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +17.68% / +18.35% / -0.46%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.77408939648555</v>
+        <v>-12.88475179946702</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1882,13 +1894,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O18" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="P18" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1905,13 +1917,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>73.477</v>
+        <v>64.297</v>
       </c>
       <c r="V18" t="n">
-        <v>19.862</v>
+        <v>18.353</v>
       </c>
       <c r="W18" t="n">
-        <v>-38.563</v>
+        <v>-39.082</v>
       </c>
     </row>
     <row r="19">
@@ -1932,12 +1944,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1959,7 +1971,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -2009,12 +2021,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2036,7 +2048,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2086,22 +2098,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ENERY.IS, KCHOL.IS</t>
+          <t>ENERY.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | ENERY.IS: 2026-09-14 | KCHOL.IS: 2026-09-10</t>
+          <t>ENERY.IS: 2026-09-14 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2109,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.40% / +2.98% / -0.24% | KCHOL.IS: -2.47% / +1.47% / -2.81%</t>
+          <t>ENERY.IS: +3.53% / +6.94% / -0.24% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.70637168969533</v>
+        <v>-14.96376449252201</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2125,10 +2137,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.9</v>
+        <v>193.5</v>
       </c>
       <c r="O21" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2148,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>51.238</v>
+        <v>49.055</v>
       </c>
       <c r="V21" t="n">
-        <v>14.572</v>
+        <v>12.902</v>
       </c>
       <c r="W21" t="n">
-        <v>-26.813</v>
+        <v>-29.021</v>
       </c>
     </row>
     <row r="22">
@@ -2175,22 +2187,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DOHOL.IS, FROTO.IS</t>
+          <t>FROTO.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-09-15 | FROTO.IS: 2026-09-15</t>
+          <t>FROTO.IS: 2026-09-15 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2198,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FROTO.IS: -1.68% / +0.57% / -2.23% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.243709623367824</v>
+        <v>-10.85755502119113</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2214,10 +2226,10 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>135.3</v>
+        <v>135.5</v>
       </c>
       <c r="O22" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -2231,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>20.244</v>
+        <v>22.516</v>
       </c>
       <c r="T22" t="n">
-        <v>20.244</v>
+        <v>22.516</v>
       </c>
       <c r="U22" t="n">
-        <v>67.768</v>
+        <v>48.269</v>
       </c>
       <c r="V22" t="n">
-        <v>25.555</v>
+        <v>21.979</v>
       </c>
       <c r="W22" t="n">
-        <v>-42.584</v>
+        <v>-43.086</v>
       </c>
     </row>
     <row r="23">
@@ -2264,22 +2276,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2287,14 +2299,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>10.28295965565247</v>
+        <v>8.999673187694079</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2303,10 +2315,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="O23" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="P23" t="n">
         <v>6.2</v>
@@ -2326,13 +2338,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>90.434</v>
+        <v>88.218</v>
       </c>
       <c r="V23" t="n">
-        <v>103.205</v>
+        <v>100.84</v>
       </c>
       <c r="W23" t="n">
-        <v>-20.816</v>
+        <v>-23.032</v>
       </c>
     </row>
     <row r="24">
@@ -2353,22 +2365,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2376,14 +2388,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.68% / +18.35% / -0.46% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>10.28295965565247</v>
+        <v>8.999673187694079</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2392,10 +2404,10 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="O24" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="P24" t="n">
         <v>6.2</v>
@@ -2415,13 +2427,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>90.434</v>
+        <v>88.218</v>
       </c>
       <c r="V24" t="n">
-        <v>103.205</v>
+        <v>100.84</v>
       </c>
       <c r="W24" t="n">
-        <v>-20.816</v>
+        <v>-23.032</v>
       </c>
     </row>
     <row r="25">
@@ -2442,12 +2454,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2469,7 +2481,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2519,12 +2531,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2546,7 +2558,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N26" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="O26" t="n">
         <v>47.7</v>
@@ -2596,25 +2608,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>23.02092795860866</v>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.589190302070103</v>
+        <v>-7.596583166845939</v>
       </c>
       <c r="L27" t="n">
         <v>4.543450519200398</v>
@@ -2623,36 +2647,36 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N27" t="n">
-        <v>177.3</v>
+        <v>177.4</v>
       </c>
       <c r="O27" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>10.755</v>
+        <v>10.762</v>
       </c>
       <c r="T27" t="n">
-        <v>10.755</v>
+        <v>10.762</v>
       </c>
       <c r="U27" t="n">
-        <v>11.903</v>
+        <v>11.894</v>
       </c>
       <c r="V27" t="n">
-        <v>4.047</v>
+        <v>4.038</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.485</v>
+        <v>-13.494</v>
       </c>
     </row>
   </sheetData>
@@ -2687,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2842,22 +2866,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2865,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>7.43636031085706</v>
+        <v>5.297823468212948</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2881,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>93.2</v>
+        <v>93.5</v>
       </c>
       <c r="O3" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2904,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>272.173</v>
+        <v>236.178</v>
       </c>
       <c r="V3" t="n">
-        <v>116.427</v>
+        <v>112.119</v>
       </c>
       <c r="W3" t="n">
-        <v>-12.899</v>
+        <v>-18.716</v>
       </c>
     </row>
     <row r="4">
@@ -2929,12 +2953,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2947,7 +2971,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.8807018120048</v>
+        <v>-12.87810704828809</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2956,7 +2980,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>120.6</v>
+        <v>120.4</v>
       </c>
       <c r="O4" t="n">
         <v>46.3</v>
@@ -2973,19 +2997,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>27.29</v>
+        <v>27.288</v>
       </c>
       <c r="T4" t="n">
-        <v>27.29</v>
+        <v>27.288</v>
       </c>
       <c r="U4" t="n">
-        <v>55.153</v>
+        <v>55.158</v>
       </c>
       <c r="V4" t="n">
-        <v>17.212</v>
+        <v>17.216</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.233</v>
+        <v>-58.228</v>
       </c>
     </row>
     <row r="5">
@@ -3004,22 +3028,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3027,14 +3051,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>7.414852572591513</v>
+        <v>5.276743844698761</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3043,10 +3067,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="O5" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3066,13 +3090,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>269.314</v>
+        <v>233.595</v>
       </c>
       <c r="V5" t="n">
-        <v>97.093</v>
+        <v>93.169</v>
       </c>
       <c r="W5" t="n">
-        <v>-12.756</v>
+        <v>-18.531</v>
       </c>
     </row>
     <row r="6">
@@ -3091,22 +3115,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENERY.IS, GUBRF.IS, ISCTR.IS, SASA.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, RALYH.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | SASA.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-16 | ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3114,14 +3138,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | GUBRF.IS: -3.78% / +0.15% / -3.92% | ISCTR.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.20386729215855</v>
+        <v>-10.96548512631721</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3130,10 +3154,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>139.2</v>
+        <v>140.4</v>
       </c>
       <c r="O6" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3147,19 +3171,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.35</v>
+        <v>26.632</v>
       </c>
       <c r="T6" t="n">
-        <v>26.35</v>
+        <v>26.632</v>
       </c>
       <c r="U6" t="n">
-        <v>24.906</v>
+        <v>21.148</v>
       </c>
       <c r="V6" t="n">
-        <v>14.127</v>
+        <v>10.694</v>
       </c>
       <c r="W6" t="n">
-        <v>-40.218</v>
+        <v>-43.976</v>
       </c>
     </row>
     <row r="7">
@@ -3178,12 +3202,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3196,7 +3220,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-12.8807018120048</v>
+        <v>-12.87810704828809</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3205,7 +3229,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>120.6</v>
+        <v>120.4</v>
       </c>
       <c r="O7" t="n">
         <v>46.3</v>
@@ -3222,19 +3246,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>27.29</v>
+        <v>27.288</v>
       </c>
       <c r="T7" t="n">
-        <v>27.29</v>
+        <v>27.288</v>
       </c>
       <c r="U7" t="n">
-        <v>55.153</v>
+        <v>55.158</v>
       </c>
       <c r="V7" t="n">
-        <v>17.212</v>
+        <v>17.216</v>
       </c>
       <c r="W7" t="n">
-        <v>-58.233</v>
+        <v>-58.228</v>
       </c>
     </row>
     <row r="8">
@@ -3253,22 +3277,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENERY.IS, ISCTR.IS, SASA.IS</t>
+          <t>ENERY.IS, RALYH.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10 | SASA.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3276,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | ISCTR.IS: -3.08% / +1.99% / -3.07% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2509101988227402</v>
+        <v>-1.41384651455515</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3292,10 +3316,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153</v>
+        <v>153.6</v>
       </c>
       <c r="O8" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3315,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>28.007</v>
+        <v>19.346</v>
       </c>
       <c r="V8" t="n">
-        <v>4.547</v>
+        <v>3.328</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.897</v>
+        <v>-28.667</v>
       </c>
     </row>
     <row r="9">
@@ -3340,12 +3364,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3367,7 +3391,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3415,12 +3439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3433,7 +3457,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.897983070125099</v>
+        <v>-3.894746413359096</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3442,7 +3466,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114.2</v>
+        <v>114</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3459,19 +3483,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20.432</v>
+        <v>20.43</v>
       </c>
       <c r="T10" t="n">
-        <v>20.432</v>
+        <v>20.43</v>
       </c>
       <c r="U10" t="n">
-        <v>9.692</v>
+        <v>9.696</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.323</v>
+        <v>-3.32</v>
       </c>
       <c r="W10" t="n">
-        <v>-28.168</v>
+        <v>-28.164</v>
       </c>
     </row>
     <row r="11">
@@ -3490,12 +3514,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3508,7 +3532,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.79934562068065</v>
+        <v>-12.79674843384874</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3517,7 +3541,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>180.4</v>
+        <v>180.1</v>
       </c>
       <c r="O11" t="n">
         <v>51.6</v>
@@ -3534,19 +3558,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>26.003</v>
+        <v>26.001</v>
       </c>
       <c r="T11" t="n">
-        <v>26.003</v>
+        <v>26.001</v>
       </c>
       <c r="U11" t="n">
-        <v>31.472</v>
+        <v>31.476</v>
       </c>
       <c r="V11" t="n">
-        <v>4.568</v>
+        <v>4.571</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.2</v>
+        <v>-46.196</v>
       </c>
     </row>
     <row r="12">
@@ -3565,12 +3589,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3588,14 +3612,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.23% / +4.37% / -1.21% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.526648711131092</v>
+        <v>6.454016698576837</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3610,7 +3634,7 @@
         <v>42.9</v>
       </c>
       <c r="P12" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3627,13 +3651,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>42.418</v>
+        <v>38.423</v>
       </c>
       <c r="V12" t="n">
-        <v>52.615</v>
+        <v>48.333</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.87</v>
+        <v>-21.865</v>
       </c>
     </row>
     <row r="13">
@@ -3652,22 +3676,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3675,14 +3699,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>7.43636031085706</v>
+        <v>5.297823468212948</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3691,10 +3715,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>93.2</v>
+        <v>93.5</v>
       </c>
       <c r="O13" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="P13" t="n">
         <v>4.3</v>
@@ -3714,13 +3738,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>272.173</v>
+        <v>236.178</v>
       </c>
       <c r="V13" t="n">
-        <v>116.427</v>
+        <v>112.119</v>
       </c>
       <c r="W13" t="n">
-        <v>-12.899</v>
+        <v>-18.716</v>
       </c>
     </row>
     <row r="14">
@@ -3739,22 +3763,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3762,14 +3786,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>7.414852572591513</v>
+        <v>5.276743844698761</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3778,10 +3802,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>82.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="O14" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
       <c r="P14" t="n">
         <v>4.7</v>
@@ -3801,13 +3825,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>269.314</v>
+        <v>233.595</v>
       </c>
       <c r="V14" t="n">
-        <v>97.093</v>
+        <v>93.169</v>
       </c>
       <c r="W14" t="n">
-        <v>-12.756</v>
+        <v>-18.531</v>
       </c>
     </row>
     <row r="16">
@@ -3952,22 +3976,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3975,14 +3999,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>7.43636031085706</v>
+        <v>5.297823468212948</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3991,10 +4015,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>93.2</v>
+        <v>93.5</v>
       </c>
       <c r="O18" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4014,13 +4038,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>272.173</v>
+        <v>236.178</v>
       </c>
       <c r="V18" t="n">
-        <v>116.427</v>
+        <v>112.119</v>
       </c>
       <c r="W18" t="n">
-        <v>-12.899</v>
+        <v>-18.716</v>
       </c>
     </row>
     <row r="19">
@@ -4041,12 +4065,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4059,7 +4083,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.8807018120048</v>
+        <v>-12.87810704828809</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4068,7 +4092,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>120.6</v>
+        <v>120.4</v>
       </c>
       <c r="O19" t="n">
         <v>46.3</v>
@@ -4085,19 +4109,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>27.29</v>
+        <v>27.288</v>
       </c>
       <c r="T19" t="n">
-        <v>27.29</v>
+        <v>27.288</v>
       </c>
       <c r="U19" t="n">
-        <v>55.153</v>
+        <v>55.158</v>
       </c>
       <c r="V19" t="n">
-        <v>17.212</v>
+        <v>17.216</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.233</v>
+        <v>-58.228</v>
       </c>
     </row>
     <row r="20">
@@ -4118,22 +4142,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENERY.IS, KUYAS.IS</t>
+          <t>ENERY.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | KUYAS.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4141,14 +4165,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.53% / +15.16% / -3.45% | KUYAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>7.414852572591513</v>
+        <v>5.276743844698761</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4157,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="O20" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4180,13 +4204,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>269.314</v>
+        <v>233.595</v>
       </c>
       <c r="V20" t="n">
-        <v>97.093</v>
+        <v>93.169</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.756</v>
+        <v>-18.531</v>
       </c>
     </row>
     <row r="21">
@@ -4207,12 +4231,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4225,7 +4249,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.79934562068065</v>
+        <v>-12.79674843384874</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4234,7 +4258,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>180.4</v>
+        <v>180.1</v>
       </c>
       <c r="O21" t="n">
         <v>51.6</v>
@@ -4251,19 +4275,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>26.003</v>
+        <v>26.001</v>
       </c>
       <c r="T21" t="n">
-        <v>26.003</v>
+        <v>26.001</v>
       </c>
       <c r="U21" t="n">
-        <v>31.472</v>
+        <v>31.476</v>
       </c>
       <c r="V21" t="n">
-        <v>4.568</v>
+        <v>4.571</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.2</v>
+        <v>-46.196</v>
       </c>
     </row>
     <row r="22">
@@ -4284,22 +4308,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENERY.IS, GUBRF.IS, ISCTR.IS, SASA.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, RALYH.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | GUBRF.IS: 2026-09-14 | ISCTR.IS: 2026-09-15 | SASA.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-16 | ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4307,14 +4331,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | GUBRF.IS: -3.78% / +0.15% / -3.92% | ISCTR.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.20386729215855</v>
+        <v>-10.96548512631721</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4323,10 +4347,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>139.2</v>
+        <v>140.4</v>
       </c>
       <c r="O22" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4340,19 +4364,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.35</v>
+        <v>26.632</v>
       </c>
       <c r="T22" t="n">
-        <v>26.35</v>
+        <v>26.632</v>
       </c>
       <c r="U22" t="n">
-        <v>24.906</v>
+        <v>21.148</v>
       </c>
       <c r="V22" t="n">
-        <v>14.127</v>
+        <v>10.694</v>
       </c>
       <c r="W22" t="n">
-        <v>-40.218</v>
+        <v>-43.976</v>
       </c>
     </row>
     <row r="23">
@@ -4373,22 +4397,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENERY.IS, ISCTR.IS, SASA.IS</t>
+          <t>ENERY.IS, RALYH.IS, SASA.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | ISCTR.IS: 2026-09-10 | SASA.IS: 2026-09-15</t>
+          <t>ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4396,14 +4420,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +17.16% / +17.85% / -0.50% | ISCTR.IS: -3.08% / +1.99% / -3.07% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2509101988227402</v>
+        <v>-1.41384651455515</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4412,10 +4436,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153</v>
+        <v>153.6</v>
       </c>
       <c r="O23" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4435,13 +4459,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>28.007</v>
+        <v>19.346</v>
       </c>
       <c r="V23" t="n">
-        <v>4.547</v>
+        <v>3.328</v>
       </c>
       <c r="W23" t="n">
-        <v>-28.897</v>
+        <v>-28.667</v>
       </c>
     </row>
     <row r="24">
@@ -4462,12 +4486,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4480,7 +4504,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.897983070125099</v>
+        <v>-3.894746413359096</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4489,7 +4513,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114.2</v>
+        <v>114</v>
       </c>
       <c r="O24" t="n">
         <v>50.2</v>
@@ -4506,19 +4530,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>20.432</v>
+        <v>20.43</v>
       </c>
       <c r="T24" t="n">
-        <v>20.432</v>
+        <v>20.43</v>
       </c>
       <c r="U24" t="n">
-        <v>9.692</v>
+        <v>9.696</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.323</v>
+        <v>-3.32</v>
       </c>
       <c r="W24" t="n">
-        <v>-28.168</v>
+        <v>-28.164</v>
       </c>
     </row>
     <row r="25">
@@ -4539,12 +4563,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4566,7 +4590,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4616,12 +4640,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4639,14 +4663,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.51% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.23% / +4.37% / -1.21% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>9.526648711131092</v>
+        <v>6.454016698576837</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4661,7 +4685,7 @@
         <v>42.9</v>
       </c>
       <c r="P26" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4678,13 +4702,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>42.418</v>
+        <v>38.423</v>
       </c>
       <c r="V26" t="n">
-        <v>52.615</v>
+        <v>48.333</v>
       </c>
       <c r="W26" t="n">
-        <v>-17.87</v>
+        <v>-21.865</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -245,8 +245,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W26" headerRowCount="1">
-  <autoFilter ref="A17:W26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W28" headerRowCount="1">
+  <autoFilter ref="A17:W28"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -743,12 +743,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.88475179946702</v>
+        <v>-17.46776500434619</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>64.297</v>
+        <v>55.653</v>
       </c>
       <c r="V3" t="n">
-        <v>18.353</v>
+        <v>12.126</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.082</v>
+        <v>-47.726</v>
       </c>
     </row>
     <row r="4">
@@ -980,12 +980,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-12.88475179946702</v>
+        <v>-17.46776500434619</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>64.297</v>
+        <v>55.653</v>
       </c>
       <c r="V6" t="n">
-        <v>18.353</v>
+        <v>12.126</v>
       </c>
       <c r="W6" t="n">
-        <v>-39.082</v>
+        <v>-47.726</v>
       </c>
     </row>
     <row r="7">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FROTO.IS, SASA.IS</t>
+          <t>FROTO.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FROTO.IS: 2026-09-15 | SASA.IS: 2026-09-16</t>
+          <t>FROTO.IS: 2026-09-15 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FROTO.IS: -1.68% / +0.57% / -2.23% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FROTO.IS: -2.38% / +0.57% / -3.57% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.85755502119113</v>
+        <v>-11.17940424773634</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>22.516</v>
+        <v>22.796</v>
       </c>
       <c r="T7" t="n">
-        <v>22.516</v>
+        <v>22.796</v>
       </c>
       <c r="U7" t="n">
-        <v>48.269</v>
+        <v>47.734</v>
       </c>
       <c r="V7" t="n">
-        <v>21.979</v>
+        <v>21.538</v>
       </c>
       <c r="W7" t="n">
-        <v>-43.086</v>
+        <v>-43.621</v>
       </c>
     </row>
     <row r="8">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-14 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +3.53% / +6.94% / -0.24% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-14.96376449252201</v>
+        <v>-17.18020291733427</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>193.5</v>
+        <v>194</v>
       </c>
       <c r="O8" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>17.749</v>
+        <v>18.479</v>
       </c>
       <c r="T8" t="n">
-        <v>17.749</v>
+        <v>18.479</v>
       </c>
       <c r="U8" t="n">
-        <v>49.055</v>
+        <v>45.17</v>
       </c>
       <c r="V8" t="n">
-        <v>12.902</v>
+        <v>9.959</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.021</v>
+        <v>-32.906</v>
       </c>
     </row>
     <row r="9">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-12.88475179946702</v>
+        <v>-17.46776500434619</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>64.297</v>
+        <v>55.653</v>
       </c>
       <c r="V9" t="n">
-        <v>18.353</v>
+        <v>12.126</v>
       </c>
       <c r="W9" t="n">
-        <v>-39.082</v>
+        <v>-47.726</v>
       </c>
     </row>
     <row r="10">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1563,67 +1563,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>55.72500398673659</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>21.76975999384314</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-8.265155599016705</v>
+        <v>-28.45194989279852</v>
       </c>
       <c r="K13" t="n">
-        <v>8.999673187694079</v>
+        <v>4.847592357308117</v>
       </c>
       <c r="L13" t="n">
-        <v>22.73189287884475</v>
+        <v>29.12044822069533</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>60.9</v>
+        <v>61.9</v>
       </c>
       <c r="O13" t="n">
-        <v>44</v>
+        <v>43.3</v>
       </c>
       <c r="P13" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>25.345</v>
+        <v>25.589</v>
       </c>
       <c r="T13" t="n">
-        <v>25.345</v>
+        <v>25.589</v>
       </c>
       <c r="U13" t="n">
-        <v>88.218</v>
+        <v>93.55200000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>100.84</v>
+        <v>103.043</v>
       </c>
       <c r="W13" t="n">
-        <v>-23.032</v>
+        <v>-32.287</v>
       </c>
     </row>
     <row r="14">
@@ -1637,7 +1625,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1650,67 +1638,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>55.72500398673659</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>21.76975999384314</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-8.265155599016705</v>
+        <v>-28.45194989279852</v>
       </c>
       <c r="K14" t="n">
-        <v>8.999673187694079</v>
+        <v>4.847592357308117</v>
       </c>
       <c r="L14" t="n">
-        <v>22.73189287884475</v>
+        <v>29.12044822069533</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>60.9</v>
+        <v>61.9</v>
       </c>
       <c r="O14" t="n">
-        <v>44</v>
+        <v>43.3</v>
       </c>
       <c r="P14" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>25.345</v>
+        <v>25.589</v>
       </c>
       <c r="T14" t="n">
-        <v>25.345</v>
+        <v>25.589</v>
       </c>
       <c r="U14" t="n">
-        <v>88.218</v>
+        <v>93.55200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>100.84</v>
+        <v>103.043</v>
       </c>
       <c r="W14" t="n">
-        <v>-23.032</v>
+        <v>-32.287</v>
       </c>
     </row>
     <row r="16">
@@ -1865,12 +1841,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1878,14 +1854,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.88475179946702</v>
+        <v>-17.46776500434619</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1917,13 +1893,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>64.297</v>
+        <v>55.653</v>
       </c>
       <c r="V18" t="n">
-        <v>18.353</v>
+        <v>12.126</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.082</v>
+        <v>-47.726</v>
       </c>
     </row>
     <row r="19">
@@ -2113,7 +2089,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-14 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2121,14 +2097,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ENERY.IS: +3.53% / +6.94% / -0.24% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.96376449252201</v>
+        <v>-17.18020291733427</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2113,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>193.5</v>
+        <v>194</v>
       </c>
       <c r="O21" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2154,19 +2130,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>17.749</v>
+        <v>18.479</v>
       </c>
       <c r="T21" t="n">
-        <v>17.749</v>
+        <v>18.479</v>
       </c>
       <c r="U21" t="n">
-        <v>49.055</v>
+        <v>45.17</v>
       </c>
       <c r="V21" t="n">
-        <v>12.902</v>
+        <v>9.959</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.021</v>
+        <v>-32.906</v>
       </c>
     </row>
     <row r="22">
@@ -2197,12 +2173,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FROTO.IS, SASA.IS</t>
+          <t>FROTO.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FROTO.IS: 2026-09-15 | SASA.IS: 2026-09-16</t>
+          <t>FROTO.IS: 2026-09-15 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2210,14 +2186,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FROTO.IS: -1.68% / +0.57% / -2.23% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FROTO.IS: -2.38% / +0.57% / -3.57% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.85755502119113</v>
+        <v>-11.17940424773634</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2243,35 +2219,35 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>22.516</v>
+        <v>22.796</v>
       </c>
       <c r="T22" t="n">
-        <v>22.516</v>
+        <v>22.796</v>
       </c>
       <c r="U22" t="n">
-        <v>48.269</v>
+        <v>47.734</v>
       </c>
       <c r="V22" t="n">
-        <v>21.979</v>
+        <v>21.538</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.086</v>
+        <v>-43.621</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2284,67 +2260,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>55.72500398673659</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>50.58108284302749</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>-8.265155599016705</v>
+        <v>13.3215021172385</v>
       </c>
       <c r="K23" t="n">
-        <v>8.999673187694079</v>
+        <v>-4.400004582905126e-07</v>
       </c>
       <c r="L23" t="n">
-        <v>22.73189287884475</v>
+        <v>5.668150937989602</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>60.9</v>
+        <v>65.8</v>
       </c>
       <c r="O23" t="n">
-        <v>44</v>
+        <v>51.9</v>
       </c>
       <c r="P23" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>25.345</v>
+        <v>7.033</v>
       </c>
       <c r="T23" t="n">
-        <v>25.345</v>
+        <v>7.033</v>
       </c>
       <c r="U23" t="n">
-        <v>88.218</v>
+        <v>85.90600000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>100.84</v>
+        <v>58.898</v>
       </c>
       <c r="W23" t="n">
-        <v>-23.032</v>
+        <v>-1.624</v>
       </c>
     </row>
     <row r="24">
@@ -2355,12 +2319,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2373,67 +2337,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>55.72500398673659</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +18.98% / +22.89% / -0.46% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>26.23135974315276</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-8.265155599016705</v>
+        <v>-4.560732390712419</v>
       </c>
       <c r="K24" t="n">
-        <v>8.999673187694079</v>
+        <v>13.5396968022099</v>
       </c>
       <c r="L24" t="n">
-        <v>22.73189287884475</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N24" t="n">
-        <v>60.9</v>
+        <v>54.1</v>
       </c>
       <c r="O24" t="n">
-        <v>44</v>
+        <v>47.7</v>
       </c>
       <c r="P24" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>25.345</v>
+        <v>11.957</v>
       </c>
       <c r="T24" t="n">
-        <v>25.345</v>
+        <v>11.957</v>
       </c>
       <c r="U24" t="n">
-        <v>88.218</v>
+        <v>33.587</v>
       </c>
       <c r="V24" t="n">
-        <v>100.84</v>
+        <v>38.164</v>
       </c>
       <c r="W24" t="n">
-        <v>-23.032</v>
+        <v>-5.167</v>
       </c>
     </row>
     <row r="25">
@@ -2444,12 +2396,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2462,55 +2414,67 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>50.58108284302749</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>23.02092795860866</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>13.3215021172385</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.400004582905126e-07</v>
+        <v>-7.596583166845939</v>
       </c>
       <c r="L25" t="n">
-        <v>5.668150937989602</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M25" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N25" t="n">
-        <v>65.8</v>
+        <v>177.4</v>
       </c>
       <c r="O25" t="n">
-        <v>51.9</v>
+        <v>48.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>7.033</v>
+        <v>10.762</v>
       </c>
       <c r="T25" t="n">
-        <v>7.033</v>
+        <v>10.762</v>
       </c>
       <c r="U25" t="n">
-        <v>85.90600000000001</v>
+        <v>11.894</v>
       </c>
       <c r="V25" t="n">
-        <v>58.898</v>
+        <v>4.038</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.624</v>
+        <v>-13.494</v>
       </c>
     </row>
     <row r="26">
@@ -2521,12 +2485,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2542,29 +2506,29 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>26.23135974315276</v>
+        <v>21.76975999384314</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>-4.560732390712419</v>
+        <v>-28.45194989279852</v>
       </c>
       <c r="K26" t="n">
-        <v>13.5396968022099</v>
+        <v>4.847592357308117</v>
       </c>
       <c r="L26" t="n">
-        <v>9.344627019167174</v>
+        <v>29.12044822069533</v>
       </c>
       <c r="M26" t="n">
-        <v>66.66666666666666</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>54.1</v>
+        <v>61.9</v>
       </c>
       <c r="O26" t="n">
-        <v>47.7</v>
+        <v>43.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2575,35 +2539,35 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>11.957</v>
+        <v>25.589</v>
       </c>
       <c r="T26" t="n">
-        <v>11.957</v>
+        <v>25.589</v>
       </c>
       <c r="U26" t="n">
-        <v>33.587</v>
+        <v>93.55200000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>38.164</v>
+        <v>103.043</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.167</v>
+        <v>-32.287</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2616,67 +2580,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>23.02092795860866</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>21.76975999384314</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>12.86015270141232</v>
+        <v>-28.45194989279852</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.596583166845939</v>
+        <v>4.847592357308117</v>
       </c>
       <c r="L27" t="n">
-        <v>4.543450519200398</v>
+        <v>29.12044822069533</v>
       </c>
       <c r="M27" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>177.4</v>
+        <v>61.9</v>
       </c>
       <c r="O27" t="n">
-        <v>48.1</v>
+        <v>43.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>10.762</v>
+        <v>25.589</v>
       </c>
       <c r="T27" t="n">
-        <v>10.762</v>
+        <v>25.589</v>
       </c>
       <c r="U27" t="n">
-        <v>11.894</v>
+        <v>93.55200000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>4.038</v>
+        <v>103.043</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.494</v>
+        <v>-32.287</v>
       </c>
     </row>
   </sheetData>
@@ -2698,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2876,12 +2828,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2889,14 +2841,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>5.297823468212948</v>
+        <v>0.680631454059899</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,10 +2857,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>93.5</v>
+        <v>93</v>
       </c>
       <c r="O3" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2919,7 +2871,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>18.106</v>
@@ -2928,13 +2880,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>236.178</v>
+        <v>221.437</v>
       </c>
       <c r="V3" t="n">
-        <v>112.119</v>
+        <v>102.818</v>
       </c>
       <c r="W3" t="n">
-        <v>-18.716</v>
+        <v>-33.457</v>
       </c>
     </row>
     <row r="4">
@@ -2971,7 +2923,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.87810704828809</v>
+        <v>-12.86455291675034</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2997,19 +2949,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>27.288</v>
+        <v>27.276</v>
       </c>
       <c r="T4" t="n">
-        <v>27.288</v>
+        <v>27.276</v>
       </c>
       <c r="U4" t="n">
-        <v>55.158</v>
+        <v>55.182</v>
       </c>
       <c r="V4" t="n">
-        <v>17.216</v>
+        <v>17.234</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.228</v>
+        <v>-58.204</v>
       </c>
     </row>
     <row r="5">
@@ -3038,12 +2990,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3051,14 +3003,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>5.276743844698761</v>
+        <v>0.66047614850544</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3067,10 +3019,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82.7</v>
+        <v>82.2</v>
       </c>
       <c r="O5" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3081,7 +3033,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>21.096</v>
@@ -3090,13 +3042,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>233.595</v>
+        <v>218.968</v>
       </c>
       <c r="V5" t="n">
-        <v>93.169</v>
+        <v>84.699</v>
       </c>
       <c r="W5" t="n">
-        <v>-18.531</v>
+        <v>-33.159</v>
       </c>
     </row>
     <row r="6">
@@ -3138,14 +3090,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.96548512631721</v>
+        <v>-11.39225598849587</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3171,19 +3123,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.632</v>
+        <v>26.984</v>
       </c>
       <c r="T6" t="n">
-        <v>26.632</v>
+        <v>26.984</v>
       </c>
       <c r="U6" t="n">
-        <v>21.148</v>
+        <v>20.568</v>
       </c>
       <c r="V6" t="n">
-        <v>10.694</v>
+        <v>10.163</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.976</v>
+        <v>-44.557</v>
       </c>
     </row>
     <row r="7">
@@ -3220,7 +3172,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-12.87810704828809</v>
+        <v>-12.86455291675034</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3246,19 +3198,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>27.288</v>
+        <v>27.276</v>
       </c>
       <c r="T7" t="n">
-        <v>27.288</v>
+        <v>27.276</v>
       </c>
       <c r="U7" t="n">
-        <v>55.158</v>
+        <v>55.182</v>
       </c>
       <c r="V7" t="n">
-        <v>17.216</v>
+        <v>17.234</v>
       </c>
       <c r="W7" t="n">
-        <v>-58.228</v>
+        <v>-58.204</v>
       </c>
     </row>
     <row r="8">
@@ -3300,14 +3252,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.41384651455515</v>
+        <v>-3.912765034490495</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3339,13 +3291,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>19.346</v>
+        <v>16.321</v>
       </c>
       <c r="V8" t="n">
-        <v>3.328</v>
+        <v>0.709</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.667</v>
+        <v>-31.692</v>
       </c>
     </row>
     <row r="9">
@@ -3457,7 +3409,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.894746413359096</v>
+        <v>-3.87783925866676</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3483,19 +3435,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20.43</v>
+        <v>20.416</v>
       </c>
       <c r="T10" t="n">
-        <v>20.43</v>
+        <v>20.416</v>
       </c>
       <c r="U10" t="n">
-        <v>9.696</v>
+        <v>9.715</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.32</v>
+        <v>-3.303</v>
       </c>
       <c r="W10" t="n">
-        <v>-28.164</v>
+        <v>-28.145</v>
       </c>
     </row>
     <row r="11">
@@ -3532,7 +3484,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.79674843384874</v>
+        <v>-12.78318164481098</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3558,19 +3510,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>26.001</v>
+        <v>25.989</v>
       </c>
       <c r="T11" t="n">
-        <v>26.001</v>
+        <v>25.989</v>
       </c>
       <c r="U11" t="n">
-        <v>31.476</v>
+        <v>31.497</v>
       </c>
       <c r="V11" t="n">
-        <v>4.571</v>
+        <v>4.588</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.196</v>
+        <v>-46.176</v>
       </c>
     </row>
     <row r="12">
@@ -3604,7 +3556,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -3612,14 +3564,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.23% / +4.37% / -1.21% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>6.454016698576837</v>
+        <v>8.086968470135879</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3628,13 +3580,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
       <c r="O12" t="n">
-        <v>42.9</v>
+        <v>42.4</v>
       </c>
       <c r="P12" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3651,13 +3603,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>38.423</v>
+        <v>40.546</v>
       </c>
       <c r="V12" t="n">
-        <v>48.333</v>
+        <v>50.609</v>
       </c>
       <c r="W12" t="n">
-        <v>-21.865</v>
+        <v>-19.742</v>
       </c>
     </row>
     <row r="13">
@@ -3671,7 +3623,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3684,67 +3636,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>86.93022416585528</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>8.530010255723974</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>1.0581145912685</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K13" t="n">
-        <v>5.297823468212948</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L13" t="n">
-        <v>28.4081875</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>93.5</v>
+        <v>35.2</v>
       </c>
       <c r="O13" t="n">
-        <v>44.5</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>18.106</v>
+        <v>8.083</v>
       </c>
       <c r="T13" t="n">
-        <v>18.106</v>
+        <v>7.916</v>
       </c>
       <c r="U13" t="n">
-        <v>236.178</v>
+        <v>6.923</v>
       </c>
       <c r="V13" t="n">
-        <v>112.119</v>
+        <v>4.916</v>
       </c>
       <c r="W13" t="n">
-        <v>-18.716</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="14">
@@ -3758,7 +3698,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3771,67 +3711,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>83.80706321463933</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>32.90971238010212</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-0.4421645194713886</v>
+        <v>3.175499702073514</v>
       </c>
       <c r="K14" t="n">
-        <v>5.276743844698761</v>
+        <v>2.680368121576793</v>
       </c>
       <c r="L14" t="n">
-        <v>32.3216328125</v>
+        <v>18.99889339779883</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>82.7</v>
+        <v>44</v>
       </c>
       <c r="O14" t="n">
-        <v>42.6</v>
+        <v>51.1</v>
       </c>
       <c r="P14" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>21.096</v>
+        <v>18.999</v>
       </c>
       <c r="T14" t="n">
-        <v>21.096</v>
+        <v>16.472</v>
       </c>
       <c r="U14" t="n">
-        <v>233.595</v>
+        <v>25.295</v>
       </c>
       <c r="V14" t="n">
-        <v>93.169</v>
+        <v>17.703</v>
       </c>
       <c r="W14" t="n">
-        <v>-18.531</v>
+        <v>-15.006</v>
       </c>
     </row>
     <row r="16">
@@ -3961,12 +3889,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | LAST_3_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 | 2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3986,12 +3914,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3999,14 +3927,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>5.297823468212948</v>
+        <v>0.680631454059899</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4015,10 +3943,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>93.5</v>
+        <v>93</v>
       </c>
       <c r="O18" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4029,7 +3957,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>18.106</v>
@@ -4038,13 +3966,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>236.178</v>
+        <v>221.437</v>
       </c>
       <c r="V18" t="n">
-        <v>112.119</v>
+        <v>102.818</v>
       </c>
       <c r="W18" t="n">
-        <v>-18.716</v>
+        <v>-33.457</v>
       </c>
     </row>
     <row r="19">
@@ -4083,7 +4011,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.87810704828809</v>
+        <v>-12.86455291675034</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4109,25 +4037,25 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>27.288</v>
+        <v>27.276</v>
       </c>
       <c r="T19" t="n">
-        <v>27.288</v>
+        <v>27.276</v>
       </c>
       <c r="U19" t="n">
-        <v>55.158</v>
+        <v>55.182</v>
       </c>
       <c r="V19" t="n">
-        <v>17.216</v>
+        <v>17.234</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.228</v>
+        <v>-58.204</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | LAST_3_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4152,12 +4080,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENERY.IS, SASA.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04 | SASA.IS: 2026-09-16</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4165,14 +4093,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +14.30% / +19.53% / -3.45% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>5.276743844698761</v>
+        <v>0.66047614850544</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4181,10 +4109,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82.7</v>
+        <v>82.2</v>
       </c>
       <c r="O20" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4195,7 +4123,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>21.096</v>
@@ -4204,13 +4132,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>233.595</v>
+        <v>218.968</v>
       </c>
       <c r="V20" t="n">
-        <v>93.169</v>
+        <v>84.699</v>
       </c>
       <c r="W20" t="n">
-        <v>-18.531</v>
+        <v>-33.159</v>
       </c>
     </row>
     <row r="21">
@@ -4249,7 +4177,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.79674843384874</v>
+        <v>-12.78318164481098</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4275,19 +4203,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>26.001</v>
+        <v>25.989</v>
       </c>
       <c r="T21" t="n">
-        <v>26.001</v>
+        <v>25.989</v>
       </c>
       <c r="U21" t="n">
-        <v>31.476</v>
+        <v>31.497</v>
       </c>
       <c r="V21" t="n">
-        <v>4.571</v>
+        <v>4.588</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.196</v>
+        <v>-46.176</v>
       </c>
     </row>
     <row r="22">
@@ -4331,14 +4259,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.96548512631721</v>
+        <v>-11.39225598849587</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4364,19 +4292,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.632</v>
+        <v>26.984</v>
       </c>
       <c r="T22" t="n">
-        <v>26.632</v>
+        <v>26.984</v>
       </c>
       <c r="U22" t="n">
-        <v>21.148</v>
+        <v>20.568</v>
       </c>
       <c r="V22" t="n">
-        <v>10.694</v>
+        <v>10.163</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.976</v>
+        <v>-44.557</v>
       </c>
     </row>
     <row r="23">
@@ -4420,14 +4348,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +16.93% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.41384651455515</v>
+        <v>-3.912765034490495</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4459,13 +4387,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>19.346</v>
+        <v>16.321</v>
       </c>
       <c r="V23" t="n">
-        <v>3.328</v>
+        <v>0.709</v>
       </c>
       <c r="W23" t="n">
-        <v>-28.667</v>
+        <v>-31.692</v>
       </c>
     </row>
     <row r="24">
@@ -4504,7 +4432,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.894746413359096</v>
+        <v>-3.87783925866676</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4530,35 +4458,35 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>20.43</v>
+        <v>20.416</v>
       </c>
       <c r="T24" t="n">
-        <v>20.43</v>
+        <v>20.416</v>
       </c>
       <c r="U24" t="n">
-        <v>9.696</v>
+        <v>9.715</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.32</v>
+        <v>-3.303</v>
       </c>
       <c r="W24" t="n">
-        <v>-28.164</v>
+        <v>-28.145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4574,29 +4502,29 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>28.40086810394897</v>
+        <v>32.90971238010212</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>15.38514121842653</v>
+        <v>3.175499702073514</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.616392554049999</v>
+        <v>2.680368121576793</v>
       </c>
       <c r="L25" t="n">
-        <v>5.127814043936619</v>
+        <v>18.99889339779883</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>74.40000000000001</v>
+        <v>44</v>
       </c>
       <c r="O25" t="n">
-        <v>49.3</v>
+        <v>51.1</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4607,25 +4535,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>13.28</v>
+        <v>18.999</v>
       </c>
       <c r="T25" t="n">
-        <v>13.28</v>
+        <v>16.472</v>
       </c>
       <c r="U25" t="n">
-        <v>7.136</v>
+        <v>25.295</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.962</v>
+        <v>17.703</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.407</v>
+        <v>-15.006</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4635,7 +4563,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4648,67 +4576,221 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-15 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>6.880672511445463</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.23% / +4.37% / -1.21% | TKFEN.IS: +15.64% / +31.83% / -0.56%</t>
-        </is>
-      </c>
+        <v>28.40086810394897</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>-18.9000927288166</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K26" t="n">
-        <v>6.454016698576837</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L26" t="n">
-        <v>31.31195090134997</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M26" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>48</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>42.9</v>
+        <v>49.3</v>
       </c>
       <c r="P26" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="T26" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7.136</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.962</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-16.407</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>8.530010255723974</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0.8142516931666233</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.846414277792909</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9.181211458048665</v>
+      </c>
+      <c r="M27" t="n">
+        <v>72.22222222222221</v>
+      </c>
+      <c r="N27" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8.083</v>
+      </c>
+      <c r="T27" t="n">
+        <v>7.916</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6.923</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4.916</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-4.88</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>6.880672511445463</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>-18.9000927288166</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8.086968470135879</v>
+      </c>
+      <c r="L28" t="n">
+        <v>31.31195090134997</v>
+      </c>
+      <c r="M28" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="N28" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="O28" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>ACIK</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>2</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>28.439</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>28.439</v>
       </c>
-      <c r="U26" t="n">
-        <v>38.423</v>
-      </c>
-      <c r="V26" t="n">
-        <v>48.333</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-21.865</v>
+      <c r="U28" t="n">
+        <v>40.546</v>
+      </c>
+      <c r="V28" t="n">
+        <v>50.609</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-19.742</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.46776500434619</v>
+        <v>-16.9418454562453</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>55.653</v>
+        <v>56.645</v>
       </c>
       <c r="V3" t="n">
-        <v>12.126</v>
+        <v>12.841</v>
       </c>
       <c r="W3" t="n">
-        <v>-47.726</v>
+        <v>-46.734</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.46776500434619</v>
+        <v>-16.9418454562453</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>55.653</v>
+        <v>56.645</v>
       </c>
       <c r="V6" t="n">
-        <v>12.126</v>
+        <v>12.841</v>
       </c>
       <c r="W6" t="n">
-        <v>-47.726</v>
+        <v>-46.734</v>
       </c>
     </row>
     <row r="7">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FROTO.IS, TKFEN.IS</t>
+          <t>SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FROTO.IS: 2026-09-15 | TKFEN.IS: 2026-09-16</t>
+          <t>SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FROTO.IS: -2.38% / +0.57% / -3.57% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.17940424773634</v>
+        <v>-11.94955908225268</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>135.5</v>
+        <v>136</v>
       </c>
       <c r="O7" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>22.796</v>
+        <v>23.465</v>
       </c>
       <c r="T7" t="n">
-        <v>22.796</v>
+        <v>23.465</v>
       </c>
       <c r="U7" t="n">
-        <v>47.734</v>
+        <v>46.453</v>
       </c>
       <c r="V7" t="n">
-        <v>21.538</v>
+        <v>20.484</v>
       </c>
       <c r="W7" t="n">
-        <v>-43.621</v>
+        <v>-44.902</v>
       </c>
     </row>
     <row r="8">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.46776500434619</v>
+        <v>-16.9418454562453</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>55.653</v>
+        <v>56.645</v>
       </c>
       <c r="V9" t="n">
-        <v>12.126</v>
+        <v>12.841</v>
       </c>
       <c r="W9" t="n">
-        <v>-47.726</v>
+        <v>-46.734</v>
       </c>
     </row>
     <row r="10">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +7.67% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.46776500434619</v>
+        <v>-16.9418454562453</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1893,13 +1893,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>55.653</v>
+        <v>56.645</v>
       </c>
       <c r="V18" t="n">
-        <v>12.126</v>
+        <v>12.841</v>
       </c>
       <c r="W18" t="n">
-        <v>-47.726</v>
+        <v>-46.734</v>
       </c>
     </row>
     <row r="19">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FROTO.IS, TKFEN.IS</t>
+          <t>SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FROTO.IS: 2026-09-15 | TKFEN.IS: 2026-09-16</t>
+          <t>SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2186,14 +2186,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FROTO.IS: -2.38% / +0.57% / -3.57% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.17940424773634</v>
+        <v>-11.94955908225268</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2202,10 +2202,10 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>135.5</v>
+        <v>136</v>
       </c>
       <c r="O22" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -2219,19 +2219,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>22.796</v>
+        <v>23.465</v>
       </c>
       <c r="T22" t="n">
-        <v>22.796</v>
+        <v>23.465</v>
       </c>
       <c r="U22" t="n">
-        <v>47.734</v>
+        <v>46.453</v>
       </c>
       <c r="V22" t="n">
-        <v>21.538</v>
+        <v>20.484</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.621</v>
+        <v>-44.902</v>
       </c>
     </row>
     <row r="23">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
+          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.680631454059899</v>
+        <v>1.310999776290278</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2880,13 +2880,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>221.437</v>
+        <v>223.449</v>
       </c>
       <c r="V3" t="n">
-        <v>102.818</v>
+        <v>104.088</v>
       </c>
       <c r="W3" t="n">
-        <v>-33.457</v>
+        <v>-31.444</v>
       </c>
     </row>
     <row r="4">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
+          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.66047614850544</v>
+        <v>1.290718276988678</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3042,13 +3042,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>218.968</v>
+        <v>220.965</v>
       </c>
       <c r="V5" t="n">
-        <v>84.699</v>
+        <v>85.85599999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-33.159</v>
+        <v>-31.162</v>
       </c>
     </row>
     <row r="6">
@@ -3090,14 +3090,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.39225598849587</v>
+        <v>-11.3882195038402</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3123,19 +3123,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.984</v>
+        <v>26.98</v>
       </c>
       <c r="T6" t="n">
-        <v>26.984</v>
+        <v>26.98</v>
       </c>
       <c r="U6" t="n">
-        <v>20.568</v>
+        <v>20.573</v>
       </c>
       <c r="V6" t="n">
-        <v>10.163</v>
+        <v>10.168</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.557</v>
+        <v>-44.551</v>
       </c>
     </row>
     <row r="7">
@@ -3252,14 +3252,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.912765034490495</v>
+        <v>-3.573665022609962</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3291,13 +3291,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>16.321</v>
+        <v>16.731</v>
       </c>
       <c r="V8" t="n">
-        <v>0.709</v>
+        <v>1.064</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.692</v>
+        <v>-31.282</v>
       </c>
     </row>
     <row r="9">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.086968470135879</v>
+        <v>7.469112049199844</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3603,13 +3603,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>40.546</v>
+        <v>39.743</v>
       </c>
       <c r="V12" t="n">
-        <v>50.609</v>
+        <v>49.748</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.742</v>
+        <v>-20.545</v>
       </c>
     </row>
     <row r="13">
@@ -3927,14 +3927,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
+          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.680631454059899</v>
+        <v>1.310999776290278</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3966,13 +3966,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>221.437</v>
+        <v>223.449</v>
       </c>
       <c r="V18" t="n">
-        <v>102.818</v>
+        <v>104.088</v>
       </c>
       <c r="W18" t="n">
-        <v>-33.457</v>
+        <v>-31.444</v>
       </c>
     </row>
     <row r="19">
@@ -4093,14 +4093,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +5.01% / +19.53% / -3.45%</t>
+          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.66047614850544</v>
+        <v>1.290718276988678</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4132,13 +4132,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>218.968</v>
+        <v>220.965</v>
       </c>
       <c r="V20" t="n">
-        <v>84.699</v>
+        <v>85.85599999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-33.159</v>
+        <v>-31.162</v>
       </c>
     </row>
     <row r="21">
@@ -4259,14 +4259,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.39225598849587</v>
+        <v>-11.3882195038402</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4292,19 +4292,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.984</v>
+        <v>26.98</v>
       </c>
       <c r="T22" t="n">
-        <v>26.984</v>
+        <v>26.98</v>
       </c>
       <c r="U22" t="n">
-        <v>20.568</v>
+        <v>20.573</v>
       </c>
       <c r="V22" t="n">
-        <v>10.163</v>
+        <v>10.168</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.557</v>
+        <v>-44.551</v>
       </c>
     </row>
     <row r="23">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +7.43% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.912765034490495</v>
+        <v>-3.573665022609962</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4387,13 +4387,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>16.321</v>
+        <v>16.731</v>
       </c>
       <c r="V23" t="n">
-        <v>0.709</v>
+        <v>1.064</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.692</v>
+        <v>-31.282</v>
       </c>
     </row>
     <row r="24">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +22.46% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K28" t="n">
-        <v>8.086968470135879</v>
+        <v>7.469112049199844</v>
       </c>
       <c r="L28" t="n">
         <v>31.31195090134997</v>
@@ -4784,13 +4784,13 @@
         <v>28.439</v>
       </c>
       <c r="U28" t="n">
-        <v>40.546</v>
+        <v>39.743</v>
       </c>
       <c r="V28" t="n">
-        <v>50.609</v>
+        <v>49.748</v>
       </c>
       <c r="W28" t="n">
-        <v>-19.742</v>
+        <v>-20.545</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.9418454562453</v>
+        <v>-16.26566475787422</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>56.645</v>
+        <v>57.92</v>
       </c>
       <c r="V3" t="n">
-        <v>12.841</v>
+        <v>13.759</v>
       </c>
       <c r="W3" t="n">
-        <v>-46.734</v>
+        <v>-45.459</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.9418454562453</v>
+        <v>-16.26566475787422</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>56.645</v>
+        <v>57.92</v>
       </c>
       <c r="V6" t="n">
-        <v>12.841</v>
+        <v>13.759</v>
       </c>
       <c r="W6" t="n">
-        <v>-46.734</v>
+        <v>-45.459</v>
       </c>
     </row>
     <row r="7">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.9418454562453</v>
+        <v>-16.26566475787422</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>56.645</v>
+        <v>57.92</v>
       </c>
       <c r="V9" t="n">
-        <v>12.841</v>
+        <v>13.759</v>
       </c>
       <c r="W9" t="n">
-        <v>-46.734</v>
+        <v>-45.459</v>
       </c>
     </row>
     <row r="10">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +8.97% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.9418454562453</v>
+        <v>-16.26566475787422</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1893,13 +1893,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>56.645</v>
+        <v>57.92</v>
       </c>
       <c r="V18" t="n">
-        <v>12.841</v>
+        <v>13.759</v>
       </c>
       <c r="W18" t="n">
-        <v>-46.734</v>
+        <v>-45.459</v>
       </c>
     </row>
     <row r="19">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
+          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>1.310999776290278</v>
+        <v>1.991644185925834</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2880,13 +2880,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>223.449</v>
+        <v>225.622</v>
       </c>
       <c r="V3" t="n">
-        <v>104.088</v>
+        <v>105.459</v>
       </c>
       <c r="W3" t="n">
-        <v>-31.444</v>
+        <v>-29.271</v>
       </c>
     </row>
     <row r="4">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
+          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>1.290718276988678</v>
+        <v>1.971226428082229</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3042,13 +3042,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>220.965</v>
+        <v>223.121</v>
       </c>
       <c r="V5" t="n">
-        <v>85.85599999999999</v>
+        <v>87.104</v>
       </c>
       <c r="W5" t="n">
-        <v>-31.162</v>
+        <v>-29.006</v>
       </c>
     </row>
     <row r="6">
@@ -3090,14 +3090,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.3882195038402</v>
+        <v>-10.6335296089389</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3123,19 +3123,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.98</v>
+        <v>26.359</v>
       </c>
       <c r="T6" t="n">
-        <v>26.98</v>
+        <v>26.359</v>
       </c>
       <c r="U6" t="n">
-        <v>20.573</v>
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>10.168</v>
+        <v>11.106</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.551</v>
+        <v>-43.524</v>
       </c>
     </row>
     <row r="7">
@@ -3252,14 +3252,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.573665022609962</v>
+        <v>-3.20752087424826</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3291,13 +3291,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>16.731</v>
+        <v>17.174</v>
       </c>
       <c r="V8" t="n">
-        <v>1.064</v>
+        <v>1.448</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.282</v>
+        <v>-30.839</v>
       </c>
     </row>
     <row r="9">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>7.469112049199844</v>
+        <v>8.841091412127099</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3603,13 +3603,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>39.743</v>
+        <v>41.527</v>
       </c>
       <c r="V12" t="n">
-        <v>49.748</v>
+        <v>51.66</v>
       </c>
       <c r="W12" t="n">
-        <v>-20.545</v>
+        <v>-18.761</v>
       </c>
     </row>
     <row r="13">
@@ -3927,14 +3927,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
+          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>1.310999776290278</v>
+        <v>1.991644185925834</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3966,13 +3966,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>223.449</v>
+        <v>225.622</v>
       </c>
       <c r="V18" t="n">
-        <v>104.088</v>
+        <v>105.459</v>
       </c>
       <c r="W18" t="n">
-        <v>-31.444</v>
+        <v>-29.271</v>
       </c>
     </row>
     <row r="19">
@@ -4093,14 +4093,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.27% / +19.52% / -3.45%</t>
+          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>1.290718276988678</v>
+        <v>1.971226428082229</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4132,13 +4132,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>220.965</v>
+        <v>223.121</v>
       </c>
       <c r="V20" t="n">
-        <v>85.85599999999999</v>
+        <v>87.104</v>
       </c>
       <c r="W20" t="n">
-        <v>-31.162</v>
+        <v>-29.006</v>
       </c>
     </row>
     <row r="21">
@@ -4259,14 +4259,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.3882195038402</v>
+        <v>-10.6335296089389</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4292,19 +4292,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.98</v>
+        <v>26.359</v>
       </c>
       <c r="T22" t="n">
-        <v>26.98</v>
+        <v>26.359</v>
       </c>
       <c r="U22" t="n">
-        <v>20.573</v>
+        <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>10.168</v>
+        <v>11.106</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.551</v>
+        <v>-43.524</v>
       </c>
     </row>
     <row r="23">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENERY.IS: +8.72% / +22.31% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.573665022609962</v>
+        <v>-3.20752087424826</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4387,13 +4387,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>16.731</v>
+        <v>17.174</v>
       </c>
       <c r="V23" t="n">
-        <v>1.064</v>
+        <v>1.448</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.282</v>
+        <v>-30.839</v>
       </c>
     </row>
     <row r="24">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +21.24% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K28" t="n">
-        <v>7.469112049199844</v>
+        <v>8.841091412127099</v>
       </c>
       <c r="L28" t="n">
         <v>31.31195090134997</v>
@@ -4784,13 +4784,13 @@
         <v>28.439</v>
       </c>
       <c r="U28" t="n">
-        <v>39.743</v>
+        <v>41.527</v>
       </c>
       <c r="V28" t="n">
-        <v>49.748</v>
+        <v>51.66</v>
       </c>
       <c r="W28" t="n">
-        <v>-20.545</v>
+        <v>-18.761</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,7 +573,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -733,37 +733,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.26566475787422</v>
+        <v>-17.24387074023273</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,21 +760,21 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="O3" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="P3" t="n">
         <v>6.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>23.832</v>
@@ -795,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>57.92</v>
+        <v>47.77</v>
       </c>
       <c r="V3" t="n">
-        <v>13.759</v>
+        <v>12.431</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.459</v>
+        <v>-44.786</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +835,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +910,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,37 +958,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.26566475787422</v>
+        <v>-17.24387074023273</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,21 +985,21 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="O6" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="P6" t="n">
         <v>6.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>23.832</v>
@@ -1032,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>57.92</v>
+        <v>47.77</v>
       </c>
       <c r="V6" t="n">
-        <v>13.759</v>
+        <v>12.431</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.459</v>
+        <v>-44.786</v>
       </c>
     </row>
     <row r="7">
@@ -1057,37 +1033,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SASA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>59.2010679593864</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.94955908225268</v>
+        <v>-11.78873025291825</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,36 +1060,36 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>136</v>
+        <v>135.7</v>
       </c>
       <c r="O7" t="n">
-        <v>46.2</v>
+        <v>46.6</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>23.465</v>
+        <v>23.45</v>
       </c>
       <c r="T7" t="n">
-        <v>23.465</v>
+        <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>46.453</v>
+        <v>38.261</v>
       </c>
       <c r="V7" t="n">
-        <v>20.484</v>
+        <v>20.704</v>
       </c>
       <c r="W7" t="n">
-        <v>-44.902</v>
+        <v>-42.061</v>
       </c>
     </row>
     <row r="8">
@@ -1144,37 +1108,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>60.64599942530686</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-17.18020291733427</v>
+        <v>-19.71698998738825</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,36 +1135,36 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>194</v>
+        <v>193.6</v>
       </c>
       <c r="O8" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>18.479</v>
+        <v>20.976</v>
       </c>
       <c r="T8" t="n">
-        <v>18.479</v>
+        <v>20.976</v>
       </c>
       <c r="U8" t="n">
-        <v>45.17</v>
+        <v>39.858</v>
       </c>
       <c r="V8" t="n">
-        <v>9.959</v>
+        <v>6.591</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.906</v>
+        <v>-37.123</v>
       </c>
     </row>
     <row r="9">
@@ -1231,37 +1183,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.26566475787422</v>
+        <v>-17.24387074023273</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,21 +1210,21 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="O9" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="P9" t="n">
         <v>6.7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>23.832</v>
@@ -1293,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>57.92</v>
+        <v>47.77</v>
       </c>
       <c r="V9" t="n">
-        <v>13.759</v>
+        <v>12.431</v>
       </c>
       <c r="W9" t="n">
-        <v>-45.459</v>
+        <v>-44.786</v>
       </c>
     </row>
     <row r="10">
@@ -1318,22 +1258,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TKFEN.IS</t>
+          <t>ASELS.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TKFEN.IS: 2026-09-16</t>
+          <t>ASELS.IS: 2026-09-17 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1341,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.71% / +4.81% / -0.85%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.596583166845939</v>
+        <v>-6.730117133477787</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,36 +1297,36 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>177.4</v>
+        <v>177.6</v>
       </c>
       <c r="O10" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="P10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
       <c r="S10" t="n">
-        <v>10.762</v>
+        <v>10.759</v>
       </c>
       <c r="T10" t="n">
-        <v>10.762</v>
+        <v>10.759</v>
       </c>
       <c r="U10" t="n">
-        <v>11.894</v>
+        <v>12.943</v>
       </c>
       <c r="V10" t="n">
-        <v>4.038</v>
+        <v>5.014</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.494</v>
+        <v>-12.445</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1345,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1372,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1475,45 +1415,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>26.23135974315276</v>
+        <v>11.25425383347203</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-4.560732390712419</v>
+        <v>-15.88441753735412</v>
       </c>
       <c r="K12" t="n">
-        <v>13.5396968022099</v>
+        <v>13.53969230415128</v>
       </c>
       <c r="L12" t="n">
-        <v>9.344627019167174</v>
+        <v>20.94951282095601</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666666</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>54.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>47.7</v>
+        <v>45.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1524,19 +1464,19 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>11.957</v>
+        <v>24.573</v>
       </c>
       <c r="T12" t="n">
-        <v>11.957</v>
+        <v>24.573</v>
       </c>
       <c r="U12" t="n">
-        <v>33.587</v>
+        <v>5.724</v>
       </c>
       <c r="V12" t="n">
-        <v>38.164</v>
+        <v>18.367</v>
       </c>
       <c r="W12" t="n">
-        <v>-5.167</v>
+        <v>-17.728</v>
       </c>
     </row>
     <row r="13">
@@ -1555,12 +1495,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1582,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="O13" t="n">
         <v>43.3</v>
@@ -1630,12 +1570,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1657,7 +1597,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="O14" t="n">
         <v>43.3</v>
@@ -1831,37 +1771,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +10.64% / +22.89% / -0.46% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.26566475787422</v>
+        <v>-17.24387074023273</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1870,21 +1798,21 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="O18" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="P18" t="n">
         <v>6.7</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>23.832</v>
@@ -1893,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>57.92</v>
+        <v>47.77</v>
       </c>
       <c r="V18" t="n">
-        <v>13.759</v>
+        <v>12.431</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.459</v>
+        <v>-44.786</v>
       </c>
     </row>
     <row r="19">
@@ -1920,12 +1848,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1947,7 +1875,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1997,12 +1925,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2024,7 +1952,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2074,37 +2002,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ENERY.IS, SASA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>60.64599942530686</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-17.18020291733427</v>
+        <v>-19.71698998738825</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2113,36 +2029,36 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>194</v>
+        <v>193.6</v>
       </c>
       <c r="O21" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>18.479</v>
+        <v>20.976</v>
       </c>
       <c r="T21" t="n">
-        <v>18.479</v>
+        <v>20.976</v>
       </c>
       <c r="U21" t="n">
-        <v>45.17</v>
+        <v>39.858</v>
       </c>
       <c r="V21" t="n">
-        <v>9.959</v>
+        <v>6.591</v>
       </c>
       <c r="W21" t="n">
-        <v>-32.906</v>
+        <v>-37.123</v>
       </c>
     </row>
     <row r="22">
@@ -2163,37 +2079,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SASA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SASA.IS: 2026-09-16 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>59.2010679593864</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.94955908225268</v>
+        <v>-11.78873025291825</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2202,36 +2106,36 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>136</v>
+        <v>135.7</v>
       </c>
       <c r="O22" t="n">
-        <v>46.2</v>
+        <v>46.6</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>23.465</v>
+        <v>23.45</v>
       </c>
       <c r="T22" t="n">
-        <v>23.465</v>
+        <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>46.453</v>
+        <v>38.261</v>
       </c>
       <c r="V22" t="n">
-        <v>20.484</v>
+        <v>20.704</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.902</v>
+        <v>-42.061</v>
       </c>
     </row>
     <row r="23">
@@ -2252,12 +2156,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2279,7 +2183,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="O23" t="n">
         <v>51.9</v>
@@ -2314,84 +2218,96 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ASELS.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ASELS.IS: 2026-09-17 | TKFEN.IS: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>26.23135974315276</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>23.02092795860866</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.71% / +4.81% / -0.85%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>-4.560732390712419</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K24" t="n">
-        <v>13.5396968022099</v>
+        <v>-6.730117133477787</v>
       </c>
       <c r="L24" t="n">
-        <v>9.344627019167174</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M24" t="n">
-        <v>66.66666666666666</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N24" t="n">
-        <v>54.1</v>
+        <v>177.6</v>
       </c>
       <c r="O24" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>11.957</v>
+        <v>10.759</v>
       </c>
       <c r="T24" t="n">
-        <v>11.957</v>
+        <v>10.759</v>
       </c>
       <c r="U24" t="n">
-        <v>33.587</v>
+        <v>12.943</v>
       </c>
       <c r="V24" t="n">
-        <v>38.164</v>
+        <v>5.014</v>
       </c>
       <c r="W24" t="n">
-        <v>-5.167</v>
+        <v>-12.445</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2401,80 +2317,68 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>23.02092795860866</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>21.76975999384314</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>12.86015270141232</v>
+        <v>-28.45194989279852</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.596583166845939</v>
+        <v>4.847592357308117</v>
       </c>
       <c r="L25" t="n">
-        <v>4.543450519200398</v>
+        <v>29.12044822069533</v>
       </c>
       <c r="M25" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>177.4</v>
+        <v>61.8</v>
       </c>
       <c r="O25" t="n">
-        <v>48.1</v>
+        <v>43.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>10.762</v>
+        <v>25.589</v>
       </c>
       <c r="T25" t="n">
-        <v>10.762</v>
+        <v>25.589</v>
       </c>
       <c r="U25" t="n">
-        <v>11.894</v>
+        <v>93.55200000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>4.038</v>
+        <v>103.043</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.494</v>
+        <v>-32.287</v>
       </c>
     </row>
     <row r="26">
@@ -2485,22 +2389,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2522,7 +2426,7 @@
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="O26" t="n">
         <v>43.3</v>
@@ -2562,50 +2466,50 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>21.76975999384314</v>
+        <v>11.25425383347203</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>-28.45194989279852</v>
+        <v>-15.88441753735412</v>
       </c>
       <c r="K27" t="n">
-        <v>4.847592357308117</v>
+        <v>13.53969230415128</v>
       </c>
       <c r="L27" t="n">
-        <v>29.12044822069533</v>
+        <v>20.94951282095601</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N27" t="n">
-        <v>61.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="P27" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2616,19 +2520,19 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>25.589</v>
+        <v>24.573</v>
       </c>
       <c r="T27" t="n">
-        <v>25.589</v>
+        <v>24.573</v>
       </c>
       <c r="U27" t="n">
-        <v>93.55200000000001</v>
+        <v>5.724</v>
       </c>
       <c r="V27" t="n">
-        <v>103.043</v>
+        <v>18.367</v>
       </c>
       <c r="W27" t="n">
-        <v>-32.287</v>
+        <v>-17.728</v>
       </c>
     </row>
   </sheetData>
@@ -2818,37 +2722,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ENERY.IS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-04</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>86.93022416585528</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>1.991644185925834</v>
+        <v>-1.593184911882817</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2857,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="O3" t="n">
         <v>44.7</v>
@@ -2867,11 +2759,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>18.106</v>
@@ -2880,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>225.622</v>
+        <v>197.173</v>
       </c>
       <c r="V3" t="n">
-        <v>105.459</v>
+        <v>98.238</v>
       </c>
       <c r="W3" t="n">
-        <v>-29.271</v>
+        <v>-38.513</v>
       </c>
     </row>
     <row r="4">
@@ -2905,12 +2797,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2932,7 +2824,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>120.4</v>
+        <v>120.1</v>
       </c>
       <c r="O4" t="n">
         <v>46.3</v>
@@ -2980,37 +2872,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ENERY.IS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-04</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>83.80706321463933</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>1.971226428082229</v>
+        <v>-1.612885021011035</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3019,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="O5" t="n">
         <v>42.9</v>
@@ -3029,11 +2909,11 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>21.096</v>
@@ -3042,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>223.121</v>
+        <v>194.89</v>
       </c>
       <c r="V5" t="n">
-        <v>87.104</v>
+        <v>80.52800000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-29.006</v>
+        <v>-38.178</v>
       </c>
     </row>
     <row r="6">
@@ -3067,22 +2947,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, RALYH.IS, SASA.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, FROTO.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-16 | ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-17 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3090,14 +2970,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.6335296089389</v>
+        <v>-14.69422345180439</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3106,13 +2986,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>140.4</v>
+        <v>142.1</v>
       </c>
       <c r="O6" t="n">
-        <v>42.2</v>
+        <v>41.6</v>
       </c>
       <c r="P6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3123,19 +3003,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.359</v>
+        <v>29.705</v>
       </c>
       <c r="T6" t="n">
-        <v>26.359</v>
+        <v>29.705</v>
       </c>
       <c r="U6" t="n">
-        <v>21.6</v>
+        <v>16.075</v>
       </c>
       <c r="V6" t="n">
-        <v>11.106</v>
+        <v>6.058</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.524</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="7">
@@ -3154,12 +3034,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3181,7 +3061,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>120.4</v>
+        <v>120.1</v>
       </c>
       <c r="O7" t="n">
         <v>46.3</v>
@@ -3229,37 +3109,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ENERY.IS, RALYH.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>48.21914524341393</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.20752087424826</v>
+        <v>-8.594955468590582</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3268,7 +3136,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.6</v>
+        <v>153.3</v>
       </c>
       <c r="O8" t="n">
         <v>41.7</v>
@@ -3278,26 +3146,26 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>21.943</v>
+        <v>25.241</v>
       </c>
       <c r="T8" t="n">
-        <v>21.943</v>
+        <v>25.241</v>
       </c>
       <c r="U8" t="n">
-        <v>17.174</v>
+        <v>7.653</v>
       </c>
       <c r="V8" t="n">
-        <v>1.448</v>
+        <v>-4.198</v>
       </c>
       <c r="W8" t="n">
-        <v>-30.839</v>
+        <v>-36.348</v>
       </c>
     </row>
     <row r="9">
@@ -3316,12 +3184,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3343,7 +3211,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3391,12 +3259,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3418,7 +3286,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114</v>
+        <v>113.8</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3466,12 +3334,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3493,7 +3361,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>180.1</v>
+        <v>179.7</v>
       </c>
       <c r="O11" t="n">
         <v>51.6</v>
@@ -3541,22 +3409,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ENERY.IS, TKFEN.IS</t>
+          <t>CANTE.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -3564,14 +3432,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.841091412127099</v>
+        <v>9.853823518422434</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3580,13 +3448,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="O12" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="P12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3603,13 +3471,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>41.527</v>
+        <v>42.844</v>
       </c>
       <c r="V12" t="n">
-        <v>51.66</v>
+        <v>53.071</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.761</v>
+        <v>-17.445</v>
       </c>
     </row>
     <row r="13">
@@ -3628,12 +3496,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3703,12 +3571,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3904,37 +3772,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ENERY.IS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-04</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>86.93022416585528</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>1.991644185925834</v>
+        <v>-1.593184911882817</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3943,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="O18" t="n">
         <v>44.7</v>
@@ -3953,11 +3809,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>18.106</v>
@@ -3966,13 +3822,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>225.622</v>
+        <v>197.173</v>
       </c>
       <c r="V18" t="n">
-        <v>105.459</v>
+        <v>98.238</v>
       </c>
       <c r="W18" t="n">
-        <v>-29.271</v>
+        <v>-38.513</v>
       </c>
     </row>
     <row r="19">
@@ -3993,12 +3849,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4020,7 +3876,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>120.4</v>
+        <v>120.1</v>
       </c>
       <c r="O19" t="n">
         <v>46.3</v>
@@ -4070,37 +3926,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ENERY.IS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-04</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>83.80706321463933</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +7.63% / +19.53% / -3.45%</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>1.971226428082229</v>
+        <v>-1.612885021011035</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4109,7 +3953,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="O20" t="n">
         <v>42.9</v>
@@ -4119,11 +3963,11 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>21.096</v>
@@ -4132,13 +3976,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>223.121</v>
+        <v>194.89</v>
       </c>
       <c r="V20" t="n">
-        <v>87.104</v>
+        <v>80.52800000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-29.006</v>
+        <v>-38.178</v>
       </c>
     </row>
     <row r="21">
@@ -4159,12 +4003,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4186,7 +4030,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>180.1</v>
+        <v>179.7</v>
       </c>
       <c r="O21" t="n">
         <v>51.6</v>
@@ -4236,22 +4080,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, RALYH.IS, SASA.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, FROTO.IS, SASA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-16 | ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-17 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4259,14 +4103,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.6335296089389</v>
+        <v>-14.69422345180439</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4275,13 +4119,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>140.4</v>
+        <v>142.1</v>
       </c>
       <c r="O22" t="n">
-        <v>42.2</v>
+        <v>41.6</v>
       </c>
       <c r="P22" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4292,19 +4136,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.359</v>
+        <v>29.705</v>
       </c>
       <c r="T22" t="n">
-        <v>26.359</v>
+        <v>29.705</v>
       </c>
       <c r="U22" t="n">
-        <v>21.6</v>
+        <v>16.075</v>
       </c>
       <c r="V22" t="n">
-        <v>11.106</v>
+        <v>6.058</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.524</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="23">
@@ -4325,37 +4169,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ENERY.IS, RALYH.IS, SASA.IS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-07 | RALYH.IS: 2026-09-16 | SASA.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>48.21914524341393</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>ENERY.IS: +10.11% / +22.32% / -0.50% | RALYH.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.20752087424826</v>
+        <v>-8.594955468590582</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4364,7 +4196,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.6</v>
+        <v>153.3</v>
       </c>
       <c r="O23" t="n">
         <v>41.7</v>
@@ -4374,26 +4206,26 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>21.943</v>
+        <v>25.241</v>
       </c>
       <c r="T23" t="n">
-        <v>21.943</v>
+        <v>25.241</v>
       </c>
       <c r="U23" t="n">
-        <v>17.174</v>
+        <v>7.653</v>
       </c>
       <c r="V23" t="n">
-        <v>1.448</v>
+        <v>-4.198</v>
       </c>
       <c r="W23" t="n">
-        <v>-30.839</v>
+        <v>-36.348</v>
       </c>
     </row>
     <row r="24">
@@ -4414,12 +4246,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4441,7 +4273,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114</v>
+        <v>113.8</v>
       </c>
       <c r="O24" t="n">
         <v>50.2</v>
@@ -4491,12 +4323,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4568,12 +4400,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -4595,7 +4427,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O26" t="n">
         <v>49.3</v>
@@ -4645,12 +4477,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -4722,22 +4554,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ENERY.IS, TKFEN.IS</t>
+          <t>CANTE.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-16 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4745,14 +4577,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +23.94% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K28" t="n">
-        <v>8.841091412127099</v>
+        <v>9.853823518422434</v>
       </c>
       <c r="L28" t="n">
         <v>31.31195090134997</v>
@@ -4761,13 +4593,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N28" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="O28" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="P28" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4784,13 +4616,13 @@
         <v>28.439</v>
       </c>
       <c r="U28" t="n">
-        <v>41.527</v>
+        <v>42.844</v>
       </c>
       <c r="V28" t="n">
-        <v>51.66</v>
+        <v>53.071</v>
       </c>
       <c r="W28" t="n">
-        <v>-18.761</v>
+        <v>-17.445</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -751,7 +751,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.24387074023273</v>
+        <v>-16.15198701460315</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -783,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>47.77</v>
+        <v>49.719</v>
       </c>
       <c r="V3" t="n">
-        <v>12.431</v>
+        <v>13.914</v>
       </c>
       <c r="W3" t="n">
-        <v>-44.786</v>
+        <v>-42.837</v>
       </c>
     </row>
     <row r="4">
@@ -976,7 +976,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.24387074023273</v>
+        <v>-16.15198701460315</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1008,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>47.77</v>
+        <v>49.719</v>
       </c>
       <c r="V6" t="n">
-        <v>12.431</v>
+        <v>13.914</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.786</v>
+        <v>-42.837</v>
       </c>
     </row>
     <row r="7">
@@ -1051,7 +1051,7 @@
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.78873025291825</v>
+        <v>-11.17068061932228</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1083,13 +1083,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>38.261</v>
+        <v>39.229</v>
       </c>
       <c r="V7" t="n">
-        <v>20.704</v>
+        <v>21.55</v>
       </c>
       <c r="W7" t="n">
-        <v>-42.061</v>
+        <v>-41.092</v>
       </c>
     </row>
     <row r="8">
@@ -1126,7 +1126,7 @@
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-19.71698998738825</v>
+        <v>-18.78168400505199</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1152,19 +1152,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>20.976</v>
+        <v>20.055</v>
       </c>
       <c r="T8" t="n">
-        <v>20.976</v>
+        <v>20.055</v>
       </c>
       <c r="U8" t="n">
-        <v>39.858</v>
+        <v>41.487</v>
       </c>
       <c r="V8" t="n">
-        <v>6.591</v>
+        <v>7.833</v>
       </c>
       <c r="W8" t="n">
-        <v>-37.123</v>
+        <v>-35.494</v>
       </c>
     </row>
     <row r="9">
@@ -1201,7 +1201,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.24387074023273</v>
+        <v>-16.15198701460315</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1233,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>47.77</v>
+        <v>49.719</v>
       </c>
       <c r="V9" t="n">
-        <v>12.431</v>
+        <v>13.914</v>
       </c>
       <c r="W9" t="n">
-        <v>-44.786</v>
+        <v>-42.837</v>
       </c>
     </row>
     <row r="10">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.71% / +4.81% / -0.85%</t>
+          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +8.10% / +9.50% / -0.85%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.730117133477787</v>
+        <v>-6.104245443853051</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1320,13 +1320,13 @@
         <v>10.759</v>
       </c>
       <c r="U10" t="n">
-        <v>12.943</v>
+        <v>13.701</v>
       </c>
       <c r="V10" t="n">
-        <v>5.014</v>
+        <v>5.719</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.445</v>
+        <v>-11.687</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.24387074023273</v>
+        <v>-16.15198701460315</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1821,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>47.77</v>
+        <v>49.719</v>
       </c>
       <c r="V18" t="n">
-        <v>12.431</v>
+        <v>13.914</v>
       </c>
       <c r="W18" t="n">
-        <v>-44.786</v>
+        <v>-42.837</v>
       </c>
     </row>
     <row r="19">
@@ -2020,7 +2020,7 @@
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-19.71698998738825</v>
+        <v>-18.78168400505199</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2046,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>20.976</v>
+        <v>20.055</v>
       </c>
       <c r="T21" t="n">
-        <v>20.976</v>
+        <v>20.055</v>
       </c>
       <c r="U21" t="n">
-        <v>39.858</v>
+        <v>41.487</v>
       </c>
       <c r="V21" t="n">
-        <v>6.591</v>
+        <v>7.833</v>
       </c>
       <c r="W21" t="n">
-        <v>-37.123</v>
+        <v>-35.494</v>
       </c>
     </row>
     <row r="22">
@@ -2097,7 +2097,7 @@
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.78873025291825</v>
+        <v>-11.17068061932228</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2129,13 +2129,13 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>38.261</v>
+        <v>39.229</v>
       </c>
       <c r="V22" t="n">
-        <v>20.704</v>
+        <v>21.55</v>
       </c>
       <c r="W22" t="n">
-        <v>-42.061</v>
+        <v>-41.092</v>
       </c>
     </row>
     <row r="23">
@@ -2256,14 +2256,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.71% / +4.81% / -0.85%</t>
+          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +8.10% / +9.50% / -0.85%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.730117133477787</v>
+        <v>-6.104245443853051</v>
       </c>
       <c r="L24" t="n">
         <v>4.543450519200398</v>
@@ -2295,13 +2295,13 @@
         <v>10.759</v>
       </c>
       <c r="U24" t="n">
-        <v>12.943</v>
+        <v>13.701</v>
       </c>
       <c r="V24" t="n">
-        <v>5.014</v>
+        <v>5.719</v>
       </c>
       <c r="W24" t="n">
-        <v>-12.445</v>
+        <v>-11.687</v>
       </c>
     </row>
     <row r="25">
@@ -2740,7 +2740,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.593184911882817</v>
+        <v>-1.187395674587866</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2772,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>197.173</v>
+        <v>198.398</v>
       </c>
       <c r="V3" t="n">
-        <v>98.238</v>
+        <v>99.05500000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>-38.513</v>
+        <v>-37.287</v>
       </c>
     </row>
     <row r="4">
@@ -2890,7 +2890,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.612885021011035</v>
+        <v>-1.207177018864802</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -2922,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>194.89</v>
+        <v>196.106</v>
       </c>
       <c r="V5" t="n">
-        <v>80.52800000000001</v>
+        <v>81.27200000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-38.178</v>
+        <v>-36.962</v>
       </c>
     </row>
     <row r="6">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-17 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2970,14 +2970,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +3.61% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-14.69422345180439</v>
+        <v>-13.74656473199725</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -2986,10 +2986,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>142.1</v>
+        <v>141.6</v>
       </c>
       <c r="O6" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="P6" t="n">
         <v>5.6</v>
@@ -3003,19 +3003,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>29.705</v>
+        <v>28.924</v>
       </c>
       <c r="T6" t="n">
-        <v>29.705</v>
+        <v>28.924</v>
       </c>
       <c r="U6" t="n">
-        <v>16.075</v>
+        <v>17.364</v>
       </c>
       <c r="V6" t="n">
-        <v>6.058</v>
+        <v>7.236</v>
       </c>
       <c r="W6" t="n">
-        <v>-49.05</v>
+        <v>-47.76</v>
       </c>
     </row>
     <row r="7">
@@ -3127,7 +3127,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.594955468590582</v>
+        <v>-8.370849418619352</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3153,19 +3153,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>25.241</v>
+        <v>25.058</v>
       </c>
       <c r="T8" t="n">
-        <v>25.241</v>
+        <v>25.058</v>
       </c>
       <c r="U8" t="n">
-        <v>7.653</v>
+        <v>7.917</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.198</v>
+        <v>-3.963</v>
       </c>
       <c r="W8" t="n">
-        <v>-36.348</v>
+        <v>-36.084</v>
       </c>
     </row>
     <row r="9">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CANTE.IS, TKFEN.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.853823518422434</v>
+        <v>11.99769626650593</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3471,13 +3471,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>42.844</v>
+        <v>45.631</v>
       </c>
       <c r="V12" t="n">
-        <v>53.071</v>
+        <v>56.058</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.445</v>
+        <v>-14.657</v>
       </c>
     </row>
     <row r="13">
@@ -3790,7 +3790,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.593184911882817</v>
+        <v>-1.187395674587866</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3822,13 +3822,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>197.173</v>
+        <v>198.398</v>
       </c>
       <c r="V18" t="n">
-        <v>98.238</v>
+        <v>99.05500000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>-38.513</v>
+        <v>-37.287</v>
       </c>
     </row>
     <row r="19">
@@ -3944,7 +3944,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.612885021011035</v>
+        <v>-1.207177018864802</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -3976,13 +3976,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>194.89</v>
+        <v>196.106</v>
       </c>
       <c r="V20" t="n">
-        <v>80.52800000000001</v>
+        <v>81.27200000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-38.178</v>
+        <v>-36.962</v>
       </c>
     </row>
     <row r="21">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-17 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4103,14 +4103,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +3.61% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-14.69422345180439</v>
+        <v>-13.74656473199725</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4119,10 +4119,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>142.1</v>
+        <v>141.6</v>
       </c>
       <c r="O22" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="P22" t="n">
         <v>5.6</v>
@@ -4136,19 +4136,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>29.705</v>
+        <v>28.924</v>
       </c>
       <c r="T22" t="n">
-        <v>29.705</v>
+        <v>28.924</v>
       </c>
       <c r="U22" t="n">
-        <v>16.075</v>
+        <v>17.364</v>
       </c>
       <c r="V22" t="n">
-        <v>6.058</v>
+        <v>7.236</v>
       </c>
       <c r="W22" t="n">
-        <v>-49.05</v>
+        <v>-47.76</v>
       </c>
     </row>
     <row r="23">
@@ -4187,7 +4187,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.594955468590582</v>
+        <v>-8.370849418619352</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4213,19 +4213,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>25.241</v>
+        <v>25.058</v>
       </c>
       <c r="T23" t="n">
-        <v>25.241</v>
+        <v>25.058</v>
       </c>
       <c r="U23" t="n">
-        <v>7.653</v>
+        <v>7.917</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.198</v>
+        <v>-3.963</v>
       </c>
       <c r="W23" t="n">
-        <v>-36.348</v>
+        <v>-36.084</v>
       </c>
     </row>
     <row r="24">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CANTE.IS, TKFEN.IS</t>
+          <t>ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4577,14 +4577,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +29.59% / +31.83% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K28" t="n">
-        <v>9.853823518422434</v>
+        <v>11.99769626650593</v>
       </c>
       <c r="L28" t="n">
         <v>31.31195090134997</v>
@@ -4616,13 +4616,13 @@
         <v>28.439</v>
       </c>
       <c r="U28" t="n">
-        <v>42.844</v>
+        <v>45.631</v>
       </c>
       <c r="V28" t="n">
-        <v>53.071</v>
+        <v>56.058</v>
       </c>
       <c r="W28" t="n">
-        <v>-17.445</v>
+        <v>-14.657</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -245,8 +245,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W28" headerRowCount="1">
-  <autoFilter ref="A17:W28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W26" headerRowCount="1">
+  <autoFilter ref="A17:W26"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -751,7 +751,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.15198701460315</v>
+        <v>-10.07588936491737</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -783,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>49.719</v>
+        <v>60.569</v>
       </c>
       <c r="V3" t="n">
-        <v>13.914</v>
+        <v>22.169</v>
       </c>
       <c r="W3" t="n">
-        <v>-42.837</v>
+        <v>-31.987</v>
       </c>
     </row>
     <row r="4">
@@ -976,7 +976,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.15198701460315</v>
+        <v>-10.07588936491737</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1008,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>49.719</v>
+        <v>60.569</v>
       </c>
       <c r="V6" t="n">
-        <v>13.914</v>
+        <v>22.169</v>
       </c>
       <c r="W6" t="n">
-        <v>-42.837</v>
+        <v>-31.987</v>
       </c>
     </row>
     <row r="7">
@@ -1051,7 +1051,7 @@
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.17068061932228</v>
+        <v>-8.975676554650303</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1083,13 +1083,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>39.229</v>
+        <v>42.67</v>
       </c>
       <c r="V7" t="n">
-        <v>21.55</v>
+        <v>24.554</v>
       </c>
       <c r="W7" t="n">
-        <v>-41.092</v>
+        <v>-37.652</v>
       </c>
     </row>
     <row r="8">
@@ -1126,7 +1126,7 @@
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-18.78168400505199</v>
+        <v>-18.28167754518812</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1152,19 +1152,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>20.055</v>
+        <v>19.563</v>
       </c>
       <c r="T8" t="n">
-        <v>20.055</v>
+        <v>19.563</v>
       </c>
       <c r="U8" t="n">
-        <v>41.487</v>
+        <v>42.358</v>
       </c>
       <c r="V8" t="n">
-        <v>7.833</v>
+        <v>8.497</v>
       </c>
       <c r="W8" t="n">
-        <v>-35.494</v>
+        <v>-34.622</v>
       </c>
     </row>
     <row r="9">
@@ -1201,7 +1201,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.15198701460315</v>
+        <v>-10.07588936491737</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1233,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>49.719</v>
+        <v>60.569</v>
       </c>
       <c r="V9" t="n">
-        <v>13.914</v>
+        <v>22.169</v>
       </c>
       <c r="W9" t="n">
-        <v>-42.837</v>
+        <v>-31.987</v>
       </c>
     </row>
     <row r="10">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +8.10% / +9.50% / -0.85%</t>
+          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.91% / +9.93% / -0.85%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.104245443853051</v>
+        <v>-5.7696600321811</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1320,13 +1320,13 @@
         <v>10.759</v>
       </c>
       <c r="U10" t="n">
-        <v>13.701</v>
+        <v>14.106</v>
       </c>
       <c r="V10" t="n">
-        <v>5.719</v>
+        <v>6.095</v>
       </c>
       <c r="W10" t="n">
-        <v>-11.687</v>
+        <v>-11.282</v>
       </c>
     </row>
     <row r="11">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1506,29 +1506,29 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>21.76975999384314</v>
+        <v>55.72500398673659</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-28.45194989279852</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>4.847592357308117</v>
+        <v>12.27104502948801</v>
       </c>
       <c r="L13" t="n">
-        <v>29.12044822069533</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>61.8</v>
+        <v>60.8</v>
       </c>
       <c r="O13" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="P13" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1539,19 +1539,19 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>25.589</v>
+        <v>25.345</v>
       </c>
       <c r="T13" t="n">
-        <v>25.589</v>
+        <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>93.55200000000001</v>
+        <v>93.867</v>
       </c>
       <c r="V13" t="n">
-        <v>103.043</v>
+        <v>106.868</v>
       </c>
       <c r="W13" t="n">
-        <v>-32.287</v>
+        <v>-17.383</v>
       </c>
     </row>
     <row r="14">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1581,29 +1581,29 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>21.76975999384314</v>
+        <v>55.72500398673659</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-28.45194989279852</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>4.847592357308117</v>
+        <v>12.27104502948801</v>
       </c>
       <c r="L14" t="n">
-        <v>29.12044822069533</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>61.8</v>
+        <v>60.8</v>
       </c>
       <c r="O14" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="P14" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1614,19 +1614,19 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>25.589</v>
+        <v>25.345</v>
       </c>
       <c r="T14" t="n">
-        <v>25.589</v>
+        <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>93.55200000000001</v>
+        <v>93.867</v>
       </c>
       <c r="V14" t="n">
-        <v>103.043</v>
+        <v>106.868</v>
       </c>
       <c r="W14" t="n">
-        <v>-32.287</v>
+        <v>-17.383</v>
       </c>
     </row>
     <row r="16">
@@ -1789,7 +1789,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.15198701460315</v>
+        <v>-10.07588936491737</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1821,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>49.719</v>
+        <v>60.569</v>
       </c>
       <c r="V18" t="n">
-        <v>13.914</v>
+        <v>22.169</v>
       </c>
       <c r="W18" t="n">
-        <v>-42.837</v>
+        <v>-31.987</v>
       </c>
     </row>
     <row r="19">
@@ -2020,7 +2020,7 @@
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-18.78168400505199</v>
+        <v>-18.28167754518812</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2046,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>20.055</v>
+        <v>19.563</v>
       </c>
       <c r="T21" t="n">
-        <v>20.055</v>
+        <v>19.563</v>
       </c>
       <c r="U21" t="n">
-        <v>41.487</v>
+        <v>42.358</v>
       </c>
       <c r="V21" t="n">
-        <v>7.833</v>
+        <v>8.497</v>
       </c>
       <c r="W21" t="n">
-        <v>-35.494</v>
+        <v>-34.622</v>
       </c>
     </row>
     <row r="22">
@@ -2097,7 +2097,7 @@
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.17068061932228</v>
+        <v>-8.975676554650303</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2129,29 +2129,29 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>39.229</v>
+        <v>42.67</v>
       </c>
       <c r="V22" t="n">
-        <v>21.55</v>
+        <v>24.554</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.092</v>
+        <v>-37.652</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2167,29 +2167,29 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>50.58108284302749</v>
+        <v>55.72500398673659</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>13.3215021172385</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.400004582905126e-07</v>
+        <v>12.27104502948801</v>
       </c>
       <c r="L23" t="n">
-        <v>5.668150937989602</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M23" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>65.7</v>
+        <v>60.8</v>
       </c>
       <c r="O23" t="n">
-        <v>51.9</v>
+        <v>44.8</v>
       </c>
       <c r="P23" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2200,35 +2200,35 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>7.033</v>
+        <v>25.345</v>
       </c>
       <c r="T23" t="n">
-        <v>7.033</v>
+        <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>85.90600000000001</v>
+        <v>93.867</v>
       </c>
       <c r="V23" t="n">
-        <v>58.898</v>
+        <v>106.868</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.624</v>
+        <v>-17.383</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2241,83 +2241,71 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ASELS.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ASELS.IS: 2026-09-17 | TKFEN.IS: 2026-09-16</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>23.02092795860866</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +8.10% / +9.50% / -0.85%</t>
-        </is>
-      </c>
+        <v>55.72500398673659</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>12.86015270141232</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.104245443853051</v>
+        <v>12.27104502948801</v>
       </c>
       <c r="L24" t="n">
-        <v>4.543450519200398</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M24" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>177.6</v>
+        <v>60.8</v>
       </c>
       <c r="O24" t="n">
-        <v>48.2</v>
+        <v>44.8</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>10.759</v>
+        <v>25.345</v>
       </c>
       <c r="T24" t="n">
-        <v>10.759</v>
+        <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>13.701</v>
+        <v>93.867</v>
       </c>
       <c r="V24" t="n">
-        <v>5.719</v>
+        <v>106.868</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.687</v>
+        <v>-17.383</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2333,29 +2321,29 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>21.76975999384314</v>
+        <v>50.58108284302749</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>-28.45194989279852</v>
+        <v>13.3215021172385</v>
       </c>
       <c r="K25" t="n">
-        <v>4.847592357308117</v>
+        <v>-4.400004582905126e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>29.12044822069533</v>
+        <v>5.668150937989602</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>61.8</v>
+        <v>65.7</v>
       </c>
       <c r="O25" t="n">
-        <v>43.3</v>
+        <v>51.9</v>
       </c>
       <c r="P25" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2366,35 +2354,35 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>25.589</v>
+        <v>7.033</v>
       </c>
       <c r="T25" t="n">
-        <v>25.589</v>
+        <v>7.033</v>
       </c>
       <c r="U25" t="n">
-        <v>93.55200000000001</v>
+        <v>85.90600000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>103.043</v>
+        <v>58.898</v>
       </c>
       <c r="W25" t="n">
-        <v>-32.287</v>
+        <v>-1.624</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2407,55 +2395,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ASELS.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ASELS.IS: 2026-09-17 | TKFEN.IS: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>21.76975999384314</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>23.02092795860866</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.91% / +9.93% / -0.85%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>-28.45194989279852</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>4.847592357308117</v>
+        <v>-5.7696600321811</v>
       </c>
       <c r="L26" t="n">
-        <v>29.12044822069533</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M26" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>61.8</v>
+        <v>177.6</v>
       </c>
       <c r="O26" t="n">
-        <v>43.3</v>
+        <v>48.2</v>
       </c>
       <c r="P26" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>25.589</v>
+        <v>10.759</v>
       </c>
       <c r="T26" t="n">
-        <v>25.589</v>
+        <v>10.759</v>
       </c>
       <c r="U26" t="n">
-        <v>93.55200000000001</v>
+        <v>14.106</v>
       </c>
       <c r="V26" t="n">
-        <v>103.043</v>
+        <v>6.095</v>
       </c>
       <c r="W26" t="n">
-        <v>-32.287</v>
+        <v>-11.282</v>
       </c>
     </row>
     <row r="27">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2740,7 +2740,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.187395674587866</v>
+        <v>4.674004419672428</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2772,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>198.398</v>
+        <v>216.099</v>
       </c>
       <c r="V3" t="n">
-        <v>99.05500000000001</v>
+        <v>110.863</v>
       </c>
       <c r="W3" t="n">
-        <v>-37.287</v>
+        <v>-19.587</v>
       </c>
     </row>
     <row r="4">
@@ -2890,7 +2890,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.207177018864802</v>
+        <v>4.653049678803001</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -2922,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>196.106</v>
+        <v>213.671</v>
       </c>
       <c r="V5" t="n">
-        <v>81.27200000000001</v>
+        <v>92.02500000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-36.962</v>
+        <v>-19.398</v>
       </c>
     </row>
     <row r="6">
@@ -2970,14 +2970,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +3.61% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +15.59% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-13.74656473199725</v>
+        <v>-11.15275059979806</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3003,19 +3003,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>28.924</v>
+        <v>26.786</v>
       </c>
       <c r="T6" t="n">
-        <v>28.924</v>
+        <v>26.786</v>
       </c>
       <c r="U6" t="n">
-        <v>17.364</v>
+        <v>20.894</v>
       </c>
       <c r="V6" t="n">
-        <v>7.236</v>
+        <v>10.461</v>
       </c>
       <c r="W6" t="n">
-        <v>-47.76</v>
+        <v>-44.231</v>
       </c>
     </row>
     <row r="7">
@@ -3127,7 +3127,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.370849418619352</v>
+        <v>-5.21732288500557</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3153,19 +3153,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>25.058</v>
+        <v>22.479</v>
       </c>
       <c r="T8" t="n">
-        <v>25.058</v>
+        <v>22.479</v>
       </c>
       <c r="U8" t="n">
-        <v>7.917</v>
+        <v>11.631</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.963</v>
+        <v>-0.658</v>
       </c>
       <c r="W8" t="n">
-        <v>-36.084</v>
+        <v>-32.37</v>
       </c>
     </row>
     <row r="9">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>11.99769626650593</v>
+        <v>13.20362468730292</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3471,13 +3471,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>45.631</v>
+        <v>47.199</v>
       </c>
       <c r="V12" t="n">
-        <v>56.058</v>
+        <v>57.738</v>
       </c>
       <c r="W12" t="n">
-        <v>-14.657</v>
+        <v>-13.089</v>
       </c>
     </row>
     <row r="13">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3507,29 +3507,29 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>8.530010255723974</v>
+        <v>86.93022416585528</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.8142516931666233</v>
+        <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>3.846414277792909</v>
+        <v>4.674004419672428</v>
       </c>
       <c r="L13" t="n">
-        <v>9.181211458048665</v>
+        <v>28.4081875</v>
       </c>
       <c r="M13" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>35.2</v>
+        <v>92.8</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>44.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3540,19 +3540,19 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>8.083</v>
+        <v>18.106</v>
       </c>
       <c r="T13" t="n">
-        <v>7.916</v>
+        <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>6.923</v>
+        <v>216.099</v>
       </c>
       <c r="V13" t="n">
-        <v>4.916</v>
+        <v>110.863</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.88</v>
+        <v>-19.587</v>
       </c>
     </row>
     <row r="14">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T1_genislik_skor|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3582,29 +3582,29 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>32.90971238010212</v>
+        <v>83.80706321463933</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>3.175499702073514</v>
+        <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>2.680368121576793</v>
+        <v>4.653049678803001</v>
       </c>
       <c r="L14" t="n">
-        <v>18.99889339779883</v>
+        <v>32.3216328125</v>
       </c>
       <c r="M14" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="O14" t="n">
-        <v>51.1</v>
+        <v>42.9</v>
       </c>
       <c r="P14" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3615,19 +3615,19 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>18.999</v>
+        <v>21.096</v>
       </c>
       <c r="T14" t="n">
-        <v>16.472</v>
+        <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>25.295</v>
+        <v>213.671</v>
       </c>
       <c r="V14" t="n">
-        <v>17.703</v>
+        <v>92.02500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-15.006</v>
+        <v>-19.398</v>
       </c>
     </row>
     <row r="16">
@@ -3757,12 +3757,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 | 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3790,7 +3790,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.187395674587866</v>
+        <v>4.674004419672428</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3822,13 +3822,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>198.398</v>
+        <v>216.099</v>
       </c>
       <c r="V18" t="n">
-        <v>99.05500000000001</v>
+        <v>110.863</v>
       </c>
       <c r="W18" t="n">
-        <v>-37.287</v>
+        <v>-19.587</v>
       </c>
     </row>
     <row r="19">
@@ -3911,7 +3911,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3944,7 +3944,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.207177018864802</v>
+        <v>4.653049678803001</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -3976,13 +3976,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>196.106</v>
+        <v>213.671</v>
       </c>
       <c r="V20" t="n">
-        <v>81.27200000000001</v>
+        <v>92.02500000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-36.962</v>
+        <v>-19.398</v>
       </c>
     </row>
     <row r="21">
@@ -4103,14 +4103,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +3.61% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +15.59% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-13.74656473199725</v>
+        <v>-11.15275059979806</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4136,19 +4136,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>28.924</v>
+        <v>26.786</v>
       </c>
       <c r="T22" t="n">
-        <v>28.924</v>
+        <v>26.786</v>
       </c>
       <c r="U22" t="n">
-        <v>17.364</v>
+        <v>20.894</v>
       </c>
       <c r="V22" t="n">
-        <v>7.236</v>
+        <v>10.461</v>
       </c>
       <c r="W22" t="n">
-        <v>-47.76</v>
+        <v>-44.231</v>
       </c>
     </row>
     <row r="23">
@@ -4187,7 +4187,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.370849418619352</v>
+        <v>-5.21732288500557</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4213,19 +4213,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>25.058</v>
+        <v>22.479</v>
       </c>
       <c r="T23" t="n">
-        <v>25.058</v>
+        <v>22.479</v>
       </c>
       <c r="U23" t="n">
-        <v>7.917</v>
+        <v>11.631</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.963</v>
+        <v>-0.658</v>
       </c>
       <c r="W23" t="n">
-        <v>-36.084</v>
+        <v>-32.37</v>
       </c>
     </row>
     <row r="24">
@@ -4308,17 +4308,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4334,29 +4334,29 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>32.90971238010212</v>
+        <v>28.40086810394897</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3.175499702073514</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>2.680368121576793</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L25" t="n">
-        <v>18.99889339779883</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>44</v>
+        <v>74.2</v>
       </c>
       <c r="O25" t="n">
-        <v>51.1</v>
+        <v>49.3</v>
       </c>
       <c r="P25" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4367,25 +4367,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>18.999</v>
+        <v>13.28</v>
       </c>
       <c r="T25" t="n">
-        <v>16.472</v>
+        <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>25.295</v>
+        <v>7.136</v>
       </c>
       <c r="V25" t="n">
-        <v>17.703</v>
+        <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-15.006</v>
+        <v>-16.407</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4408,221 +4408,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>28.40086810394897</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>6.880672511445463</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>15.38514121842653</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.616392554049999</v>
+        <v>13.20362468730292</v>
       </c>
       <c r="L26" t="n">
-        <v>5.127814043936619</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M26" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>74.2</v>
+        <v>48.8</v>
       </c>
       <c r="O26" t="n">
-        <v>49.3</v>
+        <v>42</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>13.28</v>
+        <v>28.439</v>
       </c>
       <c r="T26" t="n">
-        <v>13.28</v>
+        <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>7.136</v>
+        <v>47.199</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.962</v>
+        <v>57.738</v>
       </c>
       <c r="W26" t="n">
-        <v>-16.407</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>8.530010255723974</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>0.8142516931666233</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.846414277792909</v>
-      </c>
-      <c r="L27" t="n">
-        <v>9.181211458048665</v>
-      </c>
-      <c r="M27" t="n">
-        <v>72.22222222222221</v>
-      </c>
-      <c r="N27" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>50</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>8.083</v>
-      </c>
-      <c r="T27" t="n">
-        <v>7.916</v>
-      </c>
-      <c r="U27" t="n">
-        <v>6.923</v>
-      </c>
-      <c r="V27" t="n">
-        <v>4.916</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-4.88</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>6.880672511445463</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +33.81% / +35.69% / -0.56%</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>-18.9000927288166</v>
-      </c>
-      <c r="K28" t="n">
-        <v>11.99769626650593</v>
-      </c>
-      <c r="L28" t="n">
-        <v>31.31195090134997</v>
-      </c>
-      <c r="M28" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N28" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>42</v>
-      </c>
-      <c r="P28" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>28.439</v>
-      </c>
-      <c r="T28" t="n">
-        <v>28.439</v>
-      </c>
-      <c r="U28" t="n">
-        <v>45.631</v>
-      </c>
-      <c r="V28" t="n">
-        <v>56.058</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-14.657</v>
+        <v>-13.089</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -751,7 +751,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.07588936491737</v>
+        <v>-9.700233108330536</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -783,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>60.569</v>
+        <v>61.24</v>
       </c>
       <c r="V3" t="n">
-        <v>22.169</v>
+        <v>22.679</v>
       </c>
       <c r="W3" t="n">
-        <v>-31.987</v>
+        <v>-31.316</v>
       </c>
     </row>
     <row r="4">
@@ -976,7 +976,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.07588936491737</v>
+        <v>-9.700233108330536</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1008,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>60.569</v>
+        <v>61.24</v>
       </c>
       <c r="V6" t="n">
-        <v>22.169</v>
+        <v>22.679</v>
       </c>
       <c r="W6" t="n">
-        <v>-31.987</v>
+        <v>-31.316</v>
       </c>
     </row>
     <row r="7">
@@ -1051,7 +1051,7 @@
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.975676554650303</v>
+        <v>-9.325081671375667</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1083,13 +1083,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>42.67</v>
+        <v>42.122</v>
       </c>
       <c r="V7" t="n">
-        <v>24.554</v>
+        <v>24.076</v>
       </c>
       <c r="W7" t="n">
-        <v>-37.652</v>
+        <v>-38.2</v>
       </c>
     </row>
     <row r="8">
@@ -1201,7 +1201,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.07588936491737</v>
+        <v>-9.700233108330536</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1233,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>60.569</v>
+        <v>61.24</v>
       </c>
       <c r="V9" t="n">
-        <v>22.169</v>
+        <v>22.679</v>
       </c>
       <c r="W9" t="n">
-        <v>-31.987</v>
+        <v>-31.316</v>
       </c>
     </row>
     <row r="10">
@@ -1513,7 +1513,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>12.27104502948801</v>
+        <v>12.75670538151126</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1545,13 +1545,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>93.867</v>
+        <v>94.706</v>
       </c>
       <c r="V13" t="n">
-        <v>106.868</v>
+        <v>107.763</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.383</v>
+        <v>-16.544</v>
       </c>
     </row>
     <row r="14">
@@ -1588,7 +1588,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>12.27104502948801</v>
+        <v>12.75670538151126</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1620,13 +1620,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>93.867</v>
+        <v>94.706</v>
       </c>
       <c r="V14" t="n">
-        <v>106.868</v>
+        <v>107.763</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.383</v>
+        <v>-16.544</v>
       </c>
     </row>
     <row r="16">
@@ -1789,7 +1789,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.07588936491737</v>
+        <v>-9.700233108330536</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1821,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>60.569</v>
+        <v>61.24</v>
       </c>
       <c r="V18" t="n">
-        <v>22.169</v>
+        <v>22.679</v>
       </c>
       <c r="W18" t="n">
-        <v>-31.987</v>
+        <v>-31.316</v>
       </c>
     </row>
     <row r="19">
@@ -2097,7 +2097,7 @@
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.975676554650303</v>
+        <v>-9.325081671375667</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2129,13 +2129,13 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>42.67</v>
+        <v>42.122</v>
       </c>
       <c r="V22" t="n">
-        <v>24.554</v>
+        <v>24.076</v>
       </c>
       <c r="W22" t="n">
-        <v>-37.652</v>
+        <v>-38.2</v>
       </c>
     </row>
     <row r="23">
@@ -2174,7 +2174,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>12.27104502948801</v>
+        <v>12.75670538151126</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2206,13 +2206,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>93.867</v>
+        <v>94.706</v>
       </c>
       <c r="V23" t="n">
-        <v>106.868</v>
+        <v>107.763</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.383</v>
+        <v>-16.544</v>
       </c>
     </row>
     <row r="24">
@@ -2251,7 +2251,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>12.27104502948801</v>
+        <v>12.75670538151126</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2283,13 +2283,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>93.867</v>
+        <v>94.706</v>
       </c>
       <c r="V24" t="n">
-        <v>106.868</v>
+        <v>107.763</v>
       </c>
       <c r="W24" t="n">
-        <v>-17.383</v>
+        <v>-16.544</v>
       </c>
     </row>
     <row r="25">
@@ -2740,7 +2740,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>4.674004419672428</v>
+        <v>5.221741120755707</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2772,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>216.099</v>
+        <v>217.753</v>
       </c>
       <c r="V3" t="n">
-        <v>110.863</v>
+        <v>111.966</v>
       </c>
       <c r="W3" t="n">
-        <v>-19.587</v>
+        <v>-17.933</v>
       </c>
     </row>
     <row r="4">
@@ -2890,7 +2890,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>4.653049678803001</v>
+        <v>5.20067672820439</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -2922,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>213.671</v>
+        <v>215.312</v>
       </c>
       <c r="V5" t="n">
-        <v>92.02500000000001</v>
+        <v>93.03</v>
       </c>
       <c r="W5" t="n">
-        <v>-19.398</v>
+        <v>-17.756</v>
       </c>
     </row>
     <row r="6">
@@ -2970,14 +2970,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +15.59% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.71% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.15275059979806</v>
+        <v>-10.94543585303989</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3003,19 +3003,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.786</v>
+        <v>26.616</v>
       </c>
       <c r="T6" t="n">
-        <v>26.786</v>
+        <v>26.616</v>
       </c>
       <c r="U6" t="n">
-        <v>20.894</v>
+        <v>21.176</v>
       </c>
       <c r="V6" t="n">
-        <v>10.461</v>
+        <v>10.719</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.231</v>
+        <v>-43.949</v>
       </c>
     </row>
     <row r="7">
@@ -3127,7 +3127,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.21732288500557</v>
+        <v>-4.918987422654075</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3153,19 +3153,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>22.479</v>
+        <v>22.235</v>
       </c>
       <c r="T8" t="n">
-        <v>22.479</v>
+        <v>22.235</v>
       </c>
       <c r="U8" t="n">
-        <v>11.631</v>
+        <v>11.983</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.658</v>
+        <v>-0.346</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.37</v>
+        <v>-32.018</v>
       </c>
     </row>
     <row r="9">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>13.20362468730292</v>
+        <v>13.21172202743475</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3471,13 +3471,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>47.199</v>
+        <v>47.21</v>
       </c>
       <c r="V12" t="n">
-        <v>57.738</v>
+        <v>57.75</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.089</v>
+        <v>-13.078</v>
       </c>
     </row>
     <row r="13">
@@ -3514,7 +3514,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>4.674004419672428</v>
+        <v>5.221741120755707</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3546,13 +3546,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>216.099</v>
+        <v>217.753</v>
       </c>
       <c r="V13" t="n">
-        <v>110.863</v>
+        <v>111.966</v>
       </c>
       <c r="W13" t="n">
-        <v>-19.587</v>
+        <v>-17.933</v>
       </c>
     </row>
     <row r="14">
@@ -3589,7 +3589,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>4.653049678803001</v>
+        <v>5.20067672820439</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3621,13 +3621,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>213.671</v>
+        <v>215.312</v>
       </c>
       <c r="V14" t="n">
-        <v>92.02500000000001</v>
+        <v>93.03</v>
       </c>
       <c r="W14" t="n">
-        <v>-19.398</v>
+        <v>-17.756</v>
       </c>
     </row>
     <row r="16">
@@ -3790,7 +3790,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>4.674004419672428</v>
+        <v>5.221741120755707</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3822,13 +3822,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>216.099</v>
+        <v>217.753</v>
       </c>
       <c r="V18" t="n">
-        <v>110.863</v>
+        <v>111.966</v>
       </c>
       <c r="W18" t="n">
-        <v>-19.587</v>
+        <v>-17.933</v>
       </c>
     </row>
     <row r="19">
@@ -3944,7 +3944,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>4.653049678803001</v>
+        <v>5.20067672820439</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -3976,13 +3976,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>213.671</v>
+        <v>215.312</v>
       </c>
       <c r="V20" t="n">
-        <v>92.02500000000001</v>
+        <v>93.03</v>
       </c>
       <c r="W20" t="n">
-        <v>-19.398</v>
+        <v>-17.756</v>
       </c>
     </row>
     <row r="21">
@@ -4103,14 +4103,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +15.59% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.71% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.15275059979806</v>
+        <v>-10.94543585303989</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4136,19 +4136,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.786</v>
+        <v>26.616</v>
       </c>
       <c r="T22" t="n">
-        <v>26.786</v>
+        <v>26.616</v>
       </c>
       <c r="U22" t="n">
-        <v>20.894</v>
+        <v>21.176</v>
       </c>
       <c r="V22" t="n">
-        <v>10.461</v>
+        <v>10.719</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.231</v>
+        <v>-43.949</v>
       </c>
     </row>
     <row r="23">
@@ -4187,7 +4187,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.21732288500557</v>
+        <v>-4.918987422654075</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4213,19 +4213,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>22.479</v>
+        <v>22.235</v>
       </c>
       <c r="T23" t="n">
-        <v>22.479</v>
+        <v>22.235</v>
       </c>
       <c r="U23" t="n">
-        <v>11.631</v>
+        <v>11.983</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.658</v>
+        <v>-0.346</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.37</v>
+        <v>-32.018</v>
       </c>
     </row>
     <row r="24">
@@ -4423,14 +4423,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.19% / +36.21% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>13.20362468730292</v>
+        <v>13.21172202743475</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4462,13 +4462,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>47.199</v>
+        <v>47.21</v>
       </c>
       <c r="V26" t="n">
-        <v>57.738</v>
+        <v>57.75</v>
       </c>
       <c r="W26" t="n">
-        <v>-13.089</v>
+        <v>-13.078</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,7 +573,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -733,25 +733,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.700233108330536</v>
+        <v>-9.736349403096511</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -760,21 +772,21 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.2</v>
+        <v>102.9</v>
       </c>
       <c r="O3" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="P3" t="n">
         <v>6.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>23.832</v>
@@ -783,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>61.24</v>
+        <v>53.823</v>
       </c>
       <c r="V3" t="n">
-        <v>22.679</v>
+        <v>22.63</v>
       </c>
       <c r="W3" t="n">
-        <v>-31.316</v>
+        <v>-29.949</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -883,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -958,25 +970,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.700233108330536</v>
+        <v>-9.736349403096511</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -985,21 +1009,21 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.2</v>
+        <v>102.9</v>
       </c>
       <c r="O6" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="P6" t="n">
         <v>6.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>23.832</v>
@@ -1008,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>61.24</v>
+        <v>53.823</v>
       </c>
       <c r="V6" t="n">
-        <v>22.679</v>
+        <v>22.63</v>
       </c>
       <c r="W6" t="n">
-        <v>-31.316</v>
+        <v>-29.949</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1084,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>135.7</v>
+        <v>135.5</v>
       </c>
       <c r="O7" t="n">
         <v>46.6</v>
@@ -1083,13 +1107,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>42.122</v>
+        <v>36.336</v>
       </c>
       <c r="V7" t="n">
         <v>24.076</v>
       </c>
       <c r="W7" t="n">
-        <v>-38.2</v>
+        <v>-36.644</v>
       </c>
     </row>
     <row r="8">
@@ -1108,25 +1132,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS, TSKB.IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18 | TSKB.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>60.64599942530686</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-18.28167754518812</v>
+        <v>-18.31436051585953</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1135,36 +1171,36 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>193.6</v>
+        <v>194.7</v>
       </c>
       <c r="O8" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>19.563</v>
+        <v>19.595</v>
       </c>
       <c r="T8" t="n">
-        <v>19.563</v>
+        <v>19.595</v>
       </c>
       <c r="U8" t="n">
-        <v>42.358</v>
+        <v>38.859</v>
       </c>
       <c r="V8" t="n">
-        <v>8.497</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>-34.622</v>
+        <v>-33.84</v>
       </c>
     </row>
     <row r="9">
@@ -1183,25 +1219,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.700233108330536</v>
+        <v>-9.736349403096511</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1210,21 +1258,21 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.2</v>
+        <v>102.9</v>
       </c>
       <c r="O9" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="P9" t="n">
         <v>6.7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>23.832</v>
@@ -1233,13 +1281,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>61.24</v>
+        <v>53.823</v>
       </c>
       <c r="V9" t="n">
-        <v>22.679</v>
+        <v>22.63</v>
       </c>
       <c r="W9" t="n">
-        <v>-31.316</v>
+        <v>-29.949</v>
       </c>
     </row>
     <row r="10">
@@ -1258,22 +1306,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASELS.IS, TKFEN.IS</t>
+          <t>AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ASELS.IS: 2026-09-17 | TKFEN.IS: 2026-09-16</t>
+          <t>AKSA.IS: 2026-09-18 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1281,14 +1329,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.91% / +9.93% / -0.85%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.28% / +14.51% / -1.02%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.7696600321811</v>
+        <v>-6.64412092898321</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1297,10 +1345,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>177.6</v>
+        <v>177.7</v>
       </c>
       <c r="O10" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1320,13 +1368,13 @@
         <v>10.759</v>
       </c>
       <c r="U10" t="n">
-        <v>14.106</v>
+        <v>13.047</v>
       </c>
       <c r="V10" t="n">
-        <v>6.095</v>
+        <v>5.111</v>
       </c>
       <c r="W10" t="n">
-        <v>-11.282</v>
+        <v>-12.341</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1393,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1372,7 +1420,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>65.7</v>
+        <v>65.5</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1420,12 +1468,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1447,7 +1495,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="O12" t="n">
         <v>45.3</v>
@@ -1495,25 +1543,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>12.75670538151126</v>
+        <v>12.71160720962683</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1522,21 +1582,21 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>60.8</v>
+        <v>61.7</v>
       </c>
       <c r="O13" t="n">
-        <v>44.8</v>
+        <v>44.1</v>
       </c>
       <c r="P13" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>25.345</v>
@@ -1545,13 +1605,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>94.706</v>
+        <v>94.628</v>
       </c>
       <c r="V13" t="n">
-        <v>107.763</v>
+        <v>107.68</v>
       </c>
       <c r="W13" t="n">
-        <v>-16.544</v>
+        <v>-16.622</v>
       </c>
     </row>
     <row r="14">
@@ -1570,25 +1630,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>12.75670538151126</v>
+        <v>12.71160720962683</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1597,21 +1669,21 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>60.8</v>
+        <v>61.7</v>
       </c>
       <c r="O14" t="n">
-        <v>44.8</v>
+        <v>44.1</v>
       </c>
       <c r="P14" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>25.345</v>
@@ -1620,13 +1692,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>94.706</v>
+        <v>94.628</v>
       </c>
       <c r="V14" t="n">
-        <v>107.763</v>
+        <v>107.68</v>
       </c>
       <c r="W14" t="n">
-        <v>-16.544</v>
+        <v>-16.622</v>
       </c>
     </row>
     <row r="16">
@@ -1771,25 +1843,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.700233108330536</v>
+        <v>-9.736349403096511</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1798,21 +1882,21 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.2</v>
+        <v>102.9</v>
       </c>
       <c r="O18" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="P18" t="n">
         <v>6.7</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>23.832</v>
@@ -1821,13 +1905,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>61.24</v>
+        <v>53.823</v>
       </c>
       <c r="V18" t="n">
-        <v>22.679</v>
+        <v>22.63</v>
       </c>
       <c r="W18" t="n">
-        <v>-31.316</v>
+        <v>-29.949</v>
       </c>
     </row>
     <row r="19">
@@ -1848,12 +1932,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1875,7 +1959,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1925,12 +2009,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1952,7 +2036,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2002,25 +2086,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS, TSKB.IS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18 | TSKB.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>60.64599942530686</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-18.28167754518812</v>
+        <v>-18.31436051585953</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2029,36 +2125,36 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>193.6</v>
+        <v>194.7</v>
       </c>
       <c r="O21" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>19.563</v>
+        <v>19.595</v>
       </c>
       <c r="T21" t="n">
-        <v>19.563</v>
+        <v>19.595</v>
       </c>
       <c r="U21" t="n">
-        <v>42.358</v>
+        <v>38.859</v>
       </c>
       <c r="V21" t="n">
-        <v>8.497</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>-34.622</v>
+        <v>-33.84</v>
       </c>
     </row>
     <row r="22">
@@ -2079,12 +2175,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2106,7 +2202,7 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>135.7</v>
+        <v>135.5</v>
       </c>
       <c r="O22" t="n">
         <v>46.6</v>
@@ -2129,13 +2225,13 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>42.122</v>
+        <v>36.336</v>
       </c>
       <c r="V22" t="n">
         <v>24.076</v>
       </c>
       <c r="W22" t="n">
-        <v>-38.2</v>
+        <v>-36.644</v>
       </c>
     </row>
     <row r="23">
@@ -2156,25 +2252,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>12.75670538151126</v>
+        <v>12.71160720962683</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2183,21 +2291,21 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>60.8</v>
+        <v>61.7</v>
       </c>
       <c r="O23" t="n">
-        <v>44.8</v>
+        <v>44.1</v>
       </c>
       <c r="P23" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
         <v>25.345</v>
@@ -2206,13 +2314,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>94.706</v>
+        <v>94.628</v>
       </c>
       <c r="V23" t="n">
-        <v>107.763</v>
+        <v>107.68</v>
       </c>
       <c r="W23" t="n">
-        <v>-16.544</v>
+        <v>-16.622</v>
       </c>
     </row>
     <row r="24">
@@ -2233,25 +2341,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>12.75670538151126</v>
+        <v>12.71160720962683</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2260,21 +2380,21 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>60.8</v>
+        <v>61.7</v>
       </c>
       <c r="O24" t="n">
-        <v>44.8</v>
+        <v>44.1</v>
       </c>
       <c r="P24" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
         <v>25.345</v>
@@ -2283,13 +2403,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>94.706</v>
+        <v>94.628</v>
       </c>
       <c r="V24" t="n">
-        <v>107.763</v>
+        <v>107.68</v>
       </c>
       <c r="W24" t="n">
-        <v>-16.544</v>
+        <v>-16.622</v>
       </c>
     </row>
     <row r="25">
@@ -2310,12 +2430,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2337,7 +2457,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>65.7</v>
+        <v>65.5</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2387,22 +2507,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASELS.IS, TKFEN.IS</t>
+          <t>AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASELS.IS: 2026-09-17 | TKFEN.IS: 2026-09-16</t>
+          <t>AKSA.IS: 2026-09-18 | TKFEN.IS: 2026-09-16</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2410,14 +2530,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASELS.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.91% / +9.93% / -0.85%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.28% / +14.51% / -1.02%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.7696600321811</v>
+        <v>-6.64412092898321</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2426,10 +2546,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>177.6</v>
+        <v>177.7</v>
       </c>
       <c r="O26" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2449,13 +2569,13 @@
         <v>10.759</v>
       </c>
       <c r="U26" t="n">
-        <v>14.106</v>
+        <v>13.047</v>
       </c>
       <c r="V26" t="n">
-        <v>6.095</v>
+        <v>5.111</v>
       </c>
       <c r="W26" t="n">
-        <v>-11.282</v>
+        <v>-12.341</v>
       </c>
     </row>
     <row r="27">
@@ -2476,12 +2596,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2503,7 +2623,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N27" t="n">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="O27" t="n">
         <v>45.3</v>
@@ -2722,12 +2842,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2740,7 +2860,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>5.221741120755707</v>
+        <v>5.224085869864203</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2749,7 +2869,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>44.7</v>
@@ -2772,13 +2892,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>217.753</v>
+        <v>214.628</v>
       </c>
       <c r="V3" t="n">
-        <v>111.966</v>
+        <v>111.971</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.933</v>
+        <v>-17.749</v>
       </c>
     </row>
     <row r="4">
@@ -2797,12 +2917,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2824,7 +2944,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>120.1</v>
+        <v>119.9</v>
       </c>
       <c r="O4" t="n">
         <v>46.3</v>
@@ -2872,12 +2992,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2890,7 +3010,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>5.20067672820439</v>
+        <v>5.203021007916409</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -2899,7 +3019,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>42.9</v>
@@ -2922,13 +3042,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>215.312</v>
+        <v>212.211</v>
       </c>
       <c r="V5" t="n">
-        <v>93.03</v>
+        <v>93.03400000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-17.756</v>
+        <v>-17.574</v>
       </c>
     </row>
     <row r="6">
@@ -2947,14 +3067,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>CANTE.IS, ENERY.IS, FROTO.IS, SASA.IS, TKFEN.IS</t>
@@ -2962,7 +3082,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-18 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2970,14 +3090,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.71% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +18.21% / +22.32% / -0.50% | FROTO.IS: -2.11% / +0.36% / -2.60% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.94543585303989</v>
+        <v>-13.53028338591502</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -2986,10 +3106,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>141.6</v>
+        <v>142.3</v>
       </c>
       <c r="O6" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="P6" t="n">
         <v>5.6</v>
@@ -3003,19 +3123,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.616</v>
+        <v>28.746</v>
       </c>
       <c r="T6" t="n">
-        <v>26.616</v>
+        <v>28.746</v>
       </c>
       <c r="U6" t="n">
-        <v>21.176</v>
+        <v>17.659</v>
       </c>
       <c r="V6" t="n">
-        <v>10.719</v>
+        <v>7.505</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.949</v>
+        <v>-47.466</v>
       </c>
     </row>
     <row r="7">
@@ -3034,12 +3154,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3061,7 +3181,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>120.1</v>
+        <v>119.9</v>
       </c>
       <c r="O7" t="n">
         <v>46.3</v>
@@ -3109,12 +3229,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3127,7 +3247,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.918987422654075</v>
+        <v>-4.916447656643863</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3136,7 +3256,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.3</v>
+        <v>153.1</v>
       </c>
       <c r="O8" t="n">
         <v>41.7</v>
@@ -3153,19 +3273,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>22.235</v>
+        <v>22.233</v>
       </c>
       <c r="T8" t="n">
-        <v>22.235</v>
+        <v>22.233</v>
       </c>
       <c r="U8" t="n">
-        <v>11.983</v>
+        <v>12.026</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.346</v>
+        <v>-0.343</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.018</v>
+        <v>-32.027</v>
       </c>
     </row>
     <row r="9">
@@ -3184,12 +3304,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3211,7 +3331,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3259,12 +3379,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3286,7 +3406,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.8</v>
+        <v>113.6</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3334,12 +3454,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3361,7 +3481,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179.7</v>
+        <v>179.4</v>
       </c>
       <c r="O11" t="n">
         <v>51.6</v>
@@ -3409,14 +3529,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>ENERY.IS, TKFEN.IS</t>
@@ -3424,7 +3544,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -3432,14 +3552,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>13.21172202743475</v>
+        <v>7.753001654720459</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3448,10 +3568,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="O12" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="P12" t="n">
         <v>6</v>
@@ -3471,13 +3591,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>47.21</v>
+        <v>40.112</v>
       </c>
       <c r="V12" t="n">
-        <v>57.75</v>
+        <v>50.144</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.078</v>
+        <v>-20.176</v>
       </c>
     </row>
     <row r="13">
@@ -3496,12 +3616,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3514,7 +3634,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K13" t="n">
-        <v>5.221741120755707</v>
+        <v>5.224085869864203</v>
       </c>
       <c r="L13" t="n">
         <v>28.4081875</v>
@@ -3523,7 +3643,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>44.7</v>
@@ -3546,13 +3666,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>217.753</v>
+        <v>214.628</v>
       </c>
       <c r="V13" t="n">
-        <v>111.966</v>
+        <v>111.971</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.933</v>
+        <v>-17.749</v>
       </c>
     </row>
     <row r="14">
@@ -3571,12 +3691,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3589,7 +3709,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K14" t="n">
-        <v>5.20067672820439</v>
+        <v>5.203021007916409</v>
       </c>
       <c r="L14" t="n">
         <v>32.3216328125</v>
@@ -3598,7 +3718,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>42.9</v>
@@ -3621,13 +3741,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>215.312</v>
+        <v>212.211</v>
       </c>
       <c r="V14" t="n">
-        <v>93.03</v>
+        <v>93.03400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.756</v>
+        <v>-17.574</v>
       </c>
     </row>
     <row r="16">
@@ -3772,12 +3892,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3790,7 +3910,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>5.221741120755707</v>
+        <v>5.224085869864203</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -3799,7 +3919,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>44.7</v>
@@ -3822,13 +3942,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>217.753</v>
+        <v>214.628</v>
       </c>
       <c r="V18" t="n">
-        <v>111.966</v>
+        <v>111.971</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.933</v>
+        <v>-17.749</v>
       </c>
     </row>
     <row r="19">
@@ -3849,12 +3969,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3876,7 +3996,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>120.1</v>
+        <v>119.9</v>
       </c>
       <c r="O19" t="n">
         <v>46.3</v>
@@ -3926,12 +4046,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3944,7 +4064,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>5.20067672820439</v>
+        <v>5.203021007916409</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -3953,7 +4073,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>42.9</v>
@@ -3976,13 +4096,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>215.312</v>
+        <v>212.211</v>
       </c>
       <c r="V20" t="n">
-        <v>93.03</v>
+        <v>93.03400000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-17.756</v>
+        <v>-17.574</v>
       </c>
     </row>
     <row r="21">
@@ -4003,12 +4123,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4030,7 +4150,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179.7</v>
+        <v>179.4</v>
       </c>
       <c r="O21" t="n">
         <v>51.6</v>
@@ -4080,14 +4200,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>CANTE.IS, ENERY.IS, FROTO.IS, SASA.IS, TKFEN.IS</t>
@@ -4095,7 +4215,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-17 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-18 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4103,14 +4223,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +16.71% / +22.32% / -0.50% | FROTO.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +18.21% / +22.32% / -0.50% | FROTO.IS: -2.11% / +0.36% / -2.60% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.94543585303989</v>
+        <v>-13.53028338591502</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4119,10 +4239,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>141.6</v>
+        <v>142.3</v>
       </c>
       <c r="O22" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="P22" t="n">
         <v>5.6</v>
@@ -4136,19 +4256,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.616</v>
+        <v>28.746</v>
       </c>
       <c r="T22" t="n">
-        <v>26.616</v>
+        <v>28.746</v>
       </c>
       <c r="U22" t="n">
-        <v>21.176</v>
+        <v>17.659</v>
       </c>
       <c r="V22" t="n">
-        <v>10.719</v>
+        <v>7.505</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.949</v>
+        <v>-47.466</v>
       </c>
     </row>
     <row r="23">
@@ -4169,12 +4289,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4187,7 +4307,7 @@
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.918987422654075</v>
+        <v>-4.916447656643863</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4196,7 +4316,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.3</v>
+        <v>153.1</v>
       </c>
       <c r="O23" t="n">
         <v>41.7</v>
@@ -4213,19 +4333,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>22.235</v>
+        <v>22.233</v>
       </c>
       <c r="T23" t="n">
-        <v>22.235</v>
+        <v>22.233</v>
       </c>
       <c r="U23" t="n">
-        <v>11.983</v>
+        <v>12.026</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.346</v>
+        <v>-0.343</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.018</v>
+        <v>-32.027</v>
       </c>
     </row>
     <row r="24">
@@ -4246,12 +4366,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4273,7 +4393,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>113.8</v>
+        <v>113.6</v>
       </c>
       <c r="O24" t="n">
         <v>50.2</v>
@@ -4323,12 +4443,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4350,7 +4470,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4400,14 +4520,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>ENERY.IS, TKFEN.IS</t>
@@ -4415,7 +4535,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-17 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4423,14 +4543,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +36.20% / +36.23% / -0.56%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>13.21172202743475</v>
+        <v>7.753001654720459</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4439,10 +4559,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="O26" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="P26" t="n">
         <v>6</v>
@@ -4462,13 +4582,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>47.21</v>
+        <v>40.112</v>
       </c>
       <c r="V26" t="n">
-        <v>57.75</v>
+        <v>50.144</v>
       </c>
       <c r="W26" t="n">
-        <v>-13.078</v>
+        <v>-20.176</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,8 +573,8 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -733,37 +733,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.736349403096511</v>
+        <v>-13.36833527599406</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O3" t="n">
         <v>42.9</v>
@@ -782,11 +770,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>23.832</v>
@@ -795,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>53.823</v>
+        <v>40.093</v>
       </c>
       <c r="V3" t="n">
-        <v>22.63</v>
+        <v>17.696</v>
       </c>
       <c r="W3" t="n">
-        <v>-29.949</v>
+        <v>-34.293</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +835,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +910,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,37 +958,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.736349403096511</v>
+        <v>-13.36833527599406</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,7 +985,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O6" t="n">
         <v>42.9</v>
@@ -1019,11 +995,11 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>23.832</v>
@@ -1032,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>53.823</v>
+        <v>40.093</v>
       </c>
       <c r="V6" t="n">
-        <v>22.63</v>
+        <v>17.696</v>
       </c>
       <c r="W6" t="n">
-        <v>-29.949</v>
+        <v>-34.293</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1084,7 +1060,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>135.5</v>
+        <v>135.2</v>
       </c>
       <c r="O7" t="n">
         <v>46.6</v>
@@ -1107,13 +1083,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>36.336</v>
+        <v>30.017</v>
       </c>
       <c r="V7" t="n">
         <v>24.076</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.644</v>
+        <v>-34.946</v>
       </c>
     </row>
     <row r="8">
@@ -1132,37 +1108,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS, TSKB.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18 | TSKB.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>60.64599942530686</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-18.31436051585953</v>
+        <v>-20.6059737083233</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1171,7 +1135,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>194.7</v>
+        <v>194.3</v>
       </c>
       <c r="O8" t="n">
         <v>46.1</v>
@@ -1181,26 +1145,26 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>19.595</v>
+        <v>21.851</v>
       </c>
       <c r="T8" t="n">
-        <v>19.595</v>
+        <v>21.851</v>
       </c>
       <c r="U8" t="n">
-        <v>38.859</v>
+        <v>30.029</v>
       </c>
       <c r="V8" t="n">
-        <v>8.454000000000001</v>
+        <v>5.411</v>
       </c>
       <c r="W8" t="n">
-        <v>-33.84</v>
+        <v>-36.356</v>
       </c>
     </row>
     <row r="9">
@@ -1219,37 +1183,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.736349403096511</v>
+        <v>-13.36833527599406</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1258,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O9" t="n">
         <v>42.9</v>
@@ -1268,11 +1220,11 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>23.832</v>
@@ -1281,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>53.823</v>
+        <v>40.093</v>
       </c>
       <c r="V9" t="n">
-        <v>22.63</v>
+        <v>17.696</v>
       </c>
       <c r="W9" t="n">
-        <v>-29.949</v>
+        <v>-34.293</v>
       </c>
     </row>
     <row r="10">
@@ -1306,22 +1258,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AKSA.IS, TKFEN.IS</t>
+          <t>ANSGR.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-09-18 | TKFEN.IS: 2026-09-16</t>
+          <t>ANSGR.IS: 2026-09-21 | SOKM.IS: 2026-09-21</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1329,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.28% / +14.51% / -1.02%</t>
+          <t>ANSGR.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.64412092898321</v>
+        <v>-6.98123765429175</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1345,10 +1297,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>177.7</v>
+        <v>178.3</v>
       </c>
       <c r="O10" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1368,13 +1320,13 @@
         <v>10.759</v>
       </c>
       <c r="U10" t="n">
-        <v>13.047</v>
+        <v>12.639</v>
       </c>
       <c r="V10" t="n">
-        <v>5.111</v>
+        <v>4.731</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.341</v>
+        <v>-12.749</v>
       </c>
     </row>
     <row r="11">
@@ -1393,12 +1345,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1420,7 +1372,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1468,12 +1420,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1495,7 +1447,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>45.3</v>
@@ -1543,37 +1495,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>12.71160720962683</v>
+        <v>8.176371127440474</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1582,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="O13" t="n">
         <v>44.1</v>
@@ -1592,11 +1532,11 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>25.345</v>
@@ -1605,13 +1545,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>94.628</v>
+        <v>86.797</v>
       </c>
       <c r="V13" t="n">
-        <v>107.68</v>
+        <v>99.32299999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-16.622</v>
+        <v>-24.453</v>
       </c>
     </row>
     <row r="14">
@@ -1630,37 +1570,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>12.71160720962683</v>
+        <v>8.176371127440474</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1669,7 +1597,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="O14" t="n">
         <v>44.1</v>
@@ -1679,11 +1607,11 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>25.345</v>
@@ -1692,13 +1620,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>94.628</v>
+        <v>86.797</v>
       </c>
       <c r="V14" t="n">
-        <v>107.68</v>
+        <v>99.32299999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-16.622</v>
+        <v>-24.453</v>
       </c>
     </row>
     <row r="16">
@@ -1843,37 +1771,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>111.9220744729613</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.736349403096511</v>
+        <v>-13.36833527599406</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1882,7 +1798,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O18" t="n">
         <v>42.9</v>
@@ -1892,11 +1808,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>23.832</v>
@@ -1905,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>53.823</v>
+        <v>40.093</v>
       </c>
       <c r="V18" t="n">
-        <v>22.63</v>
+        <v>17.696</v>
       </c>
       <c r="W18" t="n">
-        <v>-29.949</v>
+        <v>-34.293</v>
       </c>
     </row>
     <row r="19">
@@ -1932,12 +1848,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1959,7 +1875,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -2009,12 +1925,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2036,7 +1952,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2086,37 +2002,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS, TSKB.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18 | TSKB.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>60.64599942530686</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-18.31436051585953</v>
+        <v>-20.6059737083233</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2125,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>194.7</v>
+        <v>194.3</v>
       </c>
       <c r="O21" t="n">
         <v>46.1</v>
@@ -2135,26 +2039,26 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>19.595</v>
+        <v>21.851</v>
       </c>
       <c r="T21" t="n">
-        <v>19.595</v>
+        <v>21.851</v>
       </c>
       <c r="U21" t="n">
-        <v>38.859</v>
+        <v>30.029</v>
       </c>
       <c r="V21" t="n">
-        <v>8.454000000000001</v>
+        <v>5.411</v>
       </c>
       <c r="W21" t="n">
-        <v>-33.84</v>
+        <v>-36.356</v>
       </c>
     </row>
     <row r="22">
@@ -2175,12 +2079,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2202,7 +2106,7 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>135.5</v>
+        <v>135.2</v>
       </c>
       <c r="O22" t="n">
         <v>46.6</v>
@@ -2225,13 +2129,13 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>36.336</v>
+        <v>30.017</v>
       </c>
       <c r="V22" t="n">
         <v>24.076</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.644</v>
+        <v>-34.946</v>
       </c>
     </row>
     <row r="23">
@@ -2252,37 +2156,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>12.71160720962683</v>
+        <v>8.176371127440474</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2291,7 +2183,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="O23" t="n">
         <v>44.1</v>
@@ -2301,11 +2193,11 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>25.345</v>
@@ -2314,13 +2206,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>94.628</v>
+        <v>86.797</v>
       </c>
       <c r="V23" t="n">
-        <v>107.68</v>
+        <v>99.32299999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-16.622</v>
+        <v>-24.453</v>
       </c>
     </row>
     <row r="24">
@@ -2341,37 +2233,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-09-18</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>55.72500398673659</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>12.71160720962683</v>
+        <v>8.176371127440474</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2380,7 +2260,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="O24" t="n">
         <v>44.1</v>
@@ -2390,11 +2270,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>25.345</v>
@@ -2403,13 +2283,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>94.628</v>
+        <v>86.797</v>
       </c>
       <c r="V24" t="n">
-        <v>107.68</v>
+        <v>99.32299999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>-16.622</v>
+        <v>-24.453</v>
       </c>
     </row>
     <row r="25">
@@ -2430,12 +2310,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2457,7 +2337,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2507,22 +2387,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AKSA.IS, TKFEN.IS</t>
+          <t>ANSGR.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-09-18 | TKFEN.IS: 2026-09-16</t>
+          <t>ANSGR.IS: 2026-09-21 | SOKM.IS: 2026-09-21</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2530,14 +2410,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +4.28% / +14.51% / -1.02%</t>
+          <t>ANSGR.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.64412092898321</v>
+        <v>-6.98123765429175</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2546,10 +2426,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>177.7</v>
+        <v>178.3</v>
       </c>
       <c r="O26" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2569,13 +2449,13 @@
         <v>10.759</v>
       </c>
       <c r="U26" t="n">
-        <v>13.047</v>
+        <v>12.639</v>
       </c>
       <c r="V26" t="n">
-        <v>5.111</v>
+        <v>4.731</v>
       </c>
       <c r="W26" t="n">
-        <v>-12.341</v>
+        <v>-12.749</v>
       </c>
     </row>
     <row r="27">
@@ -2596,12 +2476,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2623,7 +2503,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N27" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>45.3</v>
@@ -2842,12 +2722,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2869,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>44.7</v>
@@ -2892,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>214.628</v>
+        <v>206.171</v>
       </c>
       <c r="V3" t="n">
         <v>111.971</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.749</v>
+        <v>-17.272</v>
       </c>
     </row>
     <row r="4">
@@ -2917,12 +2797,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2944,7 +2824,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.9</v>
+        <v>119.7</v>
       </c>
       <c r="O4" t="n">
         <v>46.3</v>
@@ -2992,12 +2872,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -3019,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="O5" t="n">
         <v>42.9</v>
@@ -3042,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>212.211</v>
+        <v>203.819</v>
       </c>
       <c r="V5" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-17.574</v>
+        <v>-17.102</v>
       </c>
     </row>
     <row r="6">
@@ -3067,22 +2947,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, FROTO.IS, SASA.IS, TKFEN.IS</t>
+          <t>ENERY.IS, FROTO.IS, SASA.IS, SOKM.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-18 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-21 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3090,14 +2970,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +18.21% / +22.32% / -0.50% | FROTO.IS: -2.11% / +0.36% / -2.60% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
+          <t>ENERY.IS: +10.97% / +22.32% / -0.50% | FROTO.IS: +0.09% / +0.35% / -3.43% | SASA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +25.78% / +41.58% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-13.53028338591502</v>
+        <v>-16.98374175985802</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3106,10 +2986,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>142.3</v>
+        <v>143</v>
       </c>
       <c r="O6" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="P6" t="n">
         <v>5.6</v>
@@ -3123,19 +3003,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>28.746</v>
+        <v>31.591</v>
       </c>
       <c r="T6" t="n">
-        <v>28.746</v>
+        <v>31.591</v>
       </c>
       <c r="U6" t="n">
-        <v>17.659</v>
+        <v>12.959</v>
       </c>
       <c r="V6" t="n">
-        <v>7.505</v>
+        <v>3.211</v>
       </c>
       <c r="W6" t="n">
-        <v>-47.466</v>
+        <v>-52.165</v>
       </c>
     </row>
     <row r="7">
@@ -3154,12 +3034,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3181,7 +3061,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.9</v>
+        <v>119.7</v>
       </c>
       <c r="O7" t="n">
         <v>46.3</v>
@@ -3229,12 +3109,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3256,7 +3136,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.1</v>
+        <v>152.8</v>
       </c>
       <c r="O8" t="n">
         <v>41.7</v>
@@ -3279,13 +3159,13 @@
         <v>22.233</v>
       </c>
       <c r="U8" t="n">
-        <v>12.026</v>
+        <v>11.167</v>
       </c>
       <c r="V8" t="n">
         <v>-0.343</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.027</v>
+        <v>-31.781</v>
       </c>
     </row>
     <row r="9">
@@ -3304,12 +3184,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3331,7 +3211,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3379,12 +3259,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3406,7 +3286,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.6</v>
+        <v>113.4</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3454,12 +3334,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3481,7 +3361,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179.4</v>
+        <v>179</v>
       </c>
       <c r="O11" t="n">
         <v>51.6</v>
@@ -3524,80 +3404,68 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>6.880672511445463</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
-        </is>
-      </c>
+        <v>56.41058954395304</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-18.9000927288166</v>
+        <v>4.833271170608744</v>
       </c>
       <c r="K12" t="n">
-        <v>7.753001654720459</v>
+        <v>7.573509780159249</v>
       </c>
       <c r="L12" t="n">
-        <v>31.31195090134997</v>
+        <v>22.230015625</v>
       </c>
       <c r="M12" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>49.2</v>
+        <v>79.3</v>
       </c>
       <c r="O12" t="n">
-        <v>41.6</v>
+        <v>42.3</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>28.439</v>
+        <v>27.463</v>
       </c>
       <c r="T12" t="n">
-        <v>28.439</v>
+        <v>27.463</v>
       </c>
       <c r="U12" t="n">
-        <v>40.112</v>
+        <v>21.484</v>
       </c>
       <c r="V12" t="n">
-        <v>50.144</v>
+        <v>36.442</v>
       </c>
       <c r="W12" t="n">
-        <v>-20.176</v>
+        <v>-15.851</v>
       </c>
     </row>
     <row r="13">
@@ -3616,12 +3484,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3643,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>92.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>44.7</v>
@@ -3666,13 +3534,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>214.628</v>
+        <v>206.171</v>
       </c>
       <c r="V13" t="n">
         <v>111.971</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.749</v>
+        <v>-17.272</v>
       </c>
     </row>
     <row r="14">
@@ -3691,12 +3559,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3718,7 +3586,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="O14" t="n">
         <v>42.9</v>
@@ -3741,13 +3609,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>212.211</v>
+        <v>203.819</v>
       </c>
       <c r="V14" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.574</v>
+        <v>-17.102</v>
       </c>
     </row>
     <row r="16">
@@ -3892,12 +3760,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3919,7 +3787,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>44.7</v>
@@ -3942,13 +3810,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>214.628</v>
+        <v>206.171</v>
       </c>
       <c r="V18" t="n">
         <v>111.971</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.749</v>
+        <v>-17.272</v>
       </c>
     </row>
     <row r="19">
@@ -3969,12 +3837,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3996,7 +3864,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.9</v>
+        <v>119.7</v>
       </c>
       <c r="O19" t="n">
         <v>46.3</v>
@@ -4046,12 +3914,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4073,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="O20" t="n">
         <v>42.9</v>
@@ -4096,13 +3964,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>212.211</v>
+        <v>203.819</v>
       </c>
       <c r="V20" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-17.574</v>
+        <v>-17.102</v>
       </c>
     </row>
     <row r="21">
@@ -4123,12 +3991,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4150,7 +4018,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179.4</v>
+        <v>179</v>
       </c>
       <c r="O21" t="n">
         <v>51.6</v>
@@ -4200,22 +4068,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANTE.IS, ENERY.IS, FROTO.IS, SASA.IS, TKFEN.IS</t>
+          <t>ENERY.IS, FROTO.IS, SASA.IS, SOKM.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-18 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
+          <t>ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-21 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4223,14 +4091,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +18.21% / +22.32% / -0.50% | FROTO.IS: -2.11% / +0.36% / -2.60% | SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
+          <t>ENERY.IS: +10.97% / +22.32% / -0.50% | FROTO.IS: +0.09% / +0.35% / -3.43% | SASA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +25.78% / +41.58% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-13.53028338591502</v>
+        <v>-16.98374175985802</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4239,10 +4107,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>142.3</v>
+        <v>143</v>
       </c>
       <c r="O22" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="P22" t="n">
         <v>5.6</v>
@@ -4256,73 +4124,73 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>28.746</v>
+        <v>31.591</v>
       </c>
       <c r="T22" t="n">
-        <v>28.746</v>
+        <v>31.591</v>
       </c>
       <c r="U22" t="n">
-        <v>17.659</v>
+        <v>12.959</v>
       </c>
       <c r="V22" t="n">
-        <v>7.505</v>
+        <v>3.211</v>
       </c>
       <c r="W22" t="n">
-        <v>-47.466</v>
+        <v>-52.165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>48.21914524341393</v>
+        <v>56.41058954395304</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>21.4002873140223</v>
+        <v>4.833271170608744</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.916447656643863</v>
+        <v>7.573509780159249</v>
       </c>
       <c r="L23" t="n">
-        <v>16.16102048107813</v>
+        <v>22.230015625</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.1</v>
+        <v>79.3</v>
       </c>
       <c r="O23" t="n">
-        <v>41.7</v>
+        <v>42.3</v>
       </c>
       <c r="P23" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4333,73 +4201,73 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>22.233</v>
+        <v>27.463</v>
       </c>
       <c r="T23" t="n">
-        <v>22.233</v>
+        <v>27.463</v>
       </c>
       <c r="U23" t="n">
-        <v>12.026</v>
+        <v>21.484</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.343</v>
+        <v>36.442</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.027</v>
+        <v>-15.851</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T2_rotasyon|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>38.04089454478734</v>
+        <v>48.21914524341393</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>13.75066280702224</v>
+        <v>21.4002873140223</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.87783925866676</v>
+        <v>-4.916447656643863</v>
       </c>
       <c r="L24" t="n">
-        <v>5.808640829284117</v>
+        <v>16.16102048107813</v>
       </c>
       <c r="M24" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>113.6</v>
+        <v>152.8</v>
       </c>
       <c r="O24" t="n">
-        <v>50.2</v>
+        <v>41.7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4410,19 +4278,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>20.416</v>
+        <v>22.233</v>
       </c>
       <c r="T24" t="n">
-        <v>20.416</v>
+        <v>22.233</v>
       </c>
       <c r="U24" t="n">
-        <v>9.715</v>
+        <v>11.167</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.303</v>
+        <v>-0.343</v>
       </c>
       <c r="W24" t="n">
-        <v>-28.145</v>
+        <v>-31.781</v>
       </c>
     </row>
     <row r="25">
@@ -4433,50 +4301,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>28.40086810394897</v>
+        <v>38.04089454478734</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>15.38514121842653</v>
+        <v>13.75066280702224</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.616392554049999</v>
+        <v>-3.87783925866676</v>
       </c>
       <c r="L25" t="n">
-        <v>5.127814043936619</v>
+        <v>5.808640829284117</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>74.09999999999999</v>
+        <v>113.4</v>
       </c>
       <c r="O25" t="n">
-        <v>49.3</v>
+        <v>50.2</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4487,25 +4355,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>13.28</v>
+        <v>20.416</v>
       </c>
       <c r="T25" t="n">
-        <v>13.28</v>
+        <v>20.416</v>
       </c>
       <c r="U25" t="n">
-        <v>7.136</v>
+        <v>9.715</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.962</v>
+        <v>-3.303</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.407</v>
+        <v>-28.145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4515,80 +4383,68 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ENERY.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ENERY.IS: 2026-09-18 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>6.880672511445463</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +28.96% / +41.60% / -0.56%</t>
-        </is>
-      </c>
+        <v>28.40086810394897</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>-18.9000927288166</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K26" t="n">
-        <v>7.753001654720459</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L26" t="n">
-        <v>31.31195090134997</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M26" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>49.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>41.6</v>
+        <v>49.3</v>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>28.439</v>
+        <v>13.28</v>
       </c>
       <c r="T26" t="n">
-        <v>28.439</v>
+        <v>13.28</v>
       </c>
       <c r="U26" t="n">
-        <v>40.112</v>
+        <v>7.136</v>
       </c>
       <c r="V26" t="n">
-        <v>50.144</v>
+        <v>-0.962</v>
       </c>
       <c r="W26" t="n">
-        <v>-20.176</v>
+        <v>-16.407</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -751,7 +751,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.36833527599406</v>
+        <v>-13.34725655380041</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -783,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>40.093</v>
+        <v>40.127</v>
       </c>
       <c r="V3" t="n">
-        <v>17.696</v>
+        <v>17.724</v>
       </c>
       <c r="W3" t="n">
-        <v>-34.293</v>
+        <v>-34.259</v>
       </c>
     </row>
     <row r="4">
@@ -976,7 +976,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-13.36833527599406</v>
+        <v>-13.34725655380041</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1008,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>40.093</v>
+        <v>40.127</v>
       </c>
       <c r="V6" t="n">
-        <v>17.696</v>
+        <v>17.724</v>
       </c>
       <c r="W6" t="n">
-        <v>-34.293</v>
+        <v>-34.259</v>
       </c>
     </row>
     <row r="7">
@@ -1126,7 +1126,7 @@
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-20.6059737083233</v>
+        <v>-20.54316722283934</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1152,19 +1152,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>21.851</v>
+        <v>21.789</v>
       </c>
       <c r="T8" t="n">
-        <v>21.851</v>
+        <v>21.789</v>
       </c>
       <c r="U8" t="n">
-        <v>30.029</v>
+        <v>30.132</v>
       </c>
       <c r="V8" t="n">
-        <v>5.411</v>
+        <v>5.494</v>
       </c>
       <c r="W8" t="n">
-        <v>-36.356</v>
+        <v>-36.254</v>
       </c>
     </row>
     <row r="9">
@@ -1201,7 +1201,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-13.36833527599406</v>
+        <v>-13.34725655380041</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1233,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>40.093</v>
+        <v>40.127</v>
       </c>
       <c r="V9" t="n">
-        <v>17.696</v>
+        <v>17.724</v>
       </c>
       <c r="W9" t="n">
-        <v>-34.293</v>
+        <v>-34.259</v>
       </c>
     </row>
     <row r="10">
@@ -1288,7 +1288,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.98123765429175</v>
+        <v>-7.047577580992026</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1320,13 +1320,13 @@
         <v>10.759</v>
       </c>
       <c r="U10" t="n">
-        <v>12.639</v>
+        <v>12.558</v>
       </c>
       <c r="V10" t="n">
-        <v>4.731</v>
+        <v>4.657</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.749</v>
+        <v>-12.83</v>
       </c>
     </row>
     <row r="11">
@@ -1513,7 +1513,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K13" t="n">
-        <v>8.176371127440474</v>
+        <v>8.20269198462562</v>
       </c>
       <c r="L13" t="n">
         <v>22.73189287884475</v>
@@ -1545,13 +1545,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>86.797</v>
+        <v>86.842</v>
       </c>
       <c r="V13" t="n">
-        <v>99.32299999999999</v>
+        <v>99.372</v>
       </c>
       <c r="W13" t="n">
-        <v>-24.453</v>
+        <v>-24.408</v>
       </c>
     </row>
     <row r="14">
@@ -1588,7 +1588,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>8.176371127440474</v>
+        <v>8.20269198462562</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1620,13 +1620,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>86.797</v>
+        <v>86.842</v>
       </c>
       <c r="V14" t="n">
-        <v>99.32299999999999</v>
+        <v>99.372</v>
       </c>
       <c r="W14" t="n">
-        <v>-24.453</v>
+        <v>-24.408</v>
       </c>
     </row>
     <row r="16">
@@ -1789,7 +1789,7 @@
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.36833527599406</v>
+        <v>-13.34725655380041</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1821,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>40.093</v>
+        <v>40.127</v>
       </c>
       <c r="V18" t="n">
-        <v>17.696</v>
+        <v>17.724</v>
       </c>
       <c r="W18" t="n">
-        <v>-34.293</v>
+        <v>-34.259</v>
       </c>
     </row>
     <row r="19">
@@ -2020,7 +2020,7 @@
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.6059737083233</v>
+        <v>-20.54316722283934</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2046,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>21.851</v>
+        <v>21.789</v>
       </c>
       <c r="T21" t="n">
-        <v>21.851</v>
+        <v>21.789</v>
       </c>
       <c r="U21" t="n">
-        <v>30.029</v>
+        <v>30.132</v>
       </c>
       <c r="V21" t="n">
-        <v>5.411</v>
+        <v>5.494</v>
       </c>
       <c r="W21" t="n">
-        <v>-36.356</v>
+        <v>-36.254</v>
       </c>
     </row>
     <row r="22">
@@ -2174,7 +2174,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>8.176371127440474</v>
+        <v>8.20269198462562</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2206,13 +2206,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>86.797</v>
+        <v>86.842</v>
       </c>
       <c r="V23" t="n">
-        <v>99.32299999999999</v>
+        <v>99.372</v>
       </c>
       <c r="W23" t="n">
-        <v>-24.453</v>
+        <v>-24.408</v>
       </c>
     </row>
     <row r="24">
@@ -2251,7 +2251,7 @@
         <v>-8.265155599016705</v>
       </c>
       <c r="K24" t="n">
-        <v>8.176371127440474</v>
+        <v>8.20269198462562</v>
       </c>
       <c r="L24" t="n">
         <v>22.73189287884475</v>
@@ -2283,13 +2283,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>86.797</v>
+        <v>86.842</v>
       </c>
       <c r="V24" t="n">
-        <v>99.32299999999999</v>
+        <v>99.372</v>
       </c>
       <c r="W24" t="n">
-        <v>-24.453</v>
+        <v>-24.408</v>
       </c>
     </row>
     <row r="25">
@@ -2417,7 +2417,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.98123765429175</v>
+        <v>-7.047577580992026</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2449,13 +2449,13 @@
         <v>10.759</v>
       </c>
       <c r="U26" t="n">
-        <v>12.639</v>
+        <v>12.558</v>
       </c>
       <c r="V26" t="n">
-        <v>4.731</v>
+        <v>4.657</v>
       </c>
       <c r="W26" t="n">
-        <v>-12.749</v>
+        <v>-12.83</v>
       </c>
     </row>
     <row r="27">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENERY.IS, FROTO.IS, SASA.IS, SOKM.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, FROTO.IS, SOKM.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-21 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-21 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2970,14 +2970,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.97% / +22.32% / -0.50% | FROTO.IS: +0.09% / +0.35% / -3.43% | SASA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +25.78% / +41.58% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.87% / +22.32% / -0.50% | FROTO.IS: +0.23% / +0.36% / -3.42% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +26.00% / +41.59% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.98374175985802</v>
+        <v>-16.63619973832206</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3003,19 +3003,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>31.591</v>
+        <v>31.305</v>
       </c>
       <c r="T6" t="n">
-        <v>31.591</v>
+        <v>31.305</v>
       </c>
       <c r="U6" t="n">
-        <v>12.959</v>
+        <v>13.432</v>
       </c>
       <c r="V6" t="n">
-        <v>3.211</v>
+        <v>3.643</v>
       </c>
       <c r="W6" t="n">
-        <v>-52.165</v>
+        <v>-51.692</v>
       </c>
     </row>
     <row r="7">
@@ -4078,12 +4078,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENERY.IS, FROTO.IS, SASA.IS, SOKM.IS, TKFEN.IS</t>
+          <t>CANTE.IS, ENERY.IS, FROTO.IS, SOKM.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SASA.IS: 2026-09-21 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
+          <t>CANTE.IS: 2026-09-21 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ENERY.IS: +10.97% / +22.32% / -0.50% | FROTO.IS: +0.09% / +0.35% / -3.43% | SASA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +25.78% / +41.58% / -0.56%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.87% / +22.32% / -0.50% | FROTO.IS: +0.23% / +0.36% / -3.42% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +26.00% / +41.59% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-16.98374175985802</v>
+        <v>-16.63619973832206</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4124,19 +4124,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>31.591</v>
+        <v>31.305</v>
       </c>
       <c r="T22" t="n">
-        <v>31.591</v>
+        <v>31.305</v>
       </c>
       <c r="U22" t="n">
-        <v>12.959</v>
+        <v>13.432</v>
       </c>
       <c r="V22" t="n">
-        <v>3.211</v>
+        <v>3.643</v>
       </c>
       <c r="W22" t="n">
-        <v>-52.165</v>
+        <v>-51.692</v>
       </c>
     </row>
     <row r="23">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,8 +573,8 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O3" t="n">
         <v>42.9</v>
@@ -783,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>40.127</v>
+        <v>40.257</v>
       </c>
       <c r="V3" t="n">
         <v>17.724</v>
       </c>
       <c r="W3" t="n">
-        <v>-34.259</v>
+        <v>-34.291</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -858,13 +858,13 @@
         <v>21.057</v>
       </c>
       <c r="U4" t="n">
-        <v>152.823</v>
+        <v>152.873</v>
       </c>
       <c r="V4" t="n">
         <v>111.543</v>
       </c>
       <c r="W4" t="n">
-        <v>-12.802</v>
+        <v>-12.804</v>
       </c>
     </row>
     <row r="5">
@@ -883,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -933,13 +933,13 @@
         <v>19.637</v>
       </c>
       <c r="U5" t="n">
-        <v>117.451</v>
+        <v>117.494</v>
       </c>
       <c r="V5" t="n">
         <v>117.535</v>
       </c>
       <c r="W5" t="n">
-        <v>-16.188</v>
+        <v>-16.191</v>
       </c>
     </row>
     <row r="6">
@@ -958,12 +958,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O6" t="n">
         <v>42.9</v>
@@ -1008,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>40.127</v>
+        <v>40.257</v>
       </c>
       <c r="V6" t="n">
         <v>17.724</v>
       </c>
       <c r="W6" t="n">
-        <v>-34.259</v>
+        <v>-34.291</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>135.2</v>
+        <v>134.9</v>
       </c>
       <c r="O7" t="n">
         <v>46.6</v>
@@ -1083,13 +1083,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>30.017</v>
+        <v>29.285</v>
       </c>
       <c r="V7" t="n">
         <v>24.076</v>
       </c>
       <c r="W7" t="n">
-        <v>-34.946</v>
+        <v>-34.749</v>
       </c>
     </row>
     <row r="8">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>194.3</v>
+        <v>194</v>
       </c>
       <c r="O8" t="n">
         <v>46.1</v>
@@ -1158,13 +1158,13 @@
         <v>21.789</v>
       </c>
       <c r="U8" t="n">
-        <v>30.132</v>
+        <v>29.333</v>
       </c>
       <c r="V8" t="n">
         <v>5.494</v>
       </c>
       <c r="W8" t="n">
-        <v>-36.254</v>
+        <v>-36.031</v>
       </c>
     </row>
     <row r="9">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O9" t="n">
         <v>42.9</v>
@@ -1233,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>40.127</v>
+        <v>40.257</v>
       </c>
       <c r="V9" t="n">
         <v>17.724</v>
       </c>
       <c r="W9" t="n">
-        <v>-34.259</v>
+        <v>-34.291</v>
       </c>
     </row>
     <row r="10">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ANSGR.IS, SOKM.IS</t>
+          <t>ANSGR.IS, KRDMD.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ANSGR.IS: 2026-09-21 | SOKM.IS: 2026-09-21</t>
+          <t>ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ANSGR.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ANSGR.IS: -2.76% / +0.00% / -2.82% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.81% / +1.96% / -1.88%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.047577580992026</v>
+        <v>-7.897913041213823</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1297,10 +1297,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>178.3</v>
+        <v>178.5</v>
       </c>
       <c r="O10" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1311,22 +1311,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>10.759</v>
+        <v>11.053</v>
       </c>
       <c r="T10" t="n">
-        <v>10.759</v>
+        <v>11.053</v>
       </c>
       <c r="U10" t="n">
-        <v>12.558</v>
+        <v>11.529</v>
       </c>
       <c r="V10" t="n">
-        <v>4.657</v>
+        <v>3.699</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.83</v>
+        <v>-13.859</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1395,7 +1395,7 @@
         <v>7.033</v>
       </c>
       <c r="U11" t="n">
-        <v>85.90600000000001</v>
+        <v>85.934</v>
       </c>
       <c r="V11" t="n">
         <v>58.898</v>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>67.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="O12" t="n">
         <v>45.3</v>
@@ -1470,13 +1470,13 @@
         <v>24.573</v>
       </c>
       <c r="U12" t="n">
-        <v>5.724</v>
+        <v>5.735</v>
       </c>
       <c r="V12" t="n">
         <v>18.367</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.728</v>
+        <v>-17.73</v>
       </c>
     </row>
     <row r="13">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="O13" t="n">
         <v>44.1</v>
@@ -1545,13 +1545,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>86.842</v>
+        <v>86.879</v>
       </c>
       <c r="V13" t="n">
         <v>99.372</v>
       </c>
       <c r="W13" t="n">
-        <v>-24.408</v>
+        <v>-24.413</v>
       </c>
     </row>
     <row r="14">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="O14" t="n">
         <v>44.1</v>
@@ -1620,13 +1620,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>86.842</v>
+        <v>86.879</v>
       </c>
       <c r="V14" t="n">
         <v>99.372</v>
       </c>
       <c r="W14" t="n">
-        <v>-24.408</v>
+        <v>-24.413</v>
       </c>
     </row>
     <row r="16">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O18" t="n">
         <v>42.9</v>
@@ -1821,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>40.127</v>
+        <v>40.257</v>
       </c>
       <c r="V18" t="n">
         <v>17.724</v>
       </c>
       <c r="W18" t="n">
-        <v>-34.259</v>
+        <v>-34.291</v>
       </c>
     </row>
     <row r="19">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1898,13 +1898,13 @@
         <v>21.057</v>
       </c>
       <c r="U19" t="n">
-        <v>152.823</v>
+        <v>152.873</v>
       </c>
       <c r="V19" t="n">
         <v>111.543</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.802</v>
+        <v>-12.804</v>
       </c>
     </row>
     <row r="20">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1952,7 +1952,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -1975,13 +1975,13 @@
         <v>19.637</v>
       </c>
       <c r="U20" t="n">
-        <v>117.451</v>
+        <v>117.494</v>
       </c>
       <c r="V20" t="n">
         <v>117.535</v>
       </c>
       <c r="W20" t="n">
-        <v>-16.188</v>
+        <v>-16.191</v>
       </c>
     </row>
     <row r="21">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>194.3</v>
+        <v>194</v>
       </c>
       <c r="O21" t="n">
         <v>46.1</v>
@@ -2052,13 +2052,13 @@
         <v>21.789</v>
       </c>
       <c r="U21" t="n">
-        <v>30.132</v>
+        <v>29.333</v>
       </c>
       <c r="V21" t="n">
         <v>5.494</v>
       </c>
       <c r="W21" t="n">
-        <v>-36.254</v>
+        <v>-36.031</v>
       </c>
     </row>
     <row r="22">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>135.2</v>
+        <v>134.9</v>
       </c>
       <c r="O22" t="n">
         <v>46.6</v>
@@ -2129,13 +2129,13 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>30.017</v>
+        <v>29.285</v>
       </c>
       <c r="V22" t="n">
         <v>24.076</v>
       </c>
       <c r="W22" t="n">
-        <v>-34.946</v>
+        <v>-34.749</v>
       </c>
     </row>
     <row r="23">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="O23" t="n">
         <v>44.1</v>
@@ -2206,13 +2206,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>86.842</v>
+        <v>86.879</v>
       </c>
       <c r="V23" t="n">
         <v>99.372</v>
       </c>
       <c r="W23" t="n">
-        <v>-24.408</v>
+        <v>-24.413</v>
       </c>
     </row>
     <row r="24">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="O24" t="n">
         <v>44.1</v>
@@ -2283,13 +2283,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>86.842</v>
+        <v>86.879</v>
       </c>
       <c r="V24" t="n">
         <v>99.372</v>
       </c>
       <c r="W24" t="n">
-        <v>-24.408</v>
+        <v>-24.413</v>
       </c>
     </row>
     <row r="25">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2360,7 +2360,7 @@
         <v>7.033</v>
       </c>
       <c r="U25" t="n">
-        <v>85.90600000000001</v>
+        <v>85.934</v>
       </c>
       <c r="V25" t="n">
         <v>58.898</v>
@@ -2387,22 +2387,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANSGR.IS, SOKM.IS</t>
+          <t>ANSGR.IS, KRDMD.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ANSGR.IS: 2026-09-21 | SOKM.IS: 2026-09-21</t>
+          <t>ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2410,14 +2410,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ANSGR.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ANSGR.IS: -2.76% / +0.00% / -2.82% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.81% / +1.96% / -1.88%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.047577580992026</v>
+        <v>-7.897913041213823</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2426,10 +2426,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>178.3</v>
+        <v>178.5</v>
       </c>
       <c r="O26" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2440,22 +2440,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>10.759</v>
+        <v>11.053</v>
       </c>
       <c r="T26" t="n">
-        <v>10.759</v>
+        <v>11.053</v>
       </c>
       <c r="U26" t="n">
-        <v>12.558</v>
+        <v>11.529</v>
       </c>
       <c r="V26" t="n">
-        <v>4.657</v>
+        <v>3.699</v>
       </c>
       <c r="W26" t="n">
-        <v>-12.83</v>
+        <v>-13.859</v>
       </c>
     </row>
     <row r="27">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2503,7 +2503,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N27" t="n">
-        <v>67.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="O27" t="n">
         <v>45.3</v>
@@ -2526,13 +2526,13 @@
         <v>24.573</v>
       </c>
       <c r="U27" t="n">
-        <v>5.724</v>
+        <v>5.735</v>
       </c>
       <c r="V27" t="n">
         <v>18.367</v>
       </c>
       <c r="W27" t="n">
-        <v>-17.728</v>
+        <v>-17.73</v>
       </c>
     </row>
   </sheetData>
@@ -2562,7 +2562,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="O3" t="n">
         <v>44.7</v>
@@ -2772,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>206.171</v>
+        <v>208.639</v>
       </c>
       <c r="V3" t="n">
         <v>111.971</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.272</v>
+        <v>-17.411</v>
       </c>
     </row>
     <row r="4">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.7</v>
+        <v>119.4</v>
       </c>
       <c r="O4" t="n">
         <v>46.3</v>
@@ -2847,13 +2847,13 @@
         <v>27.276</v>
       </c>
       <c r="U4" t="n">
-        <v>55.182</v>
+        <v>55.213</v>
       </c>
       <c r="V4" t="n">
         <v>17.234</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.204</v>
+        <v>-58.216</v>
       </c>
     </row>
     <row r="5">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>42.9</v>
@@ -2922,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>203.819</v>
+        <v>206.268</v>
       </c>
       <c r="V5" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-17.102</v>
+        <v>-17.24</v>
       </c>
     </row>
     <row r="6">
@@ -2947,37 +2947,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CANTE.IS, ENERY.IS, FROTO.IS, SOKM.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CANTE.IS: 2026-09-21 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>60.21035987359713</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.87% / +22.32% / -0.50% | FROTO.IS: +0.23% / +0.36% / -3.42% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +26.00% / +41.59% / -0.56%</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.63619973832206</v>
+        <v>-14.37863173570025</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -2986,36 +2974,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>143</v>
+        <v>142.8</v>
       </c>
       <c r="O6" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="P6" t="n">
         <v>5.6</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>31.305</v>
+        <v>31.29</v>
       </c>
       <c r="T6" t="n">
-        <v>31.305</v>
+        <v>31.29</v>
       </c>
       <c r="U6" t="n">
-        <v>13.432</v>
+        <v>16.504</v>
       </c>
       <c r="V6" t="n">
-        <v>3.643</v>
+        <v>6.45</v>
       </c>
       <c r="W6" t="n">
-        <v>-51.692</v>
+        <v>-48.62</v>
       </c>
     </row>
     <row r="7">
@@ -3034,12 +3022,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3061,7 +3049,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.7</v>
+        <v>119.4</v>
       </c>
       <c r="O7" t="n">
         <v>46.3</v>
@@ -3084,13 +3072,13 @@
         <v>27.276</v>
       </c>
       <c r="U7" t="n">
-        <v>55.182</v>
+        <v>55.213</v>
       </c>
       <c r="V7" t="n">
         <v>17.234</v>
       </c>
       <c r="W7" t="n">
-        <v>-58.204</v>
+        <v>-58.216</v>
       </c>
     </row>
     <row r="8">
@@ -3109,12 +3097,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3136,7 +3124,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>152.8</v>
+        <v>152.5</v>
       </c>
       <c r="O8" t="n">
         <v>41.7</v>
@@ -3159,13 +3147,13 @@
         <v>22.233</v>
       </c>
       <c r="U8" t="n">
-        <v>11.167</v>
+        <v>12.505</v>
       </c>
       <c r="V8" t="n">
         <v>-0.343</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.781</v>
+        <v>-32.164</v>
       </c>
     </row>
     <row r="9">
@@ -3184,12 +3172,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3211,7 +3199,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3234,13 +3222,13 @@
         <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>7.136</v>
+        <v>7.15</v>
       </c>
       <c r="V9" t="n">
         <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.407</v>
+        <v>-16.409</v>
       </c>
     </row>
     <row r="10">
@@ -3259,12 +3247,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3286,7 +3274,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.4</v>
+        <v>113.1</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3309,13 +3297,13 @@
         <v>20.416</v>
       </c>
       <c r="U10" t="n">
-        <v>9.715</v>
+        <v>9.731</v>
       </c>
       <c r="V10" t="n">
         <v>-3.303</v>
       </c>
       <c r="W10" t="n">
-        <v>-28.145</v>
+        <v>-28.149</v>
       </c>
     </row>
     <row r="11">
@@ -3334,12 +3322,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3361,7 +3349,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179</v>
+        <v>178.7</v>
       </c>
       <c r="O11" t="n">
         <v>51.6</v>
@@ -3384,13 +3372,13 @@
         <v>25.989</v>
       </c>
       <c r="U11" t="n">
-        <v>31.497</v>
+        <v>31.523</v>
       </c>
       <c r="V11" t="n">
         <v>4.588</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.176</v>
+        <v>-46.185</v>
       </c>
     </row>
     <row r="12">
@@ -3404,68 +3392,80 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>56.41058954395304</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>6.880672511445463</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ENERY.IS: +6.85% / +7.15% / 0.00% | TKFEN.IS: +27.84% / +41.59% / -0.56%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>4.833271170608744</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>7.573509780159249</v>
+        <v>8.265188588468519</v>
       </c>
       <c r="L12" t="n">
-        <v>22.230015625</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>79.3</v>
+        <v>49.5</v>
       </c>
       <c r="O12" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="P12" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>27.463</v>
+        <v>28.439</v>
       </c>
       <c r="T12" t="n">
-        <v>27.463</v>
+        <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>21.484</v>
+        <v>40.778</v>
       </c>
       <c r="V12" t="n">
-        <v>36.442</v>
+        <v>50.857</v>
       </c>
       <c r="W12" t="n">
-        <v>-15.851</v>
+        <v>-19.51</v>
       </c>
     </row>
     <row r="13">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3511,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>92.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="O13" t="n">
         <v>44.7</v>
@@ -3534,13 +3534,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>206.171</v>
+        <v>208.639</v>
       </c>
       <c r="V13" t="n">
         <v>111.971</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.272</v>
+        <v>-17.411</v>
       </c>
     </row>
     <row r="14">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>42.9</v>
@@ -3609,13 +3609,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>203.819</v>
+        <v>206.268</v>
       </c>
       <c r="V14" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.102</v>
+        <v>-17.24</v>
       </c>
     </row>
     <row r="16">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="O18" t="n">
         <v>44.7</v>
@@ -3810,13 +3810,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>206.171</v>
+        <v>208.639</v>
       </c>
       <c r="V18" t="n">
         <v>111.971</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.272</v>
+        <v>-17.411</v>
       </c>
     </row>
     <row r="19">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3864,7 +3864,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.7</v>
+        <v>119.4</v>
       </c>
       <c r="O19" t="n">
         <v>46.3</v>
@@ -3887,13 +3887,13 @@
         <v>27.276</v>
       </c>
       <c r="U19" t="n">
-        <v>55.182</v>
+        <v>55.213</v>
       </c>
       <c r="V19" t="n">
         <v>17.234</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.204</v>
+        <v>-58.216</v>
       </c>
     </row>
     <row r="20">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>42.9</v>
@@ -3964,13 +3964,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>203.819</v>
+        <v>206.268</v>
       </c>
       <c r="V20" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-17.102</v>
+        <v>-17.24</v>
       </c>
     </row>
     <row r="21">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179</v>
+        <v>178.7</v>
       </c>
       <c r="O21" t="n">
         <v>51.6</v>
@@ -4041,13 +4041,13 @@
         <v>25.989</v>
       </c>
       <c r="U21" t="n">
-        <v>31.497</v>
+        <v>31.523</v>
       </c>
       <c r="V21" t="n">
         <v>4.588</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.176</v>
+        <v>-46.185</v>
       </c>
     </row>
     <row r="22">
@@ -4068,37 +4068,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CANTE.IS, ENERY.IS, FROTO.IS, SOKM.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>CANTE.IS: 2026-09-21 | ENERY.IS: 2026-09-07 | FROTO.IS: 2026-09-17 | SOKM.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>60.21035987359713</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +8.87% / +22.32% / -0.50% | FROTO.IS: +0.23% / +0.36% / -3.42% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +26.00% / +41.59% / -0.56%</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-16.63619973832206</v>
+        <v>-14.37863173570025</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4107,90 +4095,90 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>143</v>
+        <v>142.8</v>
       </c>
       <c r="O22" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="P22" t="n">
         <v>5.6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>31.305</v>
+        <v>31.29</v>
       </c>
       <c r="T22" t="n">
-        <v>31.305</v>
+        <v>31.29</v>
       </c>
       <c r="U22" t="n">
-        <v>13.432</v>
+        <v>16.504</v>
       </c>
       <c r="V22" t="n">
-        <v>3.643</v>
+        <v>6.45</v>
       </c>
       <c r="W22" t="n">
-        <v>-51.692</v>
+        <v>-48.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T2_rotasyon|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>56.41058954395304</v>
+        <v>48.21914524341393</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>4.833271170608744</v>
+        <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>7.573509780159249</v>
+        <v>-4.916447656643863</v>
       </c>
       <c r="L23" t="n">
-        <v>22.230015625</v>
+        <v>16.16102048107813</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>79.3</v>
+        <v>152.5</v>
       </c>
       <c r="O23" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="P23" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4201,73 +4189,73 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>27.463</v>
+        <v>22.233</v>
       </c>
       <c r="T23" t="n">
-        <v>27.463</v>
+        <v>22.233</v>
       </c>
       <c r="U23" t="n">
-        <v>21.484</v>
+        <v>12.505</v>
       </c>
       <c r="V23" t="n">
-        <v>36.442</v>
+        <v>-0.343</v>
       </c>
       <c r="W23" t="n">
-        <v>-15.851</v>
+        <v>-32.164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>48.21914524341393</v>
+        <v>38.04089454478734</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>21.4002873140223</v>
+        <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.916447656643863</v>
+        <v>-3.87783925866676</v>
       </c>
       <c r="L24" t="n">
-        <v>16.16102048107813</v>
+        <v>5.808640829284117</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>152.8</v>
+        <v>113.1</v>
       </c>
       <c r="O24" t="n">
-        <v>41.7</v>
+        <v>50.2</v>
       </c>
       <c r="P24" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4278,19 +4266,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>22.233</v>
+        <v>20.416</v>
       </c>
       <c r="T24" t="n">
-        <v>22.233</v>
+        <v>20.416</v>
       </c>
       <c r="U24" t="n">
-        <v>11.167</v>
+        <v>9.731</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.343</v>
+        <v>-3.303</v>
       </c>
       <c r="W24" t="n">
-        <v>-31.781</v>
+        <v>-28.149</v>
       </c>
     </row>
     <row r="25">
@@ -4301,50 +4289,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>38.04089454478734</v>
+        <v>28.40086810394897</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>13.75066280702224</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.87783925866676</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L25" t="n">
-        <v>5.808640829284117</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>113.4</v>
+        <v>73.8</v>
       </c>
       <c r="O25" t="n">
-        <v>50.2</v>
+        <v>49.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4355,25 +4343,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>20.416</v>
+        <v>13.28</v>
       </c>
       <c r="T25" t="n">
-        <v>20.416</v>
+        <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>9.715</v>
+        <v>7.15</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.303</v>
+        <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-28.145</v>
+        <v>-16.409</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4383,68 +4371,80 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ENERY.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ENERY.IS: 2026-09-21 | TKFEN.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>28.40086810394897</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>6.880672511445463</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ENERY.IS: +6.85% / +7.15% / 0.00% | TKFEN.IS: +27.84% / +41.59% / -0.56%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>15.38514121842653</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.616392554049999</v>
+        <v>8.265188588468519</v>
       </c>
       <c r="L26" t="n">
-        <v>5.127814043936619</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M26" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>73.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="O26" t="n">
-        <v>49.3</v>
+        <v>42.2</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>13.28</v>
+        <v>28.439</v>
       </c>
       <c r="T26" t="n">
-        <v>13.28</v>
+        <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>7.136</v>
+        <v>40.778</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.962</v>
+        <v>50.857</v>
       </c>
       <c r="W26" t="n">
-        <v>-16.407</v>
+        <v>-19.51</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,7 +573,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ANSGR.IS, KRDMD.IS, SOKM.IS</t>
+          <t>AGHOL.IS, ANSGR.IS, KRDMD.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
+          <t>AGHOL.IS: 2026-09-22 | ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ANSGR.IS: -2.76% / +0.00% / -2.82% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.81% / +1.96% / -1.88%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ANSGR.IS: -3.80% / +0.00% / -3.78% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.73% / +1.96% / -1.88%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.897913041213823</v>
+        <v>-8.082319016080785</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1297,10 +1297,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="O10" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1311,22 +1311,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>11.053</v>
+        <v>11.231</v>
       </c>
       <c r="T10" t="n">
-        <v>11.053</v>
+        <v>11.231</v>
       </c>
       <c r="U10" t="n">
-        <v>11.529</v>
+        <v>11.305</v>
       </c>
       <c r="V10" t="n">
-        <v>3.699</v>
+        <v>3.491</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.859</v>
+        <v>-14.083</v>
       </c>
     </row>
     <row r="11">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANSGR.IS, KRDMD.IS, SOKM.IS</t>
+          <t>AGHOL.IS, ANSGR.IS, KRDMD.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
+          <t>AGHOL.IS: 2026-09-22 | ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2410,14 +2410,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ANSGR.IS: -2.76% / +0.00% / -2.82% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.81% / +1.96% / -1.88%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ANSGR.IS: -3.80% / +0.00% / -3.78% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.73% / +1.96% / -1.88%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.897913041213823</v>
+        <v>-8.082319016080785</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2426,10 +2426,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="O26" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2440,22 +2440,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>11.053</v>
+        <v>11.231</v>
       </c>
       <c r="T26" t="n">
-        <v>11.053</v>
+        <v>11.231</v>
       </c>
       <c r="U26" t="n">
-        <v>11.529</v>
+        <v>11.305</v>
       </c>
       <c r="V26" t="n">
-        <v>3.699</v>
+        <v>3.491</v>
       </c>
       <c r="W26" t="n">
-        <v>-13.859</v>
+        <v>-14.083</v>
       </c>
     </row>
     <row r="27">
@@ -2965,7 +2965,7 @@
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-14.37863173570025</v>
+        <v>-14.30341432566774</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -2991,19 +2991,19 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>31.29</v>
+        <v>31.269</v>
       </c>
       <c r="T6" t="n">
-        <v>31.29</v>
+        <v>31.269</v>
       </c>
       <c r="U6" t="n">
-        <v>16.504</v>
+        <v>16.607</v>
       </c>
       <c r="V6" t="n">
-        <v>6.45</v>
+        <v>6.544</v>
       </c>
       <c r="W6" t="n">
-        <v>-48.62</v>
+        <v>-48.518</v>
       </c>
     </row>
     <row r="7">
@@ -3420,14 +3420,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.85% / +7.15% / 0.00% | TKFEN.IS: +27.84% / +41.59% / -0.56%</t>
+          <t>ENERY.IS: +6.39% / +7.41% / 0.00% | TKFEN.IS: +28.80% / +41.59% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.265188588468519</v>
+        <v>8.567272033745521</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3459,13 +3459,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>40.778</v>
+        <v>41.171</v>
       </c>
       <c r="V12" t="n">
-        <v>50.857</v>
+        <v>51.278</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.51</v>
+        <v>-19.117</v>
       </c>
     </row>
     <row r="13">
@@ -4086,7 +4086,7 @@
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-14.37863173570025</v>
+        <v>-14.30341432566774</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4112,19 +4112,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>31.29</v>
+        <v>31.269</v>
       </c>
       <c r="T22" t="n">
-        <v>31.29</v>
+        <v>31.269</v>
       </c>
       <c r="U22" t="n">
-        <v>16.504</v>
+        <v>16.607</v>
       </c>
       <c r="V22" t="n">
-        <v>6.45</v>
+        <v>6.544</v>
       </c>
       <c r="W22" t="n">
-        <v>-48.62</v>
+        <v>-48.518</v>
       </c>
     </row>
     <row r="23">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.85% / +7.15% / 0.00% | TKFEN.IS: +27.84% / +41.59% / -0.56%</t>
+          <t>ENERY.IS: +6.39% / +7.41% / 0.00% | TKFEN.IS: +28.80% / +41.59% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>8.265188588468519</v>
+        <v>8.567272033745521</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4438,13 +4438,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>40.778</v>
+        <v>41.171</v>
       </c>
       <c r="V26" t="n">
-        <v>50.857</v>
+        <v>51.278</v>
       </c>
       <c r="W26" t="n">
-        <v>-19.51</v>
+        <v>-19.117</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,10 +573,10 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O3" t="n">
         <v>42.9</v>
@@ -783,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>40.257</v>
+        <v>39.311</v>
       </c>
       <c r="V3" t="n">
         <v>17.724</v>
       </c>
       <c r="W3" t="n">
-        <v>-34.291</v>
+        <v>-34.059</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -858,13 +858,13 @@
         <v>21.057</v>
       </c>
       <c r="U4" t="n">
-        <v>152.873</v>
+        <v>152.017</v>
       </c>
       <c r="V4" t="n">
         <v>111.543</v>
       </c>
       <c r="W4" t="n">
-        <v>-12.804</v>
+        <v>-12.761</v>
       </c>
     </row>
     <row r="5">
@@ -883,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>63.4</v>
+        <v>63.2</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -933,13 +933,13 @@
         <v>19.637</v>
       </c>
       <c r="U5" t="n">
-        <v>117.494</v>
+        <v>118.36</v>
       </c>
       <c r="V5" t="n">
         <v>117.535</v>
       </c>
       <c r="W5" t="n">
-        <v>-16.191</v>
+        <v>-16.255</v>
       </c>
     </row>
     <row r="6">
@@ -958,12 +958,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O6" t="n">
         <v>42.9</v>
@@ -1008,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>40.257</v>
+        <v>39.311</v>
       </c>
       <c r="V6" t="n">
         <v>17.724</v>
       </c>
       <c r="W6" t="n">
-        <v>-34.291</v>
+        <v>-34.059</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O7" t="n">
         <v>46.6</v>
@@ -1083,13 +1083,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>29.285</v>
+        <v>29.833</v>
       </c>
       <c r="V7" t="n">
         <v>24.076</v>
       </c>
       <c r="W7" t="n">
-        <v>-34.749</v>
+        <v>-34.897</v>
       </c>
     </row>
     <row r="8">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>194</v>
+        <v>193.6</v>
       </c>
       <c r="O8" t="n">
         <v>46.1</v>
@@ -1158,13 +1158,13 @@
         <v>21.789</v>
       </c>
       <c r="U8" t="n">
-        <v>29.333</v>
+        <v>28.877</v>
       </c>
       <c r="V8" t="n">
         <v>5.494</v>
       </c>
       <c r="W8" t="n">
-        <v>-36.031</v>
+        <v>-35.904</v>
       </c>
     </row>
     <row r="9">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O9" t="n">
         <v>42.9</v>
@@ -1233,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>40.257</v>
+        <v>39.311</v>
       </c>
       <c r="V9" t="n">
         <v>17.724</v>
       </c>
       <c r="W9" t="n">
-        <v>-34.291</v>
+        <v>-34.059</v>
       </c>
     </row>
     <row r="10">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGHOL.IS, ANSGR.IS, KRDMD.IS, SOKM.IS</t>
+          <t>KRDMD.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-09-22 | ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
+          <t>KRDMD.IS: 2026-09-22</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ANSGR.IS: -3.80% / +0.00% / -3.78% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.73% / +1.96% / -1.88%</t>
+          <t>KRDMD.IS: +3.03% / +5.52% / -0.09%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.082319016080785</v>
+        <v>-6.884741006551021</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1297,10 +1297,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>179</v>
+        <v>178.6</v>
       </c>
       <c r="O10" t="n">
-        <v>47.6</v>
+        <v>48.1</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1311,22 +1311,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>11.231</v>
+        <v>11.217</v>
       </c>
       <c r="T10" t="n">
-        <v>11.231</v>
+        <v>11.217</v>
       </c>
       <c r="U10" t="n">
-        <v>11.305</v>
+        <v>12.756</v>
       </c>
       <c r="V10" t="n">
-        <v>3.491</v>
+        <v>4.84</v>
       </c>
       <c r="W10" t="n">
-        <v>-14.083</v>
+        <v>-12.632</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>65.3</v>
+        <v>65.2</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1395,13 +1395,13 @@
         <v>7.033</v>
       </c>
       <c r="U11" t="n">
-        <v>85.934</v>
+        <v>85.66</v>
       </c>
       <c r="V11" t="n">
         <v>58.898</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.624</v>
+        <v>-1.621</v>
       </c>
     </row>
     <row r="12">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>45.3</v>
@@ -1470,13 +1470,13 @@
         <v>24.573</v>
       </c>
       <c r="U12" t="n">
-        <v>5.735</v>
+        <v>7.914</v>
       </c>
       <c r="V12" t="n">
         <v>18.367</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.73</v>
+        <v>-18.096</v>
       </c>
     </row>
     <row r="13">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="O13" t="n">
         <v>44.1</v>
@@ -1545,13 +1545,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>86.879</v>
+        <v>93.86199999999999</v>
       </c>
       <c r="V13" t="n">
         <v>99.372</v>
       </c>
       <c r="W13" t="n">
-        <v>-24.413</v>
+        <v>-25.325</v>
       </c>
     </row>
     <row r="14">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="O14" t="n">
         <v>44.1</v>
@@ -1620,13 +1620,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>86.879</v>
+        <v>93.86199999999999</v>
       </c>
       <c r="V14" t="n">
         <v>99.372</v>
       </c>
       <c r="W14" t="n">
-        <v>-24.413</v>
+        <v>-25.325</v>
       </c>
     </row>
     <row r="16">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O18" t="n">
         <v>42.9</v>
@@ -1821,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>40.257</v>
+        <v>39.311</v>
       </c>
       <c r="V18" t="n">
         <v>17.724</v>
       </c>
       <c r="W18" t="n">
-        <v>-34.291</v>
+        <v>-34.059</v>
       </c>
     </row>
     <row r="19">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1898,13 +1898,13 @@
         <v>21.057</v>
       </c>
       <c r="U19" t="n">
-        <v>152.873</v>
+        <v>152.017</v>
       </c>
       <c r="V19" t="n">
         <v>111.543</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.804</v>
+        <v>-12.761</v>
       </c>
     </row>
     <row r="20">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1952,7 +1952,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>63.4</v>
+        <v>63.2</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -1975,13 +1975,13 @@
         <v>19.637</v>
       </c>
       <c r="U20" t="n">
-        <v>117.494</v>
+        <v>118.36</v>
       </c>
       <c r="V20" t="n">
         <v>117.535</v>
       </c>
       <c r="W20" t="n">
-        <v>-16.191</v>
+        <v>-16.255</v>
       </c>
     </row>
     <row r="21">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>194</v>
+        <v>193.6</v>
       </c>
       <c r="O21" t="n">
         <v>46.1</v>
@@ -2052,13 +2052,13 @@
         <v>21.789</v>
       </c>
       <c r="U21" t="n">
-        <v>29.333</v>
+        <v>28.877</v>
       </c>
       <c r="V21" t="n">
         <v>5.494</v>
       </c>
       <c r="W21" t="n">
-        <v>-36.031</v>
+        <v>-35.904</v>
       </c>
     </row>
     <row r="22">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O22" t="n">
         <v>46.6</v>
@@ -2129,13 +2129,13 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>29.285</v>
+        <v>29.833</v>
       </c>
       <c r="V22" t="n">
         <v>24.076</v>
       </c>
       <c r="W22" t="n">
-        <v>-34.749</v>
+        <v>-34.897</v>
       </c>
     </row>
     <row r="23">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="O23" t="n">
         <v>44.1</v>
@@ -2206,13 +2206,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>86.879</v>
+        <v>93.86199999999999</v>
       </c>
       <c r="V23" t="n">
         <v>99.372</v>
       </c>
       <c r="W23" t="n">
-        <v>-24.413</v>
+        <v>-25.325</v>
       </c>
     </row>
     <row r="24">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="O24" t="n">
         <v>44.1</v>
@@ -2283,13 +2283,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>86.879</v>
+        <v>93.86199999999999</v>
       </c>
       <c r="V24" t="n">
         <v>99.372</v>
       </c>
       <c r="W24" t="n">
-        <v>-24.413</v>
+        <v>-25.325</v>
       </c>
     </row>
     <row r="25">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>65.3</v>
+        <v>65.2</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2360,13 +2360,13 @@
         <v>7.033</v>
       </c>
       <c r="U25" t="n">
-        <v>85.934</v>
+        <v>85.66</v>
       </c>
       <c r="V25" t="n">
         <v>58.898</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.624</v>
+        <v>-1.621</v>
       </c>
     </row>
     <row r="26">
@@ -2387,22 +2387,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGHOL.IS, ANSGR.IS, KRDMD.IS, SOKM.IS</t>
+          <t>KRDMD.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-09-22 | ANSGR.IS: 2026-09-21 | KRDMD.IS: 2026-09-22 | SOKM.IS: 2026-09-21</t>
+          <t>KRDMD.IS: 2026-09-22</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2410,14 +2410,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ANSGR.IS: -3.80% / +0.00% / -3.78% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.73% / +1.96% / -1.88%</t>
+          <t>KRDMD.IS: +3.03% / +5.52% / -0.09%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.082319016080785</v>
+        <v>-6.884741006551021</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2426,10 +2426,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>179</v>
+        <v>178.6</v>
       </c>
       <c r="O26" t="n">
-        <v>47.6</v>
+        <v>48.1</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2440,22 +2440,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>11.231</v>
+        <v>11.217</v>
       </c>
       <c r="T26" t="n">
-        <v>11.231</v>
+        <v>11.217</v>
       </c>
       <c r="U26" t="n">
-        <v>11.305</v>
+        <v>12.756</v>
       </c>
       <c r="V26" t="n">
-        <v>3.491</v>
+        <v>4.84</v>
       </c>
       <c r="W26" t="n">
-        <v>-14.083</v>
+        <v>-12.632</v>
       </c>
     </row>
     <row r="27">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2503,7 +2503,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N27" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>45.3</v>
@@ -2526,13 +2526,13 @@
         <v>24.573</v>
       </c>
       <c r="U27" t="n">
-        <v>5.735</v>
+        <v>7.914</v>
       </c>
       <c r="V27" t="n">
         <v>18.367</v>
       </c>
       <c r="W27" t="n">
-        <v>-17.73</v>
+        <v>-18.096</v>
       </c>
     </row>
   </sheetData>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>44.7</v>
@@ -2772,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>208.639</v>
+        <v>210.115</v>
       </c>
       <c r="V3" t="n">
         <v>111.971</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.411</v>
+        <v>-17.494</v>
       </c>
     </row>
     <row r="4">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.4</v>
+        <v>119.2</v>
       </c>
       <c r="O4" t="n">
         <v>46.3</v>
@@ -2847,13 +2847,13 @@
         <v>27.276</v>
       </c>
       <c r="U4" t="n">
-        <v>55.213</v>
+        <v>53.528</v>
       </c>
       <c r="V4" t="n">
         <v>17.234</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.216</v>
+        <v>-57.584</v>
       </c>
     </row>
     <row r="5">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>42.9</v>
@@ -2922,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>206.268</v>
+        <v>207.733</v>
       </c>
       <c r="V5" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-17.24</v>
+        <v>-17.322</v>
       </c>
     </row>
     <row r="6">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-14.30341432566774</v>
+        <v>-14.29094917471617</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -2974,7 +2974,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>142.8</v>
+        <v>142.5</v>
       </c>
       <c r="O6" t="n">
         <v>41.8</v>
@@ -2997,13 +2997,13 @@
         <v>31.269</v>
       </c>
       <c r="U6" t="n">
-        <v>16.607</v>
+        <v>16.623</v>
       </c>
       <c r="V6" t="n">
-        <v>6.544</v>
+        <v>6.559</v>
       </c>
       <c r="W6" t="n">
-        <v>-48.518</v>
+        <v>-48.501</v>
       </c>
     </row>
     <row r="7">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3049,7 +3049,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.4</v>
+        <v>119.2</v>
       </c>
       <c r="O7" t="n">
         <v>46.3</v>
@@ -3072,13 +3072,13 @@
         <v>27.276</v>
       </c>
       <c r="U7" t="n">
-        <v>55.213</v>
+        <v>53.528</v>
       </c>
       <c r="V7" t="n">
         <v>17.234</v>
       </c>
       <c r="W7" t="n">
-        <v>-58.216</v>
+        <v>-57.584</v>
       </c>
     </row>
     <row r="8">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>152.5</v>
+        <v>152.2</v>
       </c>
       <c r="O8" t="n">
         <v>41.7</v>
@@ -3147,13 +3147,13 @@
         <v>22.233</v>
       </c>
       <c r="U8" t="n">
-        <v>12.505</v>
+        <v>12.877</v>
       </c>
       <c r="V8" t="n">
         <v>-0.343</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.164</v>
+        <v>-32.27</v>
       </c>
     </row>
     <row r="9">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3222,13 +3222,13 @@
         <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>7.15</v>
+        <v>6.912</v>
       </c>
       <c r="V9" t="n">
         <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.409</v>
+        <v>-16.373</v>
       </c>
     </row>
     <row r="10">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.1</v>
+        <v>112.9</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3297,13 +3297,13 @@
         <v>20.416</v>
       </c>
       <c r="U10" t="n">
-        <v>9.731</v>
+        <v>8.587</v>
       </c>
       <c r="V10" t="n">
         <v>-3.303</v>
       </c>
       <c r="W10" t="n">
-        <v>-28.149</v>
+        <v>-27.856</v>
       </c>
     </row>
     <row r="11">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3349,7 +3349,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>178.7</v>
+        <v>178.3</v>
       </c>
       <c r="O11" t="n">
         <v>51.6</v>
@@ -3372,13 +3372,13 @@
         <v>25.989</v>
       </c>
       <c r="U11" t="n">
-        <v>31.523</v>
+        <v>30.105</v>
       </c>
       <c r="V11" t="n">
         <v>4.588</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.185</v>
+        <v>-45.687</v>
       </c>
     </row>
     <row r="12">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3420,14 +3420,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.39% / +7.41% / 0.00% | TKFEN.IS: +28.80% / +41.59% / -0.56%</t>
+          <t>ENERY.IS: +9.91% / +11.34% / 0.00% | TKFEN.IS: +39.97% / +41.59% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.567272033745521</v>
+        <v>15.66593610511518</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3436,7 +3436,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="O12" t="n">
         <v>42.2</v>
@@ -3459,13 +3459,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>41.171</v>
+        <v>50.401</v>
       </c>
       <c r="V12" t="n">
-        <v>51.278</v>
+        <v>61.169</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.117</v>
+        <v>-9.887</v>
       </c>
     </row>
     <row r="13">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3511,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>92.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>44.7</v>
@@ -3534,13 +3534,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>208.639</v>
+        <v>210.115</v>
       </c>
       <c r="V13" t="n">
         <v>111.971</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.411</v>
+        <v>-17.494</v>
       </c>
     </row>
     <row r="14">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>42.9</v>
@@ -3609,13 +3609,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>206.268</v>
+        <v>207.733</v>
       </c>
       <c r="V14" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.24</v>
+        <v>-17.322</v>
       </c>
     </row>
     <row r="16">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>44.7</v>
@@ -3810,13 +3810,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>208.639</v>
+        <v>210.115</v>
       </c>
       <c r="V18" t="n">
         <v>111.971</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.411</v>
+        <v>-17.494</v>
       </c>
     </row>
     <row r="19">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3864,7 +3864,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.4</v>
+        <v>119.2</v>
       </c>
       <c r="O19" t="n">
         <v>46.3</v>
@@ -3887,13 +3887,13 @@
         <v>27.276</v>
       </c>
       <c r="U19" t="n">
-        <v>55.213</v>
+        <v>53.528</v>
       </c>
       <c r="V19" t="n">
         <v>17.234</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.216</v>
+        <v>-57.584</v>
       </c>
     </row>
     <row r="20">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>42.9</v>
@@ -3964,13 +3964,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>206.268</v>
+        <v>207.733</v>
       </c>
       <c r="V20" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-17.24</v>
+        <v>-17.322</v>
       </c>
     </row>
     <row r="21">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>178.7</v>
+        <v>178.3</v>
       </c>
       <c r="O21" t="n">
         <v>51.6</v>
@@ -4041,13 +4041,13 @@
         <v>25.989</v>
       </c>
       <c r="U21" t="n">
-        <v>31.523</v>
+        <v>30.105</v>
       </c>
       <c r="V21" t="n">
         <v>4.588</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.185</v>
+        <v>-45.687</v>
       </c>
     </row>
     <row r="22">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4086,7 +4086,7 @@
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-14.30341432566774</v>
+        <v>-14.29094917471617</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4095,7 +4095,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>142.8</v>
+        <v>142.5</v>
       </c>
       <c r="O22" t="n">
         <v>41.8</v>
@@ -4118,13 +4118,13 @@
         <v>31.269</v>
       </c>
       <c r="U22" t="n">
-        <v>16.607</v>
+        <v>16.623</v>
       </c>
       <c r="V22" t="n">
-        <v>6.544</v>
+        <v>6.559</v>
       </c>
       <c r="W22" t="n">
-        <v>-48.518</v>
+        <v>-48.501</v>
       </c>
     </row>
     <row r="23">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>152.5</v>
+        <v>152.2</v>
       </c>
       <c r="O23" t="n">
         <v>41.7</v>
@@ -4195,13 +4195,13 @@
         <v>22.233</v>
       </c>
       <c r="U23" t="n">
-        <v>12.505</v>
+        <v>12.877</v>
       </c>
       <c r="V23" t="n">
         <v>-0.343</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.164</v>
+        <v>-32.27</v>
       </c>
     </row>
     <row r="24">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4249,7 +4249,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>113.1</v>
+        <v>112.9</v>
       </c>
       <c r="O24" t="n">
         <v>50.2</v>
@@ -4272,13 +4272,13 @@
         <v>20.416</v>
       </c>
       <c r="U24" t="n">
-        <v>9.731</v>
+        <v>8.587</v>
       </c>
       <c r="V24" t="n">
         <v>-3.303</v>
       </c>
       <c r="W24" t="n">
-        <v>-28.149</v>
+        <v>-27.856</v>
       </c>
     </row>
     <row r="25">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4326,7 +4326,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4349,13 +4349,13 @@
         <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>7.15</v>
+        <v>6.912</v>
       </c>
       <c r="V25" t="n">
         <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.409</v>
+        <v>-16.373</v>
       </c>
     </row>
     <row r="26">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: +6.39% / +7.41% / 0.00% | TKFEN.IS: +28.80% / +41.59% / -0.56%</t>
+          <t>ENERY.IS: +9.91% / +11.34% / 0.00% | TKFEN.IS: +39.97% / +41.59% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>8.567272033745521</v>
+        <v>15.66593610511518</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4415,7 +4415,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="O26" t="n">
         <v>42.2</v>
@@ -4438,13 +4438,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>41.171</v>
+        <v>50.401</v>
       </c>
       <c r="V26" t="n">
-        <v>51.278</v>
+        <v>61.169</v>
       </c>
       <c r="W26" t="n">
-        <v>-19.117</v>
+        <v>-9.887</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,10 +573,10 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="O3" t="n">
         <v>42.9</v>
@@ -783,13 +783,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>39.311</v>
+        <v>38.024</v>
       </c>
       <c r="V3" t="n">
         <v>17.724</v>
       </c>
       <c r="W3" t="n">
-        <v>-34.059</v>
+        <v>-33.745</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -858,13 +858,13 @@
         <v>21.057</v>
       </c>
       <c r="U4" t="n">
-        <v>152.017</v>
+        <v>151.143</v>
       </c>
       <c r="V4" t="n">
         <v>111.543</v>
       </c>
       <c r="W4" t="n">
-        <v>-12.761</v>
+        <v>-12.717</v>
       </c>
     </row>
     <row r="5">
@@ -883,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -933,13 +933,13 @@
         <v>19.637</v>
       </c>
       <c r="U5" t="n">
-        <v>118.36</v>
+        <v>116.632</v>
       </c>
       <c r="V5" t="n">
         <v>117.535</v>
       </c>
       <c r="W5" t="n">
-        <v>-16.255</v>
+        <v>-16.127</v>
       </c>
     </row>
     <row r="6">
@@ -958,12 +958,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="O6" t="n">
         <v>42.9</v>
@@ -1008,13 +1008,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>39.311</v>
+        <v>38.024</v>
       </c>
       <c r="V6" t="n">
         <v>17.724</v>
       </c>
       <c r="W6" t="n">
-        <v>-34.059</v>
+        <v>-33.745</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.7</v>
+        <v>134.4</v>
       </c>
       <c r="O7" t="n">
         <v>46.6</v>
@@ -1083,13 +1083,13 @@
         <v>23.45</v>
       </c>
       <c r="U7" t="n">
-        <v>29.833</v>
+        <v>28.862</v>
       </c>
       <c r="V7" t="n">
         <v>24.076</v>
       </c>
       <c r="W7" t="n">
-        <v>-34.897</v>
+        <v>-34.636</v>
       </c>
     </row>
     <row r="8">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>193.6</v>
+        <v>193.2</v>
       </c>
       <c r="O8" t="n">
         <v>46.1</v>
@@ -1158,13 +1158,13 @@
         <v>21.789</v>
       </c>
       <c r="U8" t="n">
-        <v>28.877</v>
+        <v>28.44</v>
       </c>
       <c r="V8" t="n">
         <v>5.494</v>
       </c>
       <c r="W8" t="n">
-        <v>-35.904</v>
+        <v>-35.782</v>
       </c>
     </row>
     <row r="9">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="O9" t="n">
         <v>42.9</v>
@@ -1233,13 +1233,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>39.311</v>
+        <v>38.024</v>
       </c>
       <c r="V9" t="n">
         <v>17.724</v>
       </c>
       <c r="W9" t="n">
-        <v>-34.059</v>
+        <v>-33.745</v>
       </c>
     </row>
     <row r="10">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KRDMD.IS</t>
+          <t>ENKAI.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KRDMD.IS: 2026-09-22</t>
+          <t>ENKAI.IS: 2026-09-24 | KRDMD.IS: 2026-09-24</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KRDMD.IS: +3.03% / +5.52% / -0.09%</t>
+          <t>ENKAI.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.884741006551021</v>
+        <v>-6.964562509498928</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1297,10 +1297,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>178.6</v>
+        <v>179.2</v>
       </c>
       <c r="O10" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>11.217</v>
@@ -1320,13 +1320,13 @@
         <v>11.217</v>
       </c>
       <c r="U10" t="n">
-        <v>12.756</v>
+        <v>12.659</v>
       </c>
       <c r="V10" t="n">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.632</v>
+        <v>-12.729</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1395,13 +1395,13 @@
         <v>7.033</v>
       </c>
       <c r="U11" t="n">
-        <v>85.66</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>58.898</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.621</v>
+        <v>-1.618</v>
       </c>
     </row>
     <row r="12">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="O12" t="n">
         <v>45.3</v>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="O13" t="n">
         <v>44.1</v>
@@ -1545,13 +1545,13 @@
         <v>25.345</v>
       </c>
       <c r="U13" t="n">
-        <v>93.86199999999999</v>
+        <v>93.905</v>
       </c>
       <c r="V13" t="n">
         <v>99.372</v>
       </c>
       <c r="W13" t="n">
-        <v>-25.325</v>
+        <v>-25.331</v>
       </c>
     </row>
     <row r="14">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="O14" t="n">
         <v>44.1</v>
@@ -1620,13 +1620,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>93.86199999999999</v>
+        <v>93.905</v>
       </c>
       <c r="V14" t="n">
         <v>99.372</v>
       </c>
       <c r="W14" t="n">
-        <v>-25.325</v>
+        <v>-25.331</v>
       </c>
     </row>
     <row r="16">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="O18" t="n">
         <v>42.9</v>
@@ -1821,13 +1821,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>39.311</v>
+        <v>38.024</v>
       </c>
       <c r="V18" t="n">
         <v>17.724</v>
       </c>
       <c r="W18" t="n">
-        <v>-34.059</v>
+        <v>-33.745</v>
       </c>
     </row>
     <row r="19">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1898,13 +1898,13 @@
         <v>21.057</v>
       </c>
       <c r="U19" t="n">
-        <v>152.017</v>
+        <v>151.143</v>
       </c>
       <c r="V19" t="n">
         <v>111.543</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.761</v>
+        <v>-12.717</v>
       </c>
     </row>
     <row r="20">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1952,7 +1952,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -1975,13 +1975,13 @@
         <v>19.637</v>
       </c>
       <c r="U20" t="n">
-        <v>118.36</v>
+        <v>116.632</v>
       </c>
       <c r="V20" t="n">
         <v>117.535</v>
       </c>
       <c r="W20" t="n">
-        <v>-16.255</v>
+        <v>-16.127</v>
       </c>
     </row>
     <row r="21">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>193.6</v>
+        <v>193.2</v>
       </c>
       <c r="O21" t="n">
         <v>46.1</v>
@@ -2052,13 +2052,13 @@
         <v>21.789</v>
       </c>
       <c r="U21" t="n">
-        <v>28.877</v>
+        <v>28.44</v>
       </c>
       <c r="V21" t="n">
         <v>5.494</v>
       </c>
       <c r="W21" t="n">
-        <v>-35.904</v>
+        <v>-35.782</v>
       </c>
     </row>
     <row r="22">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.7</v>
+        <v>134.4</v>
       </c>
       <c r="O22" t="n">
         <v>46.6</v>
@@ -2129,13 +2129,13 @@
         <v>23.45</v>
       </c>
       <c r="U22" t="n">
-        <v>29.833</v>
+        <v>28.862</v>
       </c>
       <c r="V22" t="n">
         <v>24.076</v>
       </c>
       <c r="W22" t="n">
-        <v>-34.897</v>
+        <v>-34.636</v>
       </c>
     </row>
     <row r="23">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="O23" t="n">
         <v>44.1</v>
@@ -2206,13 +2206,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>93.86199999999999</v>
+        <v>93.905</v>
       </c>
       <c r="V23" t="n">
         <v>99.372</v>
       </c>
       <c r="W23" t="n">
-        <v>-25.325</v>
+        <v>-25.331</v>
       </c>
     </row>
     <row r="24">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="O24" t="n">
         <v>44.1</v>
@@ -2283,13 +2283,13 @@
         <v>25.345</v>
       </c>
       <c r="U24" t="n">
-        <v>93.86199999999999</v>
+        <v>93.905</v>
       </c>
       <c r="V24" t="n">
         <v>99.372</v>
       </c>
       <c r="W24" t="n">
-        <v>-25.325</v>
+        <v>-25.331</v>
       </c>
     </row>
     <row r="25">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="O25" t="n">
         <v>51.9</v>
@@ -2360,13 +2360,13 @@
         <v>7.033</v>
       </c>
       <c r="U25" t="n">
-        <v>85.66</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>58.898</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.621</v>
+        <v>-1.618</v>
       </c>
     </row>
     <row r="26">
@@ -2387,22 +2387,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KRDMD.IS</t>
+          <t>ENKAI.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>KRDMD.IS: 2026-09-22</t>
+          <t>ENKAI.IS: 2026-09-24 | KRDMD.IS: 2026-09-24</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2410,14 +2410,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KRDMD.IS: +3.03% / +5.52% / -0.09%</t>
+          <t>ENKAI.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.884741006551021</v>
+        <v>-6.964562509498928</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2426,10 +2426,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>178.6</v>
+        <v>179.2</v>
       </c>
       <c r="O26" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>11.217</v>
@@ -2449,13 +2449,13 @@
         <v>11.217</v>
       </c>
       <c r="U26" t="n">
-        <v>12.756</v>
+        <v>12.659</v>
       </c>
       <c r="V26" t="n">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="W26" t="n">
-        <v>-12.632</v>
+        <v>-12.729</v>
       </c>
     </row>
     <row r="27">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2503,7 +2503,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N27" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="O27" t="n">
         <v>45.3</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>44.7</v>
@@ -2772,13 +2772,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>210.115</v>
+        <v>207.525</v>
       </c>
       <c r="V3" t="n">
         <v>111.971</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.494</v>
+        <v>-17.348</v>
       </c>
     </row>
     <row r="4">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.2</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>46.3</v>
@@ -2847,13 +2847,13 @@
         <v>27.276</v>
       </c>
       <c r="U4" t="n">
-        <v>53.528</v>
+        <v>50.052</v>
       </c>
       <c r="V4" t="n">
         <v>17.234</v>
       </c>
       <c r="W4" t="n">
-        <v>-57.584</v>
+        <v>-56.28</v>
       </c>
     </row>
     <row r="5">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O5" t="n">
         <v>42.9</v>
@@ -2922,13 +2922,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>207.733</v>
+        <v>205.163</v>
       </c>
       <c r="V5" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-17.322</v>
+        <v>-17.178</v>
       </c>
     </row>
     <row r="6">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>142.5</v>
+        <v>142.2</v>
       </c>
       <c r="O6" t="n">
         <v>41.8</v>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3049,7 +3049,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.2</v>
+        <v>119</v>
       </c>
       <c r="O7" t="n">
         <v>46.3</v>
@@ -3072,13 +3072,13 @@
         <v>27.276</v>
       </c>
       <c r="U7" t="n">
-        <v>53.528</v>
+        <v>50.052</v>
       </c>
       <c r="V7" t="n">
         <v>17.234</v>
       </c>
       <c r="W7" t="n">
-        <v>-57.584</v>
+        <v>-56.28</v>
       </c>
     </row>
     <row r="8">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>152.2</v>
+        <v>151.9</v>
       </c>
       <c r="O8" t="n">
         <v>41.7</v>
@@ -3147,13 +3147,13 @@
         <v>22.233</v>
       </c>
       <c r="U8" t="n">
-        <v>12.877</v>
+        <v>12.049</v>
       </c>
       <c r="V8" t="n">
         <v>-0.343</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.27</v>
+        <v>-32.033</v>
       </c>
     </row>
     <row r="9">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>73.7</v>
+        <v>73.5</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3222,13 +3222,13 @@
         <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>6.912</v>
+        <v>6.273</v>
       </c>
       <c r="V9" t="n">
         <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.373</v>
+        <v>-16.275</v>
       </c>
     </row>
     <row r="10">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>112.9</v>
+        <v>112.7</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3297,13 +3297,13 @@
         <v>20.416</v>
       </c>
       <c r="U10" t="n">
-        <v>8.587</v>
+        <v>7.888</v>
       </c>
       <c r="V10" t="n">
         <v>-3.303</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.856</v>
+        <v>-27.676</v>
       </c>
     </row>
     <row r="11">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3349,7 +3349,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>178.3</v>
+        <v>178</v>
       </c>
       <c r="O11" t="n">
         <v>51.6</v>
@@ -3372,13 +3372,13 @@
         <v>25.989</v>
       </c>
       <c r="U11" t="n">
-        <v>30.105</v>
+        <v>29.633</v>
       </c>
       <c r="V11" t="n">
         <v>4.588</v>
       </c>
       <c r="W11" t="n">
-        <v>-45.687</v>
+        <v>-45.522</v>
       </c>
     </row>
     <row r="12">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3420,14 +3420,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.91% / +11.34% / 0.00% | TKFEN.IS: +39.97% / +41.59% / -0.56%</t>
+          <t>ENERY.IS: +9.93% / +11.34% / 0.00% | TKFEN.IS: +43.05% / +48.34% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>15.66593610511518</v>
+        <v>17.23750265346325</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3436,7 +3436,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="O12" t="n">
         <v>42.2</v>
@@ -3459,13 +3459,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>50.401</v>
+        <v>52.445</v>
       </c>
       <c r="V12" t="n">
-        <v>61.169</v>
+        <v>63.359</v>
       </c>
       <c r="W12" t="n">
-        <v>-9.887</v>
+        <v>-7.843</v>
       </c>
     </row>
     <row r="13">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3511,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>92.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>44.7</v>
@@ -3534,13 +3534,13 @@
         <v>18.106</v>
       </c>
       <c r="U13" t="n">
-        <v>210.115</v>
+        <v>207.525</v>
       </c>
       <c r="V13" t="n">
         <v>111.971</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.494</v>
+        <v>-17.348</v>
       </c>
     </row>
     <row r="14">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O14" t="n">
         <v>42.9</v>
@@ -3609,13 +3609,13 @@
         <v>21.096</v>
       </c>
       <c r="U14" t="n">
-        <v>207.733</v>
+        <v>205.163</v>
       </c>
       <c r="V14" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.322</v>
+        <v>-17.178</v>
       </c>
     </row>
     <row r="16">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>44.7</v>
@@ -3810,13 +3810,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>210.115</v>
+        <v>207.525</v>
       </c>
       <c r="V18" t="n">
         <v>111.971</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.494</v>
+        <v>-17.348</v>
       </c>
     </row>
     <row r="19">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3864,7 +3864,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.2</v>
+        <v>119</v>
       </c>
       <c r="O19" t="n">
         <v>46.3</v>
@@ -3887,13 +3887,13 @@
         <v>27.276</v>
       </c>
       <c r="U19" t="n">
-        <v>53.528</v>
+        <v>50.052</v>
       </c>
       <c r="V19" t="n">
         <v>17.234</v>
       </c>
       <c r="W19" t="n">
-        <v>-57.584</v>
+        <v>-56.28</v>
       </c>
     </row>
     <row r="20">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O20" t="n">
         <v>42.9</v>
@@ -3964,13 +3964,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>207.733</v>
+        <v>205.163</v>
       </c>
       <c r="V20" t="n">
         <v>93.03400000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-17.322</v>
+        <v>-17.178</v>
       </c>
     </row>
     <row r="21">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>178.3</v>
+        <v>178</v>
       </c>
       <c r="O21" t="n">
         <v>51.6</v>
@@ -4041,13 +4041,13 @@
         <v>25.989</v>
       </c>
       <c r="U21" t="n">
-        <v>30.105</v>
+        <v>29.633</v>
       </c>
       <c r="V21" t="n">
         <v>4.588</v>
       </c>
       <c r="W21" t="n">
-        <v>-45.687</v>
+        <v>-45.522</v>
       </c>
     </row>
     <row r="22">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>142.5</v>
+        <v>142.2</v>
       </c>
       <c r="O22" t="n">
         <v>41.8</v>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>152.2</v>
+        <v>151.9</v>
       </c>
       <c r="O23" t="n">
         <v>41.7</v>
@@ -4195,13 +4195,13 @@
         <v>22.233</v>
       </c>
       <c r="U23" t="n">
-        <v>12.877</v>
+        <v>12.049</v>
       </c>
       <c r="V23" t="n">
         <v>-0.343</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.27</v>
+        <v>-32.033</v>
       </c>
     </row>
     <row r="24">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4249,7 +4249,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>112.9</v>
+        <v>112.7</v>
       </c>
       <c r="O24" t="n">
         <v>50.2</v>
@@ -4272,13 +4272,13 @@
         <v>20.416</v>
       </c>
       <c r="U24" t="n">
-        <v>8.587</v>
+        <v>7.888</v>
       </c>
       <c r="V24" t="n">
         <v>-3.303</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.856</v>
+        <v>-27.676</v>
       </c>
     </row>
     <row r="25">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4326,7 +4326,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>73.7</v>
+        <v>73.5</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4349,13 +4349,13 @@
         <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>6.912</v>
+        <v>6.273</v>
       </c>
       <c r="V25" t="n">
         <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.373</v>
+        <v>-16.275</v>
       </c>
     </row>
     <row r="26">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.91% / +11.34% / 0.00% | TKFEN.IS: +39.97% / +41.59% / -0.56%</t>
+          <t>ENERY.IS: +9.93% / +11.34% / 0.00% | TKFEN.IS: +43.05% / +48.34% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>15.66593610511518</v>
+        <v>17.23750265346325</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4415,7 +4415,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="O26" t="n">
         <v>42.2</v>
@@ -4438,13 +4438,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>50.401</v>
+        <v>52.445</v>
       </c>
       <c r="V26" t="n">
-        <v>61.169</v>
+        <v>63.359</v>
       </c>
       <c r="W26" t="n">
-        <v>-9.887</v>
+        <v>-7.843</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -1288,7 +1288,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.964562509498928</v>
+        <v>-7.094408072556558</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1320,13 +1320,13 @@
         <v>11.217</v>
       </c>
       <c r="U10" t="n">
-        <v>12.659</v>
+        <v>12.502</v>
       </c>
       <c r="V10" t="n">
-        <v>4.75</v>
+        <v>4.604</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.729</v>
+        <v>-12.886</v>
       </c>
     </row>
     <row r="11">
@@ -2417,7 +2417,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.964562509498928</v>
+        <v>-7.094408072556558</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2449,13 +2449,13 @@
         <v>11.217</v>
       </c>
       <c r="U26" t="n">
-        <v>12.659</v>
+        <v>12.502</v>
       </c>
       <c r="V26" t="n">
-        <v>4.75</v>
+        <v>4.604</v>
       </c>
       <c r="W26" t="n">
-        <v>-12.729</v>
+        <v>-12.886</v>
       </c>
     </row>
     <row r="27">
@@ -3420,14 +3420,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.93% / +11.34% / 0.00% | TKFEN.IS: +43.05% / +48.34% / -0.56%</t>
+          <t>ENERY.IS: +9.95% / +11.32% / 0.00% | TKFEN.IS: +44.12% / +48.36% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>17.23750265346325</v>
+        <v>17.78904658142388</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3459,13 +3459,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>52.445</v>
+        <v>53.162</v>
       </c>
       <c r="V12" t="n">
-        <v>63.359</v>
+        <v>64.128</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.843</v>
+        <v>-7.126</v>
       </c>
     </row>
     <row r="13">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.93% / +11.34% / 0.00% | TKFEN.IS: +43.05% / +48.34% / -0.56%</t>
+          <t>ENERY.IS: +9.95% / +11.32% / 0.00% | TKFEN.IS: +44.12% / +48.36% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>17.23750265346325</v>
+        <v>17.78904658142388</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4438,13 +4438,13 @@
         <v>28.439</v>
       </c>
       <c r="U26" t="n">
-        <v>52.445</v>
+        <v>53.162</v>
       </c>
       <c r="V26" t="n">
-        <v>63.359</v>
+        <v>64.128</v>
       </c>
       <c r="W26" t="n">
-        <v>-7.843</v>
+        <v>-7.126</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -3420,14 +3420,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.95% / +11.32% / 0.00% | TKFEN.IS: +44.12% / +48.36% / -0.56%</t>
+          <t>ENERY.IS: +9.94% / +11.32% / 0.00% | TKFEN.IS: +44.12% / +48.36% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>17.78904658142388</v>
+        <v>17.78885339502336</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3465,7 +3465,7 @@
         <v>64.128</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.126</v>
+        <v>-7.127</v>
       </c>
     </row>
     <row r="13">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ENERY.IS: +9.95% / +11.32% / 0.00% | TKFEN.IS: +44.12% / +48.36% / -0.56%</t>
+          <t>ENERY.IS: +9.94% / +11.32% / 0.00% | TKFEN.IS: +44.12% / +48.36% / -0.56%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K26" t="n">
-        <v>17.78904658142388</v>
+        <v>17.78885339502336</v>
       </c>
       <c r="L26" t="n">
         <v>31.31195090134997</v>
@@ -4444,7 +4444,7 @@
         <v>64.128</v>
       </c>
       <c r="W26" t="n">
-        <v>-7.126</v>
+        <v>-7.127</v>
       </c>
     </row>
   </sheetData>
